--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -6888,17 +6888,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>researcher</t>
+          <t>researcher role</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that is a researcher but unclear what discipline.</t>
+          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>occupational role</t>
         </is>
       </c>
       <c r="E108" s="2" t="n"/>
@@ -7089,7 +7089,7 @@
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="2" t="n"/>
       <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="n"/>
       <c r="R111" s="2" t="n"/>
       <c r="S111" s="2" t="n"/>
       <c r="T111" s="2" t="inlineStr">

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>researcher role</t>
+          <t>researcher</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>occupational role</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E108" s="2" t="n"/>

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -535,27 +535,27 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Curation status</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>To be reviewed by</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer query</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Definition_ID</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Curator</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Curation status</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>To be reviewed by</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Definition_ID</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Reviewer query</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
         </is>
       </c>
       <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
@@ -657,12 +657,12 @@
         </is>
       </c>
       <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
@@ -709,12 +709,12 @@
         </is>
       </c>
       <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="n"/>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -769,12 +769,12 @@
         </is>
       </c>
       <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n"/>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="n"/>
       <c r="Y5" s="2" t="inlineStr">
         <is>
@@ -833,12 +833,12 @@
         </is>
       </c>
       <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="n"/>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="n"/>
       <c r="Y6" s="2" t="n"/>
       <c r="Z6" s="2" t="n"/>
@@ -893,12 +893,12 @@
         </is>
       </c>
       <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="n"/>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="n"/>
       <c r="X7" s="2" t="n"/>
       <c r="Y7" s="2" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
         </is>
       </c>
       <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="n"/>
       <c r="X8" s="2" t="n"/>
       <c r="Y8" s="2" t="inlineStr">
         <is>
@@ -1021,12 +1021,12 @@
         </is>
       </c>
       <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n"/>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="n"/>
       <c r="X9" s="2" t="n"/>
       <c r="Y9" s="2" t="inlineStr">
         <is>
@@ -1081,12 +1081,12 @@
         </is>
       </c>
       <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="n"/>
       <c r="Y10" s="2" t="inlineStr">
         <is>
@@ -1145,12 +1145,12 @@
         </is>
       </c>
       <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n"/>
       <c r="X11" s="2" t="n"/>
       <c r="Y11" s="2" t="inlineStr">
         <is>
@@ -1209,12 +1209,12 @@
         </is>
       </c>
       <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n"/>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="n"/>
       <c r="X12" s="2" t="n"/>
       <c r="Y12" s="2" t="inlineStr">
         <is>
@@ -1273,12 +1273,12 @@
         </is>
       </c>
       <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n"/>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="n"/>
       <c r="X13" s="2" t="n"/>
       <c r="Y13" s="2" t="inlineStr">
         <is>
@@ -1331,17 +1331,17 @@
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>JH</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n"/>
       <c r="X14" s="2" t="n"/>
       <c r="Y14" s="2" t="n"/>
-      <c r="Z14" s="2" t="n"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1393,12 +1393,12 @@
         </is>
       </c>
       <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="n"/>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="n"/>
       <c r="X15" s="2" t="n"/>
       <c r="Y15" s="2" t="inlineStr">
         <is>
@@ -1453,12 +1453,12 @@
         </is>
       </c>
       <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="n"/>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="n"/>
       <c r="Z16" s="2" t="n"/>
@@ -1513,12 +1513,12 @@
         </is>
       </c>
       <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="n"/>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="n"/>
       <c r="Y17" s="2" t="inlineStr">
         <is>
@@ -1573,12 +1573,12 @@
         </is>
       </c>
       <c r="U18" s="2" t="n"/>
-      <c r="V18" s="2" t="n"/>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n"/>
       <c r="X18" s="2" t="n"/>
       <c r="Y18" s="2" t="n"/>
       <c r="Z18" s="2" t="n"/>
@@ -1633,12 +1633,12 @@
         </is>
       </c>
       <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="n"/>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="n"/>
       <c r="Y19" s="2" t="inlineStr">
         <is>
@@ -1689,12 +1689,12 @@
         </is>
       </c>
       <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="n"/>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="n"/>
       <c r="Y20" s="2" t="n"/>
       <c r="Z20" s="2" t="n"/>
@@ -1749,12 +1749,12 @@
         </is>
       </c>
       <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="n"/>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="n"/>
       <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="inlineStr">
         <is>
@@ -1813,12 +1813,12 @@
         </is>
       </c>
       <c r="U22" s="2" t="n"/>
-      <c r="V22" s="2" t="n"/>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="n"/>
       <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
@@ -1877,12 +1877,12 @@
         </is>
       </c>
       <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="n"/>
       <c r="Y23" s="2" t="inlineStr">
         <is>
@@ -1941,12 +1941,12 @@
         </is>
       </c>
       <c r="U24" s="2" t="n"/>
-      <c r="V24" s="2" t="n"/>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="inlineStr">
         <is>
@@ -2005,12 +2005,12 @@
         </is>
       </c>
       <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="n"/>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="n"/>
       <c r="X25" s="2" t="n"/>
       <c r="Y25" s="2" t="inlineStr">
         <is>
@@ -2069,12 +2069,12 @@
         </is>
       </c>
       <c r="U26" s="2" t="n"/>
-      <c r="V26" s="2" t="n"/>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="n"/>
       <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
@@ -2131,17 +2131,17 @@
       <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="n"/>
       <c r="X27" s="2" t="n"/>
       <c r="Y27" s="2" t="n"/>
-      <c r="Z27" s="2" t="n"/>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2193,12 +2193,12 @@
         </is>
       </c>
       <c r="U28" s="2" t="n"/>
-      <c r="V28" s="2" t="n"/>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="n"/>
       <c r="X28" s="2" t="n"/>
       <c r="Y28" s="2" t="n"/>
       <c r="Z28" s="2" t="n"/>
@@ -2249,12 +2249,12 @@
         </is>
       </c>
       <c r="U29" s="2" t="n"/>
-      <c r="V29" s="2" t="n"/>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="n"/>
       <c r="X29" s="2" t="n"/>
       <c r="Y29" s="2" t="n"/>
       <c r="Z29" s="2" t="n"/>
@@ -2309,12 +2309,12 @@
         </is>
       </c>
       <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="n"/>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="n"/>
       <c r="X30" s="2" t="n"/>
       <c r="Y30" s="2" t="inlineStr">
         <is>
@@ -2373,12 +2373,12 @@
         </is>
       </c>
       <c r="U31" s="2" t="n"/>
-      <c r="V31" s="2" t="n"/>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="n"/>
       <c r="X31" s="2" t="n"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
@@ -2429,12 +2429,12 @@
         </is>
       </c>
       <c r="U32" s="2" t="n"/>
-      <c r="V32" s="2" t="n"/>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="n"/>
       <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="n"/>
       <c r="Z32" s="2" t="n"/>
@@ -2481,12 +2481,12 @@
         </is>
       </c>
       <c r="U33" s="2" t="n"/>
-      <c r="V33" s="2" t="n"/>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="n"/>
       <c r="X33" s="2" t="n"/>
       <c r="Y33" s="2" t="n"/>
       <c r="Z33" s="2" t="n"/>
@@ -2541,12 +2541,12 @@
         </is>
       </c>
       <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="n"/>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="n"/>
       <c r="X34" s="2" t="n"/>
       <c r="Y34" s="2" t="inlineStr">
         <is>
@@ -2607,12 +2607,12 @@
         </is>
       </c>
       <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="n"/>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="n"/>
       <c r="X35" s="2" t="n"/>
       <c r="Y35" s="2" t="inlineStr">
         <is>
@@ -2667,12 +2667,12 @@
         </is>
       </c>
       <c r="U36" s="2" t="n"/>
-      <c r="V36" s="2" t="n"/>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="n"/>
       <c r="X36" s="2" t="n"/>
       <c r="Y36" s="2" t="n"/>
       <c r="Z36" s="2" t="n"/>
@@ -2727,12 +2727,12 @@
         </is>
       </c>
       <c r="U37" s="2" t="n"/>
-      <c r="V37" s="2" t="n"/>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="n"/>
       <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="n"/>
       <c r="Z37" s="2" t="n"/>
@@ -2783,12 +2783,12 @@
         </is>
       </c>
       <c r="U38" s="2" t="n"/>
-      <c r="V38" s="2" t="n"/>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="n"/>
       <c r="X38" s="2" t="n"/>
       <c r="Y38" s="2" t="n"/>
       <c r="Z38" s="2" t="n"/>
@@ -2837,17 +2837,17 @@
       <c r="U39" s="2" t="n"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="n"/>
       <c r="X39" s="2" t="n"/>
       <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="n"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2897,17 +2897,17 @@
       <c r="U40" s="2" t="n"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="n"/>
       <c r="X40" s="2" t="n"/>
       <c r="Y40" s="2" t="n"/>
-      <c r="Z40" s="2" t="n"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
         </is>
       </c>
       <c r="U41" s="2" t="n"/>
-      <c r="V41" s="2" t="n"/>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="n"/>
       <c r="X41" s="2" t="n"/>
       <c r="Y41" s="2" t="inlineStr">
         <is>
@@ -3015,12 +3015,12 @@
         </is>
       </c>
       <c r="U42" s="2" t="n"/>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="n"/>
       <c r="X42" s="2" t="n"/>
       <c r="Y42" s="2" t="n"/>
       <c r="Z42" s="2" t="n"/>
@@ -3069,17 +3069,17 @@
       <c r="U43" s="2" t="n"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="n"/>
       <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="n"/>
-      <c r="Z43" s="2" t="n"/>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3127,12 +3127,12 @@
         </is>
       </c>
       <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="n"/>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="n"/>
       <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
@@ -3187,12 +3187,12 @@
         </is>
       </c>
       <c r="U45" s="2" t="n"/>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="n"/>
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
@@ -3247,12 +3247,12 @@
         </is>
       </c>
       <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
@@ -3307,12 +3307,12 @@
         </is>
       </c>
       <c r="U47" s="2" t="n"/>
-      <c r="V47" s="2" t="n"/>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="n"/>
       <c r="X47" s="2" t="n"/>
       <c r="Y47" s="2" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
         </is>
       </c>
       <c r="U48" s="2" t="n"/>
-      <c r="V48" s="2" t="n"/>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="n"/>
       <c r="X48" s="2" t="n"/>
       <c r="Y48" s="2" t="inlineStr">
         <is>
@@ -3435,12 +3435,12 @@
         </is>
       </c>
       <c r="U49" s="2" t="n"/>
-      <c r="V49" s="2" t="n"/>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="n"/>
       <c r="X49" s="2" t="n"/>
       <c r="Y49" s="2" t="inlineStr">
         <is>
@@ -3495,12 +3495,12 @@
         </is>
       </c>
       <c r="U50" s="2" t="n"/>
-      <c r="V50" s="2" t="n"/>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="n"/>
       <c r="X50" s="2" t="n"/>
       <c r="Y50" s="2" t="n"/>
       <c r="Z50" s="2" t="n"/>
@@ -3551,12 +3551,12 @@
         </is>
       </c>
       <c r="U51" s="2" t="n"/>
-      <c r="V51" s="2" t="n"/>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="n"/>
       <c r="X51" s="2" t="n"/>
       <c r="Y51" s="2" t="n"/>
       <c r="Z51" s="2" t="n"/>
@@ -3611,12 +3611,12 @@
         </is>
       </c>
       <c r="U52" s="2" t="n"/>
-      <c r="V52" s="2" t="n"/>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="n"/>
       <c r="X52" s="2" t="n"/>
       <c r="Y52" s="2" t="inlineStr">
         <is>
@@ -3667,12 +3667,12 @@
         </is>
       </c>
       <c r="U53" s="2" t="n"/>
-      <c r="V53" s="2" t="n"/>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="n"/>
       <c r="X53" s="2" t="n"/>
       <c r="Y53" s="2" t="n"/>
       <c r="Z53" s="2" t="n"/>
@@ -3727,12 +3727,12 @@
         </is>
       </c>
       <c r="U54" s="2" t="n"/>
-      <c r="V54" s="2" t="n"/>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="n"/>
       <c r="X54" s="2" t="n"/>
       <c r="Y54" s="2" t="inlineStr">
         <is>
@@ -3787,12 +3787,12 @@
         </is>
       </c>
       <c r="U55" s="2" t="n"/>
-      <c r="V55" s="2" t="n"/>
-      <c r="W55" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="n"/>
       <c r="X55" s="2" t="n"/>
       <c r="Y55" s="2" t="n"/>
       <c r="Z55" s="2" t="n"/>
@@ -3843,12 +3843,12 @@
         </is>
       </c>
       <c r="U56" s="2" t="n"/>
-      <c r="V56" s="2" t="n"/>
-      <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="n"/>
       <c r="X56" s="2" t="n"/>
       <c r="Y56" s="2" t="n"/>
       <c r="Z56" s="2" t="n"/>
@@ -3903,12 +3903,12 @@
         </is>
       </c>
       <c r="U57" s="2" t="n"/>
-      <c r="V57" s="2" t="n"/>
-      <c r="W57" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="n"/>
       <c r="X57" s="2" t="n"/>
       <c r="Y57" s="2" t="inlineStr">
         <is>
@@ -3967,12 +3967,12 @@
         </is>
       </c>
       <c r="U58" s="2" t="n"/>
-      <c r="V58" s="2" t="n"/>
-      <c r="W58" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="n"/>
       <c r="X58" s="2" t="n"/>
       <c r="Y58" s="2" t="inlineStr">
         <is>
@@ -4027,12 +4027,12 @@
         </is>
       </c>
       <c r="U59" s="2" t="n"/>
-      <c r="V59" s="2" t="n"/>
-      <c r="W59" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="n"/>
       <c r="X59" s="2" t="n"/>
       <c r="Y59" s="2" t="inlineStr">
         <is>
@@ -4091,12 +4091,12 @@
         </is>
       </c>
       <c r="U60" s="2" t="n"/>
-      <c r="V60" s="2" t="n"/>
-      <c r="W60" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="n"/>
       <c r="X60" s="2" t="n"/>
       <c r="Y60" s="2" t="inlineStr">
         <is>
@@ -4151,12 +4151,12 @@
         </is>
       </c>
       <c r="U61" s="2" t="n"/>
-      <c r="V61" s="2" t="n"/>
-      <c r="W61" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="n"/>
       <c r="X61" s="2" t="n"/>
       <c r="Y61" s="2" t="n"/>
       <c r="Z61" s="2" t="n"/>
@@ -4209,17 +4209,17 @@
       <c r="U62" s="2" t="n"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W62" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="n"/>
       <c r="X62" s="2" t="n"/>
       <c r="Y62" s="2" t="n"/>
-      <c r="Z62" s="2" t="n"/>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
         </is>
       </c>
       <c r="U63" s="2" t="n"/>
-      <c r="V63" s="2" t="n"/>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="n"/>
       <c r="X63" s="2" t="n"/>
       <c r="Y63" s="2" t="inlineStr">
         <is>
@@ -4331,12 +4331,12 @@
         </is>
       </c>
       <c r="U64" s="2" t="n"/>
-      <c r="V64" s="2" t="n"/>
-      <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="n"/>
       <c r="X64" s="2" t="n"/>
       <c r="Y64" s="2" t="n"/>
       <c r="Z64" s="2" t="n"/>
@@ -4391,12 +4391,12 @@
         </is>
       </c>
       <c r="U65" s="2" t="n"/>
-      <c r="V65" s="2" t="n"/>
-      <c r="W65" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="n"/>
       <c r="X65" s="2" t="n"/>
       <c r="Y65" s="2" t="inlineStr">
         <is>
@@ -4455,12 +4455,12 @@
         </is>
       </c>
       <c r="U66" s="2" t="n"/>
-      <c r="V66" s="2" t="n"/>
-      <c r="W66" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="n"/>
       <c r="X66" s="2" t="n"/>
       <c r="Y66" s="2" t="inlineStr">
         <is>
@@ -4519,12 +4519,12 @@
         </is>
       </c>
       <c r="U67" s="2" t="n"/>
-      <c r="V67" s="2" t="n"/>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="n"/>
       <c r="X67" s="2" t="n"/>
       <c r="Y67" s="2" t="inlineStr">
         <is>
@@ -4583,12 +4583,12 @@
         </is>
       </c>
       <c r="U68" s="2" t="n"/>
-      <c r="V68" s="2" t="n"/>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="n"/>
       <c r="X68" s="2" t="n"/>
       <c r="Y68" s="2" t="inlineStr">
         <is>
@@ -4647,12 +4647,12 @@
         </is>
       </c>
       <c r="U69" s="2" t="n"/>
-      <c r="V69" s="2" t="n"/>
-      <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="n"/>
       <c r="X69" s="2" t="n"/>
       <c r="Y69" s="2" t="inlineStr">
         <is>
@@ -4707,12 +4707,12 @@
         </is>
       </c>
       <c r="U70" s="2" t="n"/>
-      <c r="V70" s="2" t="n"/>
-      <c r="W70" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="n"/>
       <c r="X70" s="2" t="n"/>
       <c r="Y70" s="2" t="n"/>
       <c r="Z70" s="2" t="n"/>
@@ -4767,12 +4767,12 @@
         </is>
       </c>
       <c r="U71" s="2" t="n"/>
-      <c r="V71" s="2" t="n"/>
-      <c r="W71" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="n"/>
       <c r="X71" s="2" t="n"/>
       <c r="Y71" s="2" t="inlineStr">
         <is>
@@ -4827,12 +4827,12 @@
         </is>
       </c>
       <c r="U72" s="2" t="n"/>
-      <c r="V72" s="2" t="n"/>
-      <c r="W72" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="n"/>
       <c r="X72" s="2" t="n"/>
       <c r="Y72" s="2" t="n"/>
       <c r="Z72" s="2" t="n"/>
@@ -4883,12 +4883,12 @@
         </is>
       </c>
       <c r="U73" s="2" t="n"/>
-      <c r="V73" s="2" t="n"/>
-      <c r="W73" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="n"/>
       <c r="X73" s="2" t="n"/>
       <c r="Y73" s="2" t="n"/>
       <c r="Z73" s="2" t="n"/>
@@ -4943,12 +4943,12 @@
         </is>
       </c>
       <c r="U74" s="2" t="n"/>
-      <c r="V74" s="2" t="n"/>
-      <c r="W74" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="n"/>
       <c r="X74" s="2" t="n"/>
       <c r="Y74" s="2" t="inlineStr">
         <is>
@@ -5003,12 +5003,12 @@
         </is>
       </c>
       <c r="U75" s="2" t="n"/>
-      <c r="V75" s="2" t="n"/>
-      <c r="W75" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="n"/>
       <c r="X75" s="2" t="n"/>
       <c r="Y75" s="2" t="inlineStr">
         <is>
@@ -5067,12 +5067,12 @@
         </is>
       </c>
       <c r="U76" s="2" t="n"/>
-      <c r="V76" s="2" t="n"/>
-      <c r="W76" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="n"/>
       <c r="X76" s="2" t="n"/>
       <c r="Y76" s="2" t="inlineStr">
         <is>
@@ -5131,12 +5131,12 @@
         </is>
       </c>
       <c r="U77" s="2" t="n"/>
-      <c r="V77" s="2" t="n"/>
-      <c r="W77" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="n"/>
       <c r="X77" s="2" t="n"/>
       <c r="Y77" s="2" t="inlineStr">
         <is>
@@ -5191,12 +5191,12 @@
         </is>
       </c>
       <c r="U78" s="2" t="n"/>
-      <c r="V78" s="2" t="n"/>
-      <c r="W78" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="n"/>
       <c r="X78" s="2" t="n"/>
       <c r="Y78" s="2" t="n"/>
       <c r="Z78" s="2" t="n"/>
@@ -5251,12 +5251,12 @@
         </is>
       </c>
       <c r="U79" s="2" t="n"/>
-      <c r="V79" s="2" t="n"/>
-      <c r="W79" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="n"/>
       <c r="X79" s="2" t="n"/>
       <c r="Y79" s="2" t="inlineStr">
         <is>
@@ -5313,17 +5313,17 @@
       <c r="U80" s="2" t="n"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>BG; PS</t>
-        </is>
-      </c>
-      <c r="W80" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="n"/>
       <c r="X80" s="2" t="n"/>
       <c r="Y80" s="2" t="n"/>
-      <c r="Z80" s="2" t="n"/>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>BG; PS</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
         </is>
       </c>
       <c r="U81" s="2" t="n"/>
-      <c r="V81" s="2" t="n"/>
-      <c r="W81" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="n"/>
       <c r="X81" s="2" t="n"/>
       <c r="Y81" s="2" t="n"/>
       <c r="Z81" s="2" t="n"/>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
           <t>RW</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>External</t>
         </is>
       </c>
     </row>
@@ -5465,12 +5465,12 @@
         </is>
       </c>
       <c r="U83" s="2" t="n"/>
-      <c r="V83" s="2" t="n"/>
-      <c r="W83" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="n"/>
       <c r="X83" s="2" t="n"/>
       <c r="Y83" s="2" t="n"/>
       <c r="Z83" s="2" t="n"/>
@@ -5525,12 +5525,12 @@
         </is>
       </c>
       <c r="U84" s="2" t="n"/>
-      <c r="V84" s="2" t="n"/>
-      <c r="W84" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="n"/>
       <c r="X84" s="2" t="n"/>
       <c r="Y84" s="2" t="inlineStr">
         <is>
@@ -5585,12 +5585,12 @@
         </is>
       </c>
       <c r="U85" s="2" t="n"/>
-      <c r="V85" s="2" t="n"/>
-      <c r="W85" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="n"/>
       <c r="X85" s="2" t="n"/>
       <c r="Y85" s="2" t="n"/>
       <c r="Z85" s="2" t="n"/>
@@ -5641,12 +5641,12 @@
         </is>
       </c>
       <c r="U86" s="2" t="n"/>
-      <c r="V86" s="2" t="n"/>
-      <c r="W86" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="n"/>
       <c r="X86" s="2" t="n"/>
       <c r="Y86" s="2" t="n"/>
       <c r="Z86" s="2" t="n"/>
@@ -5693,12 +5693,12 @@
         </is>
       </c>
       <c r="U87" s="2" t="n"/>
-      <c r="V87" s="2" t="n"/>
-      <c r="W87" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="n"/>
       <c r="X87" s="2" t="n"/>
       <c r="Y87" s="2" t="n"/>
       <c r="Z87" s="2" t="n"/>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
           <t>AW</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>External</t>
         </is>
       </c>
     </row>
@@ -5788,17 +5788,17 @@
       <c r="U89" s="2" t="n"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="W89" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="n"/>
       <c r="X89" s="2" t="n"/>
       <c r="Y89" s="2" t="n"/>
-      <c r="Z89" s="2" t="n"/>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
         </is>
       </c>
       <c r="U90" s="2" t="n"/>
-      <c r="V90" s="2" t="n"/>
-      <c r="W90" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="n"/>
       <c r="X90" s="2" t="n"/>
       <c r="Y90" s="2" t="n"/>
       <c r="Z90" s="2" t="n"/>
@@ -5902,12 +5902,12 @@
         </is>
       </c>
       <c r="U91" s="2" t="n"/>
-      <c r="V91" s="2" t="n"/>
-      <c r="W91" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="n"/>
       <c r="X91" s="2" t="n"/>
       <c r="Y91" s="2" t="inlineStr">
         <is>
@@ -5958,12 +5958,12 @@
         </is>
       </c>
       <c r="U92" s="2" t="n"/>
-      <c r="V92" s="2" t="n"/>
-      <c r="W92" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="n"/>
       <c r="X92" s="2" t="n"/>
       <c r="Y92" s="2" t="n"/>
       <c r="Z92" s="2" t="n"/>
@@ -6018,12 +6018,12 @@
         </is>
       </c>
       <c r="U93" s="2" t="n"/>
-      <c r="V93" s="2" t="n"/>
-      <c r="W93" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="n"/>
       <c r="X93" s="2" t="n"/>
       <c r="Y93" s="2" t="inlineStr">
         <is>
@@ -6082,12 +6082,12 @@
         </is>
       </c>
       <c r="U94" s="2" t="n"/>
-      <c r="V94" s="2" t="n"/>
-      <c r="W94" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="n"/>
       <c r="X94" s="2" t="n"/>
       <c r="Y94" s="2" t="inlineStr">
         <is>
@@ -6146,12 +6146,12 @@
         </is>
       </c>
       <c r="U95" s="2" t="n"/>
-      <c r="V95" s="2" t="n"/>
-      <c r="W95" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="n"/>
       <c r="X95" s="2" t="n"/>
       <c r="Y95" s="2" t="inlineStr">
         <is>
@@ -6210,12 +6210,12 @@
         </is>
       </c>
       <c r="U96" s="2" t="n"/>
-      <c r="V96" s="2" t="n"/>
-      <c r="W96" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="n"/>
       <c r="X96" s="2" t="n"/>
       <c r="Y96" s="2" t="inlineStr">
         <is>
@@ -6274,12 +6274,12 @@
         </is>
       </c>
       <c r="U97" s="2" t="n"/>
-      <c r="V97" s="2" t="n"/>
-      <c r="W97" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="n"/>
       <c r="X97" s="2" t="n"/>
       <c r="Y97" s="2" t="inlineStr">
         <is>
@@ -6334,12 +6334,12 @@
         </is>
       </c>
       <c r="U98" s="2" t="n"/>
-      <c r="V98" s="2" t="n"/>
-      <c r="W98" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="n"/>
       <c r="X98" s="2" t="n"/>
       <c r="Y98" s="2" t="n"/>
       <c r="Z98" s="2" t="n"/>
@@ -6390,12 +6390,12 @@
         </is>
       </c>
       <c r="U99" s="2" t="n"/>
-      <c r="V99" s="2" t="n"/>
-      <c r="W99" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="n"/>
       <c r="X99" s="2" t="n"/>
       <c r="Y99" s="2" t="inlineStr">
         <is>
@@ -6450,12 +6450,12 @@
         </is>
       </c>
       <c r="U100" s="2" t="n"/>
-      <c r="V100" s="2" t="n"/>
-      <c r="W100" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="n"/>
       <c r="X100" s="2" t="n"/>
       <c r="Y100" s="2" t="inlineStr">
         <is>
@@ -6514,12 +6514,12 @@
         </is>
       </c>
       <c r="U101" s="2" t="n"/>
-      <c r="V101" s="2" t="n"/>
-      <c r="W101" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="n"/>
       <c r="X101" s="2" t="n"/>
       <c r="Y101" s="2" t="inlineStr">
         <is>
@@ -6570,12 +6570,12 @@
         </is>
       </c>
       <c r="U102" s="2" t="n"/>
-      <c r="V102" s="2" t="n"/>
-      <c r="W102" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="n"/>
       <c r="X102" s="2" t="n"/>
       <c r="Y102" s="2" t="n"/>
       <c r="Z102" s="2" t="n"/>
@@ -6630,12 +6630,12 @@
         </is>
       </c>
       <c r="U103" s="2" t="n"/>
-      <c r="V103" s="2" t="n"/>
-      <c r="W103" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="n"/>
       <c r="X103" s="2" t="n"/>
       <c r="Y103" s="2" t="inlineStr">
         <is>
@@ -6686,12 +6686,12 @@
         </is>
       </c>
       <c r="U104" s="2" t="n"/>
-      <c r="V104" s="2" t="n"/>
-      <c r="W104" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="n"/>
       <c r="X104" s="2" t="n"/>
       <c r="Y104" s="2" t="n"/>
       <c r="Z104" s="2" t="n"/>
@@ -6746,12 +6746,12 @@
         </is>
       </c>
       <c r="U105" s="2" t="n"/>
-      <c r="V105" s="2" t="n"/>
-      <c r="W105" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="n"/>
       <c r="X105" s="2" t="n"/>
       <c r="Y105" s="2" t="inlineStr">
         <is>
@@ -6806,12 +6806,12 @@
         </is>
       </c>
       <c r="U106" s="2" t="n"/>
-      <c r="V106" s="2" t="n"/>
-      <c r="W106" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="n"/>
       <c r="X106" s="2" t="n"/>
       <c r="Y106" s="2" t="n"/>
       <c r="Z106" s="2" t="n"/>
@@ -6866,12 +6866,12 @@
         </is>
       </c>
       <c r="U107" s="2" t="n"/>
-      <c r="V107" s="2" t="n"/>
-      <c r="W107" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="n"/>
       <c r="X107" s="2" t="n"/>
       <c r="Y107" s="2" t="inlineStr">
         <is>
@@ -6926,12 +6926,12 @@
         </is>
       </c>
       <c r="U108" s="2" t="n"/>
-      <c r="V108" s="2" t="n"/>
-      <c r="W108" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="n"/>
       <c r="X108" s="2" t="n"/>
       <c r="Y108" s="2" t="n"/>
       <c r="Z108" s="2" t="n"/>
@@ -6982,12 +6982,12 @@
         </is>
       </c>
       <c r="U109" s="2" t="n"/>
-      <c r="V109" s="2" t="n"/>
-      <c r="W109" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="n"/>
       <c r="X109" s="2" t="n"/>
       <c r="Y109" s="2" t="n"/>
       <c r="Z109" s="2" t="n"/>
@@ -7042,12 +7042,12 @@
         </is>
       </c>
       <c r="U110" s="2" t="n"/>
-      <c r="V110" s="2" t="n"/>
-      <c r="W110" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="n"/>
       <c r="X110" s="2" t="n"/>
       <c r="Y110" s="2" t="inlineStr">
         <is>
@@ -7098,12 +7098,12 @@
         </is>
       </c>
       <c r="U111" s="2" t="n"/>
-      <c r="V111" s="2" t="n"/>
-      <c r="W111" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="n"/>
       <c r="X111" s="2" t="n"/>
       <c r="Y111" s="2" t="n"/>
       <c r="Z111" s="2" t="n"/>
@@ -7158,12 +7158,12 @@
         </is>
       </c>
       <c r="U112" s="2" t="n"/>
-      <c r="V112" s="2" t="n"/>
-      <c r="W112" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="n"/>
       <c r="X112" s="2" t="n"/>
       <c r="Y112" s="2" t="inlineStr">
         <is>
@@ -7222,12 +7222,12 @@
         </is>
       </c>
       <c r="U113" s="2" t="n"/>
-      <c r="V113" s="2" t="n"/>
-      <c r="W113" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="n"/>
       <c r="X113" s="2" t="n"/>
       <c r="Y113" s="2" t="inlineStr">
         <is>
@@ -7282,12 +7282,12 @@
         </is>
       </c>
       <c r="U114" s="2" t="n"/>
-      <c r="V114" s="2" t="n"/>
-      <c r="W114" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="n"/>
       <c r="X114" s="2" t="n"/>
       <c r="Y114" s="2" t="inlineStr">
         <is>
@@ -7342,12 +7342,12 @@
         </is>
       </c>
       <c r="U115" s="2" t="n"/>
-      <c r="V115" s="2" t="n"/>
-      <c r="W115" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="n"/>
       <c r="X115" s="2" t="n"/>
       <c r="Y115" s="2" t="n"/>
       <c r="Z115" s="2" t="n"/>
@@ -7402,12 +7402,12 @@
         </is>
       </c>
       <c r="U116" s="2" t="n"/>
-      <c r="V116" s="2" t="n"/>
-      <c r="W116" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="n"/>
       <c r="X116" s="2" t="n"/>
       <c r="Y116" s="2" t="inlineStr">
         <is>
@@ -7466,12 +7466,12 @@
         </is>
       </c>
       <c r="U117" s="2" t="n"/>
-      <c r="V117" s="2" t="n"/>
-      <c r="W117" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W117" s="2" t="n"/>
       <c r="X117" s="2" t="n"/>
       <c r="Y117" s="2" t="inlineStr">
         <is>
@@ -7530,12 +7530,12 @@
         </is>
       </c>
       <c r="U118" s="2" t="n"/>
-      <c r="V118" s="2" t="n"/>
-      <c r="W118" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="n"/>
       <c r="X118" s="2" t="n"/>
       <c r="Y118" s="2" t="inlineStr">
         <is>
@@ -7594,12 +7594,12 @@
         </is>
       </c>
       <c r="U119" s="2" t="n"/>
-      <c r="V119" s="2" t="n"/>
-      <c r="W119" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W119" s="2" t="n"/>
       <c r="X119" s="2" t="n"/>
       <c r="Y119" s="2" t="inlineStr">
         <is>
@@ -7654,12 +7654,12 @@
         </is>
       </c>
       <c r="U120" s="2" t="n"/>
-      <c r="V120" s="2" t="n"/>
-      <c r="W120" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W120" s="2" t="n"/>
       <c r="X120" s="2" t="n"/>
       <c r="Y120" s="2" t="n"/>
       <c r="Z120" s="2" t="n"/>
@@ -7706,12 +7706,12 @@
         </is>
       </c>
       <c r="U121" s="2" t="n"/>
-      <c r="V121" s="2" t="n"/>
-      <c r="W121" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W121" s="2" t="n"/>
       <c r="X121" s="2" t="n"/>
       <c r="Y121" s="2" t="n"/>
       <c r="Z121" s="2" t="n"/>
@@ -7758,12 +7758,12 @@
         </is>
       </c>
       <c r="U122" s="2" t="n"/>
-      <c r="V122" s="2" t="n"/>
-      <c r="W122" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W122" s="2" t="n"/>
       <c r="X122" s="2" t="n"/>
       <c r="Y122" s="2" t="n"/>
       <c r="Z122" s="2" t="n"/>
@@ -7810,12 +7810,12 @@
         </is>
       </c>
       <c r="U123" s="2" t="n"/>
-      <c r="V123" s="2" t="n"/>
-      <c r="W123" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="n"/>
       <c r="X123" s="2" t="n"/>
       <c r="Y123" s="2" t="n"/>
       <c r="Z123" s="2" t="n"/>
@@ -7870,12 +7870,12 @@
         </is>
       </c>
       <c r="U124" s="2" t="n"/>
-      <c r="V124" s="2" t="n"/>
-      <c r="W124" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="n"/>
       <c r="X124" s="2" t="n"/>
       <c r="Y124" s="2" t="inlineStr">
         <is>
@@ -7934,12 +7934,12 @@
         </is>
       </c>
       <c r="U125" s="2" t="n"/>
-      <c r="V125" s="2" t="n"/>
-      <c r="W125" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="n"/>
       <c r="X125" s="2" t="n"/>
       <c r="Y125" s="2" t="inlineStr">
         <is>
@@ -7998,12 +7998,12 @@
         </is>
       </c>
       <c r="U126" s="2" t="n"/>
-      <c r="V126" s="2" t="n"/>
-      <c r="W126" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="n"/>
       <c r="X126" s="2" t="n"/>
       <c r="Y126" s="2" t="inlineStr">
         <is>
@@ -8062,12 +8062,12 @@
         </is>
       </c>
       <c r="U127" s="2" t="n"/>
-      <c r="V127" s="2" t="n"/>
-      <c r="W127" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W127" s="2" t="n"/>
       <c r="X127" s="2" t="n"/>
       <c r="Y127" s="2" t="inlineStr">
         <is>
@@ -8122,12 +8122,12 @@
         </is>
       </c>
       <c r="U128" s="2" t="n"/>
-      <c r="V128" s="2" t="n"/>
-      <c r="W128" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W128" s="2" t="n"/>
       <c r="X128" s="2" t="n"/>
       <c r="Y128" s="2" t="n"/>
       <c r="Z128" s="2" t="n"/>
@@ -8176,17 +8176,17 @@
       <c r="U129" s="2" t="n"/>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W129" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W129" s="2" t="n"/>
       <c r="X129" s="2" t="n"/>
       <c r="Y129" s="2" t="n"/>
-      <c r="Z129" s="2" t="n"/>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
         </is>
       </c>
       <c r="U130" s="2" t="n"/>
-      <c r="V130" s="2" t="n"/>
-      <c r="W130" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="n"/>
       <c r="X130" s="2" t="n"/>
       <c r="Y130" s="2" t="n"/>
       <c r="Z130" s="2" t="n"/>
@@ -8294,12 +8294,12 @@
         </is>
       </c>
       <c r="U131" s="2" t="n"/>
-      <c r="V131" s="2" t="n"/>
-      <c r="W131" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="n"/>
       <c r="X131" s="2" t="n"/>
       <c r="Y131" s="2" t="n"/>
       <c r="Z131" s="2" t="n"/>
@@ -8354,12 +8354,12 @@
         </is>
       </c>
       <c r="U132" s="2" t="n"/>
-      <c r="V132" s="2" t="n"/>
-      <c r="W132" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="n"/>
       <c r="X132" s="2" t="n"/>
       <c r="Y132" s="2" t="inlineStr">
         <is>
@@ -8418,12 +8418,12 @@
         </is>
       </c>
       <c r="U133" s="2" t="n"/>
-      <c r="V133" s="2" t="n"/>
-      <c r="W133" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="n"/>
       <c r="X133" s="2" t="n"/>
       <c r="Y133" s="2" t="inlineStr">
         <is>
@@ -8478,12 +8478,12 @@
         </is>
       </c>
       <c r="U134" s="2" t="n"/>
-      <c r="V134" s="2" t="n"/>
-      <c r="W134" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W134" s="2" t="n"/>
       <c r="X134" s="2" t="n"/>
       <c r="Y134" s="2" t="inlineStr">
         <is>
@@ -8538,12 +8538,12 @@
         </is>
       </c>
       <c r="U135" s="2" t="n"/>
-      <c r="V135" s="2" t="n"/>
-      <c r="W135" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V135" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W135" s="2" t="n"/>
       <c r="X135" s="2" t="n"/>
       <c r="Y135" s="2" t="n"/>
       <c r="Z135" s="2" t="n"/>
@@ -8598,12 +8598,12 @@
         </is>
       </c>
       <c r="U136" s="2" t="n"/>
-      <c r="V136" s="2" t="n"/>
-      <c r="W136" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V136" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W136" s="2" t="n"/>
       <c r="X136" s="2" t="n"/>
       <c r="Y136" s="2" t="inlineStr">
         <is>
@@ -8662,12 +8662,12 @@
         </is>
       </c>
       <c r="U137" s="2" t="n"/>
-      <c r="V137" s="2" t="n"/>
-      <c r="W137" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V137" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W137" s="2" t="n"/>
       <c r="X137" s="2" t="n"/>
       <c r="Y137" s="2" t="inlineStr">
         <is>
@@ -8679,22 +8679,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>undergraduate student role</t>
+          <t>trainee role</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
@@ -8709,11 +8709,7 @@
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="2" t="n"/>
       <c r="P138" s="2" t="n"/>
-      <c r="Q138" s="2" t="inlineStr">
-        <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
+      <c r="Q138" s="2" t="n"/>
       <c r="R138" s="2" t="n"/>
       <c r="S138" s="2" t="n"/>
       <c r="T138" s="2" t="inlineStr">
@@ -8722,12 +8718,12 @@
         </is>
       </c>
       <c r="U138" s="2" t="n"/>
-      <c r="V138" s="2" t="n"/>
-      <c r="W138" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V138" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W138" s="2" t="n"/>
       <c r="X138" s="2" t="n"/>
       <c r="Y138" s="2" t="n"/>
       <c r="Z138" s="2" t="n"/>
@@ -8735,23 +8731,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">university and higher education teacher
-</t>
+          <t>undergraduate student role</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -8768,14 +8763,10 @@
       <c r="P139" s="2" t="n"/>
       <c r="Q139" s="2" t="inlineStr">
         <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
-      <c r="R139" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>undergraduate student</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="n"/>
       <c r="S139" s="2" t="n"/>
       <c r="T139" s="2" t="inlineStr">
         <is>
@@ -8783,39 +8774,36 @@
         </is>
       </c>
       <c r="U139" s="2" t="n"/>
-      <c r="V139" s="2" t="n"/>
-      <c r="W139" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V139" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W139" s="2" t="n"/>
       <c r="X139" s="2" t="n"/>
-      <c r="Y139" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 231</t>
-        </is>
-      </c>
+      <c r="Y139" s="2" t="n"/>
       <c r="Z139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">veterinarian </t>
+          <t xml:space="preserve">university and higher education teacher
+</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals. </t>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
@@ -8832,7 +8820,7 @@
       <c r="P140" s="2" t="n"/>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr">
@@ -8847,16 +8835,16 @@
         </is>
       </c>
       <c r="U140" s="2" t="n"/>
-      <c r="V140" s="2" t="n"/>
-      <c r="W140" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V140" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W140" s="2" t="n"/>
       <c r="X140" s="2" t="n"/>
       <c r="Y140" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 225</t>
+          <t>ISCO: 231</t>
         </is>
       </c>
       <c r="Z140" s="2" t="n"/>
@@ -8864,22 +8852,22 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>vocational education teacher</t>
+          <t xml:space="preserve">veterinarian </t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges. </t>
+          <t xml:space="preserve">A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals. </t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
@@ -8896,7 +8884,7 @@
       <c r="P141" s="2" t="n"/>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
@@ -8911,16 +8899,16 @@
         </is>
       </c>
       <c r="U141" s="2" t="n"/>
-      <c r="V141" s="2" t="n"/>
-      <c r="W141" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V141" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W141" s="2" t="n"/>
       <c r="X141" s="2" t="n"/>
       <c r="Y141" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 232</t>
+          <t>ISCO: 225</t>
         </is>
       </c>
       <c r="Z141" s="2" t="n"/>
@@ -8928,22 +8916,22 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>vocational training student or trainee role</t>
+          <t>vocational education teacher</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t xml:space="preserve">A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges. </t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
@@ -8958,8 +8946,16 @@
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="2" t="n"/>
       <c r="P142" s="2" t="n"/>
-      <c r="Q142" s="2" t="n"/>
-      <c r="R142" s="2" t="n"/>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S142" s="2" t="n"/>
       <c r="T142" s="2" t="inlineStr">
         <is>
@@ -8967,14 +8963,18 @@
         </is>
       </c>
       <c r="U142" s="2" t="n"/>
-      <c r="V142" s="2" t="n"/>
-      <c r="W142" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V142" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W142" s="2" t="n"/>
       <c r="X142" s="2" t="n"/>
-      <c r="Y142" s="2" t="n"/>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 232</t>
+        </is>
+      </c>
       <c r="Z142" s="2" t="n"/>
     </row>
     <row r="143">
@@ -9027,12 +9027,12 @@
         </is>
       </c>
       <c r="U143" s="2" t="n"/>
-      <c r="V143" s="2" t="n"/>
-      <c r="W143" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W143" s="2" t="n"/>
       <c r="X143" s="2" t="n"/>
       <c r="Y143" s="2" t="n"/>
       <c r="Z143" s="2" t="n"/>

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting. </t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007fffd4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffffff"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,10 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z143"/>
+  <dimension ref="A1:Z144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,27 +541,27 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Curator</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Curation status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>To be reviewed by</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Definition_ID</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Reviewer query</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Definition_ID</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Curator</t>
         </is>
       </c>
     </row>
@@ -601,12 +607,12 @@
         </is>
       </c>
       <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
@@ -657,12 +663,12 @@
         </is>
       </c>
       <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
@@ -709,12 +715,12 @@
         </is>
       </c>
       <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -769,12 +775,12 @@
         </is>
       </c>
       <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="n"/>
+      <c r="V5" s="2" t="n"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="n"/>
       <c r="Y5" s="2" t="inlineStr">
         <is>
@@ -833,12 +839,12 @@
         </is>
       </c>
       <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="n"/>
+      <c r="V6" s="2" t="n"/>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X6" s="2" t="n"/>
       <c r="Y6" s="2" t="n"/>
       <c r="Z6" s="2" t="n"/>
@@ -893,12 +899,12 @@
         </is>
       </c>
       <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="n"/>
+      <c r="V7" s="2" t="n"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X7" s="2" t="n"/>
       <c r="Y7" s="2" t="inlineStr">
         <is>
@@ -957,12 +963,12 @@
         </is>
       </c>
       <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="n"/>
+      <c r="V8" s="2" t="n"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="n"/>
       <c r="Y8" s="2" t="inlineStr">
         <is>
@@ -1021,12 +1027,12 @@
         </is>
       </c>
       <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="n"/>
+      <c r="V9" s="2" t="n"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="n"/>
       <c r="Y9" s="2" t="inlineStr">
         <is>
@@ -1081,12 +1087,12 @@
         </is>
       </c>
       <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="n"/>
       <c r="Y10" s="2" t="inlineStr">
         <is>
@@ -1145,12 +1151,12 @@
         </is>
       </c>
       <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X11" s="2" t="n"/>
       <c r="Y11" s="2" t="inlineStr">
         <is>
@@ -1209,12 +1215,12 @@
         </is>
       </c>
       <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X12" s="2" t="n"/>
       <c r="Y12" s="2" t="inlineStr">
         <is>
@@ -1273,12 +1279,12 @@
         </is>
       </c>
       <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="n"/>
+      <c r="V13" s="2" t="n"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X13" s="2" t="n"/>
       <c r="Y13" s="2" t="inlineStr">
         <is>
@@ -1331,101 +1337,81 @@
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="n"/>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="n"/>
       <c r="Y14" s="2" t="n"/>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>JH</t>
-        </is>
-      </c>
+      <c r="Z14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010057</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">business and administration associate professional </t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">technician and associate professional </t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="n"/>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="n"/>
-      <c r="X15" s="2" t="n"/>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 33</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="n"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>BCIO:030000</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>behaviour change intervention study investigator role</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>researcher</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>carer</t>
+          <t xml:space="preserve">business and administration associate professional </t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -1442,10 +1428,14 @@
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>carer</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="n"/>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
@@ -1453,35 +1443,39 @@
         </is>
       </c>
       <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X16" s="2" t="n"/>
-      <c r="Y16" s="2" t="n"/>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 33</t>
+        </is>
+      </c>
       <c r="Z16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">child care worker </t>
+          <t>carer</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -1498,14 +1492,10 @@
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>carer</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
@@ -1513,39 +1503,35 @@
         </is>
       </c>
       <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X17" s="2" t="n"/>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 5311</t>
-        </is>
-      </c>
+      <c r="Y17" s="2" t="n"/>
       <c r="Z17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>child relationship</t>
+          <t xml:space="preserve">child care worker </t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
@@ -1562,10 +1548,14 @@
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>daughter, son, step-daughter, step-son</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n"/>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
@@ -1573,35 +1563,39 @@
         </is>
       </c>
       <c r="U18" s="2" t="n"/>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X18" s="2" t="n"/>
-      <c r="Y18" s="2" t="n"/>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 5311</t>
+        </is>
+      </c>
       <c r="Z18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">clerical support worker </t>
+          <t>child relationship</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments. </t>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -1618,14 +1612,10 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>daughter, son, step-daughter, step-son</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
@@ -1633,39 +1623,35 @@
         </is>
       </c>
       <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="n"/>
+      <c r="V19" s="2" t="n"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X19" s="2" t="n"/>
-      <c r="Y19" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 4</t>
-        </is>
-      </c>
+      <c r="Y19" s="2" t="n"/>
       <c r="Z19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>colleague</t>
+          <t xml:space="preserve">clerical support worker </t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+          <t xml:space="preserve">An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments. </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -1680,8 +1666,16 @@
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
@@ -1689,35 +1683,39 @@
         </is>
       </c>
       <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X20" s="2" t="n"/>
-      <c r="Y20" s="2" t="n"/>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 4</t>
+        </is>
+      </c>
       <c r="Z20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">community health worker </t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -1732,16 +1730,8 @@
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
@@ -1749,39 +1739,35 @@
         </is>
       </c>
       <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X21" s="2" t="n"/>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 3253</t>
-        </is>
-      </c>
+      <c r="Y21" s="2" t="n"/>
       <c r="Z21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">craft and related trades worker </t>
+          <t xml:space="preserve">community health worker </t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -1798,7 +1784,7 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -1813,16 +1799,16 @@
         </is>
       </c>
       <c r="U22" s="2" t="n"/>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 7</t>
+          <t>ISCO: 3253</t>
         </is>
       </c>
       <c r="Z22" s="2" t="n"/>
@@ -1830,22 +1816,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">creative and performing artist </t>
+          <t xml:space="preserve">craft and related trades worker </t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -1862,7 +1848,7 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -1877,16 +1863,16 @@
         </is>
       </c>
       <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="n"/>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X23" s="2" t="n"/>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 265</t>
+          <t>ISCO: 7</t>
         </is>
       </c>
       <c r="Z23" s="2" t="n"/>
@@ -1894,22 +1880,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dental assistant and therapist </t>
+          <t xml:space="preserve">creative and performing artist </t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
@@ -1926,7 +1912,7 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -1941,16 +1927,16 @@
         </is>
       </c>
       <c r="U24" s="2" t="n"/>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3251</t>
+          <t>ISCO: 265</t>
         </is>
       </c>
       <c r="Z24" s="2" t="n"/>
@@ -1958,22 +1944,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dentist </t>
+          <t xml:space="preserve">dental assistant and therapist </t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry. </t>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
@@ -1990,7 +1976,7 @@
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -2005,16 +1991,16 @@
         </is>
       </c>
       <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="n"/>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2261</t>
+          <t>ISCO: 3251</t>
         </is>
       </c>
       <c r="Z25" s="2" t="n"/>
@@ -2022,17 +2008,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dietician and nutritionist </t>
+          <t xml:space="preserve">dentist </t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+          <t xml:space="preserve">A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry. </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2054,7 +2040,7 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2069,16 +2055,16 @@
         </is>
       </c>
       <c r="U26" s="2" t="n"/>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2265</t>
+          <t>ISCO: 2261</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -2086,22 +2072,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>discipline of current programme of study or training</t>
+          <t xml:space="preserve">dietician and nutritionist </t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>expertise discipline</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
@@ -2118,10 +2104,14 @@
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>psychology, medicine, hairdressing</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="n"/>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
@@ -2129,34 +2119,34 @@
         </is>
       </c>
       <c r="U27" s="2" t="n"/>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X27" s="2" t="n"/>
-      <c r="Y27" s="2" t="n"/>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2265</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>discipline of pre-existing knowledge or skill</t>
+          <t>discipline of current programme of study or training</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The expertise discipline in which the person source has acquired their pre-existing knowledge and skills. </t>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2174,15 +2164,11 @@
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+          <t>psychology, medicine, hairdressing</t>
         </is>
       </c>
       <c r="R28" s="2" t="n"/>
@@ -2195,10 +2181,14 @@
       <c r="U28" s="2" t="n"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="n"/>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X28" s="2" t="n"/>
       <c r="Y28" s="2" t="n"/>
       <c r="Z28" s="2" t="n"/>
@@ -2206,22 +2196,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>discipline of pre-existing knowledge or skill</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+          <t xml:space="preserve">The expertise discipline in which the person source has acquired their pre-existing knowledge and skills. </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>expertise discipline</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
@@ -2234,11 +2224,15 @@
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>PhD student</t>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
         </is>
       </c>
       <c r="R29" s="2" t="n"/>
@@ -2249,12 +2243,12 @@
         </is>
       </c>
       <c r="U29" s="2" t="n"/>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="n"/>
+      <c r="V29" s="2" t="n"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X29" s="2" t="n"/>
       <c r="Y29" s="2" t="n"/>
       <c r="Z29" s="2" t="n"/>
@@ -2262,22 +2256,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">early childhood educator </t>
+          <t>doctoral student role</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
@@ -2294,14 +2288,10 @@
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Early childhood educator, Pre-school teacher</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>PhD student</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
@@ -2309,39 +2299,35 @@
         </is>
       </c>
       <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X30" s="2" t="n"/>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2342</t>
-        </is>
-      </c>
+      <c r="Y30" s="2" t="n"/>
       <c r="Z30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">elementary occupation </t>
+          <t xml:space="preserve">early childhood educator </t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
@@ -2358,7 +2344,7 @@
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -2373,16 +2359,16 @@
         </is>
       </c>
       <c r="U31" s="2" t="n"/>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="n"/>
+      <c r="V31" s="2" t="n"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X31" s="2" t="n"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 9</t>
+          <t>ISCO: 2342</t>
         </is>
       </c>
       <c r="Z31" s="2" t="n"/>
@@ -2390,22 +2376,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>embedded in participants’ community</t>
+          <t xml:space="preserve">elementary occupation </t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
@@ -2420,8 +2406,16 @@
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
@@ -2429,30 +2423,34 @@
         </is>
       </c>
       <c r="U32" s="2" t="n"/>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="n"/>
+      <c r="V32" s="2" t="n"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X32" s="2" t="n"/>
-      <c r="Y32" s="2" t="n"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 9</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>employer</t>
+          <t>embedded in participants’ community</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2481,12 +2479,12 @@
         </is>
       </c>
       <c r="U33" s="2" t="n"/>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="n"/>
+      <c r="V33" s="2" t="n"/>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X33" s="2" t="n"/>
       <c r="Y33" s="2" t="n"/>
       <c r="Z33" s="2" t="n"/>
@@ -2494,22 +2492,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">environmental and occupational health and hygiene professional </t>
+          <t>employer</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
@@ -2524,16 +2522,8 @@
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
@@ -2541,41 +2531,35 @@
         </is>
       </c>
       <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="n"/>
+      <c r="V34" s="2" t="n"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X34" s="2" t="n"/>
-      <c r="Y34" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2263</t>
-        </is>
-      </c>
+      <c r="Y34" s="2" t="n"/>
       <c r="Z34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">environmental and occupational health inspector and associate </t>
+          <t xml:space="preserve">environmental and occupational health and hygiene professional </t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.
-</t>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
@@ -2592,7 +2576,7 @@
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -2607,16 +2591,16 @@
         </is>
       </c>
       <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="n"/>
+      <c r="V35" s="2" t="n"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X35" s="2" t="n"/>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3257</t>
+          <t>ISCO: 2263</t>
         </is>
       </c>
       <c r="Z35" s="2" t="n"/>
@@ -2624,22 +2608,24 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ethnic group membership of person source</t>
+          <t xml:space="preserve">environmental and occupational health inspector and associate </t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+          <t xml:space="preserve">A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.
+</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E36" s="2" t="n"/>
@@ -2656,10 +2642,14 @@
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="n"/>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
@@ -2667,35 +2657,39 @@
         </is>
       </c>
       <c r="U36" s="2" t="n"/>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="n"/>
+      <c r="V36" s="2" t="n"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X36" s="2" t="n"/>
-      <c r="Y36" s="2" t="n"/>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3257</t>
+        </is>
+      </c>
       <c r="Z36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>expertise discipline</t>
+          <t>ethnic group membership of person source</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E37" s="2" t="n"/>
@@ -2712,27 +2706,23 @@
       <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+          <t>black, white, Indian, Chinese, Somalian</t>
         </is>
       </c>
       <c r="R37" s="2" t="n"/>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
-        </is>
-      </c>
+      <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
       <c r="U37" s="2" t="n"/>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="n"/>
+      <c r="V37" s="2" t="n"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="n"/>
       <c r="Z37" s="2" t="n"/>
@@ -2740,22 +2730,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>expertise of person source</t>
+          <t>expertise discipline</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+          <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
@@ -2768,27 +2758,31 @@
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="n"/>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+        </is>
+      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
       <c r="U38" s="2" t="n"/>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="n"/>
+      <c r="V38" s="2" t="n"/>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X38" s="2" t="n"/>
       <c r="Y38" s="2" t="n"/>
       <c r="Z38" s="2" t="n"/>
@@ -2796,22 +2790,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="E39" s="2" t="n"/>
@@ -2824,7 +2818,11 @@
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="n"/>
@@ -2835,39 +2833,35 @@
         </is>
       </c>
       <c r="U39" s="2" t="n"/>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="n"/>
+      <c r="V39" s="2" t="n"/>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X39" s="2" t="n"/>
       <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010095</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>female gender</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E40" s="2" t="n"/>
@@ -2882,11 +2876,7 @@
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>female, woman</t>
-        </is>
-      </c>
+      <c r="Q40" s="2" t="n"/>
       <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="inlineStr">
@@ -2897,37 +2887,37 @@
       <c r="U40" s="2" t="n"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="n"/>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X40" s="2" t="n"/>
       <c r="Y40" s="2" t="n"/>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fitness and recreation instructor and programme leader </t>
+          <t>female gender</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+          <t>A gender identity as being female.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sport and fitness worker </t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="E41" s="2" t="n"/>
@@ -2944,14 +2934,10 @@
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>female, woman</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
@@ -2961,37 +2947,37 @@
       <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="n"/>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X41" s="2" t="n"/>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 3423</t>
-        </is>
-      </c>
+      <c r="Y41" s="2" t="n"/>
       <c r="Z41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t xml:space="preserve">fitness and recreation instructor and programme leader </t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t xml:space="preserve">sport and fitness worker </t>
         </is>
       </c>
       <c r="E42" s="2" t="n"/>
@@ -3006,8 +2992,16 @@
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="n"/>
-      <c r="Q42" s="2" t="n"/>
-      <c r="R42" s="2" t="n"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
@@ -3015,35 +3009,39 @@
         </is>
       </c>
       <c r="U42" s="2" t="n"/>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="n"/>
+      <c r="V42" s="2" t="n"/>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X42" s="2" t="n"/>
-      <c r="Y42" s="2" t="n"/>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3423</t>
+        </is>
+      </c>
       <c r="Z42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>self-identity</t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="E43" s="2" t="n"/>
@@ -3063,43 +3061,39 @@
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="n"/>
+      <c r="V43" s="2" t="n"/>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="n"/>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>gender of person source</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>self-identity</t>
         </is>
       </c>
       <c r="E44" s="2" t="n"/>
@@ -3114,25 +3108,25 @@
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
+      <c r="Q44" s="2" t="n"/>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="U44" s="2" t="n"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="n"/>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
@@ -3140,22 +3134,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">generalist medical practitioner </t>
+          <t>gender of person source</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities. </t>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical doctor </t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E45" s="2" t="n"/>
@@ -3172,14 +3166,10 @@
       <c r="P45" s="2" t="n"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>Primary care physician, family doctor, GP</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
@@ -3187,39 +3177,35 @@
         </is>
       </c>
       <c r="U45" s="2" t="n"/>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="n"/>
+      <c r="V45" s="2" t="n"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X45" s="2" t="n"/>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2211</t>
-        </is>
-      </c>
+      <c r="Y45" s="2" t="n"/>
       <c r="Z45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>graduate student role</t>
+          <t xml:space="preserve">generalist medical practitioner </t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities. </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t xml:space="preserve">medical doctor </t>
         </is>
       </c>
       <c r="E46" s="2" t="n"/>
@@ -3236,10 +3222,14 @@
       <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>graduate student</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="n"/>
+          <t>Primary care physician, family doctor, GP</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
@@ -3247,35 +3237,39 @@
         </is>
       </c>
       <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
+      <c r="V46" s="2" t="n"/>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="n"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2211</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>graduate student role</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E47" s="2" t="n"/>
@@ -3292,14 +3286,10 @@
       <c r="P47" s="2" t="n"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veterinary Technician </t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>graduate student</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
@@ -3307,39 +3297,35 @@
         </is>
       </c>
       <c r="U47" s="2" t="n"/>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="n"/>
+      <c r="V47" s="2" t="n"/>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X47" s="2" t="n"/>
-      <c r="Y47" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 32</t>
-        </is>
-      </c>
+      <c r="Y47" s="2" t="n"/>
       <c r="Z47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health care assistant </t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E48" s="2" t="n"/>
@@ -3356,7 +3342,7 @@
       <c r="P48" s="2" t="n"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
+          <t xml:space="preserve">Veterinary Technician </t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -3371,16 +3357,16 @@
         </is>
       </c>
       <c r="U48" s="2" t="n"/>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="n"/>
+      <c r="V48" s="2" t="n"/>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X48" s="2" t="n"/>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 5321</t>
+          <t>ISCO: 32</t>
         </is>
       </c>
       <c r="Z48" s="2" t="n"/>
@@ -3388,22 +3374,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">health care assistant </t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E49" s="2" t="n"/>
@@ -3420,7 +3406,7 @@
       <c r="P49" s="2" t="n"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -3435,16 +3421,16 @@
         </is>
       </c>
       <c r="U49" s="2" t="n"/>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="n"/>
+      <c r="V49" s="2" t="n"/>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X49" s="2" t="n"/>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 22</t>
+          <t>ISCO: 5321</t>
         </is>
       </c>
       <c r="Z49" s="2" t="n"/>
@@ -3452,22 +3438,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>health status of person source</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E50" s="2" t="n"/>
@@ -3484,10 +3470,14 @@
       <c r="P50" s="2" t="n"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="n"/>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
@@ -3495,35 +3485,39 @@
         </is>
       </c>
       <c r="U50" s="2" t="n"/>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="n"/>
+      <c r="V50" s="2" t="n"/>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X50" s="2" t="n"/>
-      <c r="Y50" s="2" t="n"/>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 22</t>
+        </is>
+      </c>
       <c r="Z50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>health status of person source</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. </t>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E51" s="2" t="n"/>
@@ -3540,7 +3534,7 @@
       <c r="P51" s="2" t="n"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
         </is>
       </c>
       <c r="R51" s="2" t="n"/>
@@ -3551,12 +3545,12 @@
         </is>
       </c>
       <c r="U51" s="2" t="n"/>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="n"/>
+      <c r="V51" s="2" t="n"/>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X51" s="2" t="n"/>
       <c r="Y51" s="2" t="n"/>
       <c r="Z51" s="2" t="n"/>
@@ -3564,22 +3558,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">home-based personal care worker </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+          <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. </t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E52" s="2" t="n"/>
@@ -3596,14 +3590,10 @@
       <c r="P52" s="2" t="n"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="inlineStr">
         <is>
@@ -3611,39 +3601,35 @@
         </is>
       </c>
       <c r="U52" s="2" t="n"/>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="n"/>
+      <c r="V52" s="2" t="n"/>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X52" s="2" t="n"/>
-      <c r="Y52" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 5322</t>
-        </is>
-      </c>
+      <c r="Y52" s="2" t="n"/>
       <c r="Z52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t xml:space="preserve">home-based personal care worker </t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
@@ -3658,8 +3644,16 @@
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="n"/>
-      <c r="Q53" s="2" t="n"/>
-      <c r="R53" s="2" t="n"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="2" t="inlineStr">
         <is>
@@ -3667,35 +3661,39 @@
         </is>
       </c>
       <c r="U53" s="2" t="n"/>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="n"/>
+      <c r="V53" s="2" t="n"/>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X53" s="2" t="n"/>
-      <c r="Y53" s="2" t="n"/>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 5322</t>
+        </is>
+      </c>
       <c r="Z53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">information and communications technician </t>
+          <t>informal education student role</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
@@ -3710,16 +3708,8 @@
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="n"/>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="inlineStr">
         <is>
@@ -3727,39 +3717,35 @@
         </is>
       </c>
       <c r="U54" s="2" t="n"/>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="n"/>
+      <c r="V54" s="2" t="n"/>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X54" s="2" t="n"/>
-      <c r="Y54" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 35</t>
-        </is>
-      </c>
+      <c r="Y54" s="2" t="n"/>
       <c r="Z54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010121</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>knowledge or skill</t>
+          <t xml:space="preserve">information and communications technician </t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention. </t>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>expertise of person source</t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E55" s="2" t="n"/>
@@ -3776,10 +3762,14 @@
       <c r="P55" s="2" t="n"/>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>trained (if unclear whether pre-existing or acquired)</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="n"/>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="n"/>
       <c r="T55" s="2" t="inlineStr">
         <is>
@@ -3787,35 +3777,39 @@
         </is>
       </c>
       <c r="U55" s="2" t="n"/>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W55" s="2" t="n"/>
+      <c r="V55" s="2" t="n"/>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X55" s="2" t="n"/>
-      <c r="Y55" s="2" t="n"/>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 35</t>
+        </is>
+      </c>
       <c r="Z55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>BCIO:010121</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>language proficiency of person source</t>
+          <t>knowledge or skill</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+          <t xml:space="preserve">An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention. </t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="E56" s="2" t="n"/>
@@ -3832,7 +3826,7 @@
       <c r="P56" s="2" t="n"/>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>fluent, native</t>
+          <t>trained (if unclear whether pre-existing or acquired)</t>
         </is>
       </c>
       <c r="R56" s="2" t="n"/>
@@ -3843,12 +3837,12 @@
         </is>
       </c>
       <c r="U56" s="2" t="n"/>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="n"/>
+      <c r="V56" s="2" t="n"/>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X56" s="2" t="n"/>
       <c r="Y56" s="2" t="n"/>
       <c r="Z56" s="2" t="n"/>
@@ -3856,22 +3850,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal and related associate professional  </t>
+          <t>language proficiency of person source</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients. </t>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E57" s="2" t="n"/>
@@ -3888,14 +3882,10 @@
       <c r="P57" s="2" t="n"/>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>fluent, native</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="2" t="inlineStr">
         <is>
@@ -3903,39 +3893,35 @@
         </is>
       </c>
       <c r="U57" s="2" t="n"/>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W57" s="2" t="n"/>
+      <c r="V57" s="2" t="n"/>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X57" s="2" t="n"/>
-      <c r="Y57" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 3411</t>
-        </is>
-      </c>
+      <c r="Y57" s="2" t="n"/>
       <c r="Z57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal professional </t>
+          <t xml:space="preserve">legal and related associate professional  </t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+          <t xml:space="preserve">A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients. </t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E58" s="2" t="n"/>
@@ -3952,7 +3938,7 @@
       <c r="P58" s="2" t="n"/>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Lawyer, Judge, Coroner</t>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -3967,16 +3953,16 @@
         </is>
       </c>
       <c r="U58" s="2" t="n"/>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W58" s="2" t="n"/>
+      <c r="V58" s="2" t="n"/>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X58" s="2" t="n"/>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 261</t>
+          <t>ISCO: 3411</t>
         </is>
       </c>
       <c r="Z58" s="2" t="n"/>
@@ -3984,22 +3970,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">legal professional </t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">legal, social and cultural professional </t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies. </t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>professional</t>
         </is>
       </c>
       <c r="E59" s="2" t="n"/>
@@ -4014,7 +4000,11 @@
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="n"/>
-      <c r="Q59" s="2" t="n"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
+        </is>
+      </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -4027,16 +4017,16 @@
         </is>
       </c>
       <c r="U59" s="2" t="n"/>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W59" s="2" t="n"/>
+      <c r="V59" s="2" t="n"/>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X59" s="2" t="n"/>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 26</t>
+          <t>ISCO: 261</t>
         </is>
       </c>
       <c r="Z59" s="2" t="n"/>
@@ -4044,22 +4034,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">librarian, archivist and curator </t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments. </t>
+          <t xml:space="preserve">A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies. </t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E60" s="2" t="n"/>
@@ -4074,11 +4064,7 @@
       <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="n"/>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>Librarian, Archivist,  Curator</t>
-        </is>
-      </c>
+      <c r="Q60" s="2" t="n"/>
       <c r="R60" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -4091,16 +4077,16 @@
         </is>
       </c>
       <c r="U60" s="2" t="n"/>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W60" s="2" t="n"/>
+      <c r="V60" s="2" t="n"/>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X60" s="2" t="n"/>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 262</t>
+          <t>ISCO: 26</t>
         </is>
       </c>
       <c r="Z60" s="2" t="n"/>
@@ -4108,17 +4094,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>linguist</t>
+          <t xml:space="preserve">librarian, archivist and curator </t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+          <t xml:space="preserve">A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments. </t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4140,10 +4126,14 @@
       <c r="P61" s="2" t="n"/>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="n"/>
+          <t>Librarian, Archivist,  Curator</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="2" t="inlineStr">
         <is>
@@ -4151,35 +4141,39 @@
         </is>
       </c>
       <c r="U61" s="2" t="n"/>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W61" s="2" t="n"/>
+      <c r="V61" s="2" t="n"/>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X61" s="2" t="n"/>
-      <c r="Y61" s="2" t="n"/>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 262</t>
+        </is>
+      </c>
       <c r="Z61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>male gender</t>
+          <t>linguist</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -4196,7 +4190,7 @@
       <c r="P62" s="2" t="n"/>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>male, man</t>
+          <t>Interpretator; other linguist</t>
         </is>
       </c>
       <c r="R62" s="2" t="n"/>
@@ -4207,39 +4201,35 @@
         </is>
       </c>
       <c r="U62" s="2" t="n"/>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W62" s="2" t="n"/>
+      <c r="V62" s="2" t="n"/>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X62" s="2" t="n"/>
       <c r="Y62" s="2" t="n"/>
-      <c r="Z62" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>male gender</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+          <t>A gender identity as being male.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -4256,14 +4246,10 @@
       <c r="P63" s="2" t="n"/>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>male, man</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="2" t="inlineStr">
         <is>
@@ -4273,37 +4259,37 @@
       <c r="U63" s="2" t="n"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W63" s="2" t="n"/>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X63" s="2" t="n"/>
-      <c r="Y63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISCO: 1 </t>
-        </is>
-      </c>
+      <c r="Y63" s="2" t="n"/>
       <c r="Z63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>masters student role</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -4320,10 +4306,14 @@
       <c r="P64" s="2" t="n"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>MSc student, Masters student</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="n"/>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="inlineStr">
         <is>
@@ -4331,35 +4321,39 @@
         </is>
       </c>
       <c r="U64" s="2" t="n"/>
-      <c r="V64" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W64" s="2" t="n"/>
+      <c r="V64" s="2" t="n"/>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X64" s="2" t="n"/>
-      <c r="Y64" s="2" t="n"/>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISCO: 1 </t>
+        </is>
+      </c>
       <c r="Z64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical and pharmaceutical technician </t>
+          <t>masters student role</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -4376,14 +4370,10 @@
       <c r="P65" s="2" t="n"/>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>MSc student, Masters student</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="n"/>
       <c r="S65" s="2" t="n"/>
       <c r="T65" s="2" t="inlineStr">
         <is>
@@ -4391,34 +4381,30 @@
         </is>
       </c>
       <c r="U65" s="2" t="n"/>
-      <c r="V65" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W65" s="2" t="n"/>
+      <c r="V65" s="2" t="n"/>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X65" s="2" t="n"/>
-      <c r="Y65" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 321</t>
-        </is>
-      </c>
+      <c r="Y65" s="2" t="n"/>
       <c r="Z65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical assistant </t>
+          <t xml:space="preserve">medical and pharmaceutical technician </t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional. </t>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4440,7 +4426,7 @@
       <c r="P66" s="2" t="n"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -4455,16 +4441,16 @@
         </is>
       </c>
       <c r="U66" s="2" t="n"/>
-      <c r="V66" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W66" s="2" t="n"/>
+      <c r="V66" s="2" t="n"/>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X66" s="2" t="n"/>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3256</t>
+          <t>ISCO: 321</t>
         </is>
       </c>
       <c r="Z66" s="2" t="n"/>
@@ -4472,22 +4458,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical doctor </t>
+          <t xml:space="preserve">medical assistant </t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+          <t xml:space="preserve">A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional. </t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E67" s="2" t="n"/>
@@ -4504,7 +4490,7 @@
       <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
@@ -4519,16 +4505,16 @@
         </is>
       </c>
       <c r="U67" s="2" t="n"/>
-      <c r="V67" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W67" s="2" t="n"/>
+      <c r="V67" s="2" t="n"/>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X67" s="2" t="n"/>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 221</t>
+          <t>ISCO: 3256</t>
         </is>
       </c>
       <c r="Z67" s="2" t="n"/>
@@ -4536,22 +4522,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">midwifery associate professional </t>
+          <t xml:space="preserve">medical doctor </t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery associate professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E68" s="2" t="n"/>
@@ -4568,7 +4554,7 @@
       <c r="P68" s="2" t="n"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Assistant midwife, Traditional midwife</t>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -4583,16 +4569,16 @@
         </is>
       </c>
       <c r="U68" s="2" t="n"/>
-      <c r="V68" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W68" s="2" t="n"/>
+      <c r="V68" s="2" t="n"/>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X68" s="2" t="n"/>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3222</t>
+          <t>ISCO: 221</t>
         </is>
       </c>
       <c r="Z68" s="2" t="n"/>
@@ -4600,22 +4586,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">midwifery professional </t>
+          <t xml:space="preserve">midwifery associate professional </t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">nursing and midwifery associate professional </t>
         </is>
       </c>
       <c r="E69" s="2" t="n"/>
@@ -4632,7 +4618,7 @@
       <c r="P69" s="2" t="n"/>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -4647,16 +4633,16 @@
         </is>
       </c>
       <c r="U69" s="2" t="n"/>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W69" s="2" t="n"/>
+      <c r="V69" s="2" t="n"/>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X69" s="2" t="n"/>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2222</t>
+          <t>ISCO: 3222</t>
         </is>
       </c>
       <c r="Z69" s="2" t="n"/>
@@ -4664,22 +4650,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010131</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>monetary payment</t>
+          <t xml:space="preserve">midwifery professional </t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>payment of person source</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E70" s="2" t="n"/>
@@ -4696,10 +4682,14 @@
       <c r="P70" s="2" t="n"/>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>paid in cash, vouchers</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="n"/>
+          <t>Midwife</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S70" s="2" t="n"/>
       <c r="T70" s="2" t="inlineStr">
         <is>
@@ -4707,35 +4697,39 @@
         </is>
       </c>
       <c r="U70" s="2" t="n"/>
-      <c r="V70" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W70" s="2" t="n"/>
+      <c r="V70" s="2" t="n"/>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X70" s="2" t="n"/>
-      <c r="Y70" s="2" t="n"/>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2222</t>
+        </is>
+      </c>
       <c r="Z70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010131</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">music teacher </t>
+          <t>monetary payment</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="E71" s="2" t="n"/>
@@ -4752,14 +4746,10 @@
       <c r="P71" s="2" t="n"/>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>paid in cash, vouchers</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="n"/>
       <c r="S71" s="2" t="n"/>
       <c r="T71" s="2" t="inlineStr">
         <is>
@@ -4767,39 +4757,35 @@
         </is>
       </c>
       <c r="U71" s="2" t="n"/>
-      <c r="V71" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W71" s="2" t="n"/>
+      <c r="V71" s="2" t="n"/>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X71" s="2" t="n"/>
-      <c r="Y71" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2354</t>
-        </is>
-      </c>
+      <c r="Y71" s="2" t="n"/>
       <c r="Z71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>non-monetary payment</t>
+          <t xml:space="preserve">music teacher </t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>payment of person source</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -4816,10 +4802,14 @@
       <c r="P72" s="2" t="n"/>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>course credit</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="n"/>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="inlineStr">
         <is>
@@ -4827,35 +4817,39 @@
         </is>
       </c>
       <c r="U72" s="2" t="n"/>
-      <c r="V72" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W72" s="2" t="n"/>
+      <c r="V72" s="2" t="n"/>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X72" s="2" t="n"/>
-      <c r="Y72" s="2" t="n"/>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2354</t>
+        </is>
+      </c>
       <c r="Z72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>number of people delivering intervention to each participant</t>
+          <t>non-monetary payment</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -4867,14 +4861,14 @@
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="N73" s="2" t="n"/>
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="n"/>
-      <c r="Q73" s="2" t="n"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>course credit</t>
+        </is>
+      </c>
       <c r="R73" s="2" t="n"/>
       <c r="S73" s="2" t="n"/>
       <c r="T73" s="2" t="inlineStr">
@@ -4883,12 +4877,12 @@
         </is>
       </c>
       <c r="U73" s="2" t="n"/>
-      <c r="V73" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W73" s="2" t="n"/>
+      <c r="V73" s="2" t="n"/>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X73" s="2" t="n"/>
       <c r="Y73" s="2" t="n"/>
       <c r="Z73" s="2" t="n"/>
@@ -4896,22 +4890,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery associate professional </t>
+          <t>number of people delivering intervention to each participant</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -4923,19 +4917,15 @@
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
-      <c r="N74" s="2" t="n"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="n"/>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
-        </is>
-      </c>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q74" s="2" t="n"/>
+      <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="inlineStr">
         <is>
@@ -4943,39 +4933,35 @@
         </is>
       </c>
       <c r="U74" s="2" t="n"/>
-      <c r="V74" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W74" s="2" t="n"/>
+      <c r="V74" s="2" t="n"/>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X74" s="2" t="n"/>
-      <c r="Y74" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 322</t>
-        </is>
-      </c>
+      <c r="Y74" s="2" t="n"/>
       <c r="Z74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery professional </t>
+          <t xml:space="preserve">nursing and midwifery associate professional </t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>health professional</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -4990,7 +4976,11 @@
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="n"/>
-      <c r="Q75" s="2" t="n"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
+        </is>
+      </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -5003,16 +4993,16 @@
         </is>
       </c>
       <c r="U75" s="2" t="n"/>
-      <c r="V75" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W75" s="2" t="n"/>
+      <c r="V75" s="2" t="n"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X75" s="2" t="n"/>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 222</t>
+          <t>ISCO: 322</t>
         </is>
       </c>
       <c r="Z75" s="2" t="n"/>
@@ -5020,22 +5010,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing associate professional </t>
+          <t xml:space="preserve">nursing and midwifery professional </t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery associate professional </t>
+          <t>health professional</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -5050,11 +5040,7 @@
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="n"/>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
-        </is>
-      </c>
+      <c r="Q76" s="2" t="n"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -5067,16 +5053,16 @@
         </is>
       </c>
       <c r="U76" s="2" t="n"/>
-      <c r="V76" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W76" s="2" t="n"/>
+      <c r="V76" s="2" t="n"/>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X76" s="2" t="n"/>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3221</t>
+          <t>ISCO: 222</t>
         </is>
       </c>
       <c r="Z76" s="2" t="n"/>
@@ -5084,22 +5070,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing professional </t>
+          <t xml:space="preserve">nursing associate professional </t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health. </t>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">nursing and midwifery associate professional </t>
         </is>
       </c>
       <c r="E77" s="2" t="n"/>
@@ -5116,7 +5102,7 @@
       <c r="P77" s="2" t="n"/>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
@@ -5131,16 +5117,16 @@
         </is>
       </c>
       <c r="U77" s="2" t="n"/>
-      <c r="V77" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W77" s="2" t="n"/>
+      <c r="V77" s="2" t="n"/>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X77" s="2" t="n"/>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2221</t>
+          <t>ISCO: 3221</t>
         </is>
       </c>
       <c r="Z77" s="2" t="n"/>
@@ -5148,22 +5134,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">nursing professional </t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+          <t xml:space="preserve">A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health. </t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>personal role of source</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E78" s="2" t="n"/>
@@ -5180,10 +5166,14 @@
       <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Interventionist, facilitator, study staff</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="n"/>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S78" s="2" t="n"/>
       <c r="T78" s="2" t="inlineStr">
         <is>
@@ -5191,35 +5181,39 @@
         </is>
       </c>
       <c r="U78" s="2" t="n"/>
-      <c r="V78" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W78" s="2" t="n"/>
+      <c r="V78" s="2" t="n"/>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X78" s="2" t="n"/>
-      <c r="Y78" s="2" t="n"/>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2221</t>
+        </is>
+      </c>
       <c r="Z78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">optometrist and ophthalmic optician </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system. </t>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>personal role of source</t>
         </is>
       </c>
       <c r="E79" s="2" t="n"/>
@@ -5236,14 +5230,10 @@
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
-        </is>
-      </c>
-      <c r="R79" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>Interventionist, facilitator, study staff</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="n"/>
       <c r="S79" s="2" t="n"/>
       <c r="T79" s="2" t="inlineStr">
         <is>
@@ -5251,39 +5241,35 @@
         </is>
       </c>
       <c r="U79" s="2" t="n"/>
-      <c r="V79" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W79" s="2" t="n"/>
+      <c r="V79" s="2" t="n"/>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X79" s="2" t="n"/>
-      <c r="Y79" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2267</t>
-        </is>
-      </c>
+      <c r="Y79" s="2" t="n"/>
       <c r="Z79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>organisation source</t>
+          <t xml:space="preserve">optometrist and ophthalmic optician </t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+          <t xml:space="preserve">A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system. </t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">organization </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E80" s="2" t="n"/>
@@ -5297,13 +5283,17 @@
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>(organisation and 'has characteristic' some 'organisational source role')</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="n"/>
-      <c r="R80" s="2" t="n"/>
+      <c r="P80" s="2" t="n"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S80" s="2" t="n"/>
       <c r="T80" s="2" t="inlineStr">
         <is>
@@ -5311,39 +5301,39 @@
         </is>
       </c>
       <c r="U80" s="2" t="n"/>
-      <c r="V80" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W80" s="2" t="n"/>
+      <c r="V80" s="2" t="n"/>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X80" s="2" t="n"/>
-      <c r="Y80" s="2" t="n"/>
-      <c r="Z80" s="2" t="inlineStr">
-        <is>
-          <t>BG; PS</t>
-        </is>
-      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2267</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>organisational source role</t>
+          <t>organisation source</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>behaviour change intervention source</t>
+          <t xml:space="preserve">organization </t>
         </is>
       </c>
       <c r="E81" s="2" t="n"/>
@@ -5357,7 +5347,11 @@
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="n"/>
       <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="n"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>(organisation and 'has characteristic' some 'organisational source role')</t>
+        </is>
+      </c>
       <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="n"/>
       <c r="S81" s="2" t="n"/>
@@ -5369,131 +5363,131 @@
       <c r="U81" s="2" t="n"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W81" s="2" t="n"/>
+          <t>BG; PS</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X81" s="2" t="n"/>
       <c r="Y81" s="2" t="n"/>
       <c r="Z81" s="2" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010138</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>A BCI source role that is borne by an organisation.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n"/>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="n"/>
+      <c r="P82" s="2" t="n"/>
+      <c r="Q82" s="2" t="n"/>
+      <c r="R82" s="2" t="n"/>
+      <c r="S82" s="2" t="n"/>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="n"/>
+      <c r="V82" s="2" t="n"/>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="n"/>
+      <c r="Y82" s="2" t="n"/>
+      <c r="Z82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>OBI:0000245</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t xml:space="preserve">organization </t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t xml:space="preserve">An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members. </t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>organisational source role</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>RW</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010113</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>other gender</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female. </t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>gender of person source</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="n"/>
-      <c r="F83" s="2" t="n"/>
-      <c r="G83" s="2" t="n"/>
-      <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="n"/>
-      <c r="L83" s="2" t="n"/>
-      <c r="M83" s="2" t="n"/>
-      <c r="N83" s="2" t="n"/>
-      <c r="O83" s="2" t="n"/>
-      <c r="P83" s="2" t="n"/>
-      <c r="Q83" s="2" t="inlineStr">
-        <is>
-          <t>non-binary, transexual</t>
-        </is>
-      </c>
-      <c r="R83" s="2" t="n"/>
-      <c r="S83" s="2" t="n"/>
-      <c r="T83" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U83" s="2" t="n"/>
-      <c r="V83" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W83" s="2" t="n"/>
-      <c r="X83" s="2" t="n"/>
-      <c r="Y83" s="2" t="n"/>
-      <c r="Z83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">paramedical practitioner </t>
+          <t>other gender</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+          <t xml:space="preserve">A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female. </t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>gender of person source</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -5510,14 +5504,10 @@
       <c r="P84" s="2" t="n"/>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
-        </is>
-      </c>
-      <c r="R84" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>non-binary, transexual</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="n"/>
       <c r="S84" s="2" t="n"/>
       <c r="T84" s="2" t="inlineStr">
         <is>
@@ -5525,39 +5515,35 @@
         </is>
       </c>
       <c r="U84" s="2" t="n"/>
-      <c r="V84" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W84" s="2" t="n"/>
+      <c r="V84" s="2" t="n"/>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X84" s="2" t="n"/>
-      <c r="Y84" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 224</t>
-        </is>
-      </c>
+      <c r="Y84" s="2" t="n"/>
       <c r="Z84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>parent or guardian</t>
+          <t xml:space="preserve">paramedical practitioner </t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -5574,10 +5560,14 @@
       <c r="P85" s="2" t="n"/>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
-        </is>
-      </c>
-      <c r="R85" s="2" t="n"/>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S85" s="2" t="n"/>
       <c r="T85" s="2" t="inlineStr">
         <is>
@@ -5585,43 +5575,43 @@
         </is>
       </c>
       <c r="U85" s="2" t="n"/>
-      <c r="V85" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W85" s="2" t="n"/>
+      <c r="V85" s="2" t="n"/>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X85" s="2" t="n"/>
-      <c r="Y85" s="2" t="n"/>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 224</t>
+        </is>
+      </c>
       <c r="Z85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>payment of person source</t>
+          <t>parent or guardian</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
@@ -5632,7 +5622,11 @@
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="2" t="n"/>
       <c r="P86" s="2" t="n"/>
-      <c r="Q86" s="2" t="n"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>mother, father, step-mother, step-father, guardian</t>
+        </is>
+      </c>
       <c r="R86" s="2" t="n"/>
       <c r="S86" s="2" t="n"/>
       <c r="T86" s="2" t="inlineStr">
@@ -5641,12 +5635,12 @@
         </is>
       </c>
       <c r="U86" s="2" t="n"/>
-      <c r="V86" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W86" s="2" t="n"/>
+      <c r="V86" s="2" t="n"/>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X86" s="2" t="n"/>
       <c r="Y86" s="2" t="n"/>
       <c r="Z86" s="2" t="n"/>
@@ -5654,26 +5648,30 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010130</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>peer</t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc. </t>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
@@ -5693,132 +5691,124 @@
         </is>
       </c>
       <c r="U87" s="2" t="n"/>
-      <c r="V87" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W87" s="2" t="n"/>
+      <c r="V87" s="2" t="n"/>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X87" s="2" t="n"/>
       <c r="Y87" s="2" t="n"/>
       <c r="Z87" s="2" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010104</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>peer</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc. </t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="n"/>
+      <c r="P88" s="2" t="n"/>
+      <c r="Q88" s="2" t="n"/>
+      <c r="R88" s="2" t="n"/>
+      <c r="S88" s="2" t="n"/>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="n"/>
+      <c r="V88" s="2" t="n"/>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="n"/>
+      <c r="Y88" s="2" t="n"/>
+      <c r="Z88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>MF:0000016</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t xml:space="preserve">An extended organism that is a member of the species Homo sapiens. </t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>extended organism</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
         <is>
           <t>External</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010002</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="n"/>
-      <c r="L89" s="2" t="n"/>
-      <c r="M89" s="2" t="n"/>
-      <c r="N89" s="2" t="n"/>
-      <c r="O89" s="2" t="n"/>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>(person and 'has characteristic' some 'person source role')</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="n"/>
-      <c r="R89" s="2" t="n"/>
-      <c r="S89" s="2" t="n"/>
-      <c r="T89" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U89" s="2" t="n"/>
-      <c r="V89" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W89" s="2" t="n"/>
-      <c r="X89" s="2" t="n"/>
-      <c r="Y89" s="2" t="n"/>
-      <c r="Z89" s="2" t="inlineStr">
-        <is>
-          <t>BG</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>person source role</t>
+          <t>person source</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>behaviour change intervention source</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E90" s="2" t="n"/>
@@ -5832,7 +5822,11 @@
       <c r="M90" s="2" t="n"/>
       <c r="N90" s="2" t="n"/>
       <c r="O90" s="2" t="n"/>
-      <c r="P90" s="2" t="n"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>(person and 'has characteristic' some 'person source role')</t>
+        </is>
+      </c>
       <c r="Q90" s="2" t="n"/>
       <c r="R90" s="2" t="n"/>
       <c r="S90" s="2" t="n"/>
@@ -5844,10 +5838,14 @@
       <c r="U90" s="2" t="n"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W90" s="2" t="n"/>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X90" s="2" t="n"/>
       <c r="Y90" s="2" t="n"/>
       <c r="Z90" s="2" t="n"/>
@@ -5855,22 +5853,22 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t>person source role</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t>behaviour change intervention source</t>
         </is>
       </c>
       <c r="E91" s="2" t="n"/>
@@ -5885,16 +5883,8 @@
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="2" t="n"/>
       <c r="P91" s="2" t="n"/>
-      <c r="Q91" s="2" t="inlineStr">
-        <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
-      <c r="R91" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q91" s="2" t="n"/>
+      <c r="R91" s="2" t="n"/>
       <c r="S91" s="2" t="n"/>
       <c r="T91" s="2" t="inlineStr">
         <is>
@@ -5902,39 +5892,35 @@
         </is>
       </c>
       <c r="U91" s="2" t="n"/>
-      <c r="V91" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W91" s="2" t="n"/>
+      <c r="V91" s="2" t="n"/>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X91" s="2" t="n"/>
-      <c r="Y91" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 53</t>
-        </is>
-      </c>
+      <c r="Y91" s="2" t="n"/>
       <c r="Z91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>personal role of source</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A role that inheres in a person source. </t>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
@@ -5949,8 +5935,16 @@
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="2" t="n"/>
       <c r="P92" s="2" t="n"/>
-      <c r="Q92" s="2" t="n"/>
-      <c r="R92" s="2" t="n"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>Personal carer</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S92" s="2" t="n"/>
       <c r="T92" s="2" t="inlineStr">
         <is>
@@ -5958,35 +5952,39 @@
         </is>
       </c>
       <c r="U92" s="2" t="n"/>
-      <c r="V92" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W92" s="2" t="n"/>
+      <c r="V92" s="2" t="n"/>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X92" s="2" t="n"/>
-      <c r="Y92" s="2" t="n"/>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 53</t>
+        </is>
+      </c>
       <c r="Z92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal services worker </t>
+          <t>personal role of source</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+          <t xml:space="preserve">A role that inheres in a person source. </t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t>role</t>
         </is>
       </c>
       <c r="E93" s="2" t="n"/>
@@ -6001,16 +5999,8 @@
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="2" t="n"/>
       <c r="P93" s="2" t="n"/>
-      <c r="Q93" s="2" t="inlineStr">
-        <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
-      <c r="R93" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q93" s="2" t="n"/>
+      <c r="R93" s="2" t="n"/>
       <c r="S93" s="2" t="n"/>
       <c r="T93" s="2" t="inlineStr">
         <is>
@@ -6018,39 +6008,35 @@
         </is>
       </c>
       <c r="U93" s="2" t="n"/>
-      <c r="V93" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W93" s="2" t="n"/>
+      <c r="V93" s="2" t="n"/>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X93" s="2" t="n"/>
-      <c r="Y93" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 51</t>
-        </is>
-      </c>
+      <c r="Y93" s="2" t="n"/>
       <c r="Z93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>pharmacist</t>
+          <t xml:space="preserve">personal services worker </t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
@@ -6067,7 +6053,7 @@
       <c r="P94" s="2" t="n"/>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr">
@@ -6082,16 +6068,16 @@
         </is>
       </c>
       <c r="U94" s="2" t="n"/>
-      <c r="V94" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W94" s="2" t="n"/>
+      <c r="V94" s="2" t="n"/>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X94" s="2" t="n"/>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2262</t>
+          <t>ISCO: 51</t>
         </is>
       </c>
       <c r="Z94" s="2" t="n"/>
@@ -6099,17 +6085,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t>pharmacist</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -6131,7 +6117,7 @@
       <c r="P95" s="2" t="n"/>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
         </is>
       </c>
       <c r="R95" s="2" t="inlineStr">
@@ -6146,16 +6132,16 @@
         </is>
       </c>
       <c r="U95" s="2" t="n"/>
-      <c r="V95" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W95" s="2" t="n"/>
+      <c r="V95" s="2" t="n"/>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X95" s="2" t="n"/>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2264</t>
+          <t>ISCO: 2262</t>
         </is>
       </c>
       <c r="Z95" s="2" t="n"/>
@@ -6163,22 +6149,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">physiotherapy technician and assistant </t>
+          <t>physiotherapist</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
@@ -6195,7 +6181,7 @@
       <c r="P96" s="2" t="n"/>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
@@ -6210,16 +6196,16 @@
         </is>
       </c>
       <c r="U96" s="2" t="n"/>
-      <c r="V96" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W96" s="2" t="n"/>
+      <c r="V96" s="2" t="n"/>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X96" s="2" t="n"/>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3255</t>
+          <t>ISCO: 2264</t>
         </is>
       </c>
       <c r="Z96" s="2" t="n"/>
@@ -6227,22 +6213,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">plant and machine operator </t>
+          <t xml:space="preserve">physiotherapy technician and assistant </t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment. </t>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E97" s="2" t="n"/>
@@ -6259,7 +6245,7 @@
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
@@ -6274,16 +6260,16 @@
         </is>
       </c>
       <c r="U97" s="2" t="n"/>
-      <c r="V97" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W97" s="2" t="n"/>
+      <c r="V97" s="2" t="n"/>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X97" s="2" t="n"/>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 8</t>
+          <t>ISCO: 3255</t>
         </is>
       </c>
       <c r="Z97" s="2" t="n"/>
@@ -6291,22 +6277,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>pre-existing knowledge or skill</t>
+          <t xml:space="preserve">plant and machine operator </t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+          <t xml:space="preserve">An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment. </t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>knowledge or skill</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E98" s="2" t="n"/>
@@ -6323,10 +6309,14 @@
       <c r="P98" s="2" t="n"/>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
-        </is>
-      </c>
-      <c r="R98" s="2" t="n"/>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S98" s="2" t="n"/>
       <c r="T98" s="2" t="inlineStr">
         <is>
@@ -6334,35 +6324,39 @@
         </is>
       </c>
       <c r="U98" s="2" t="n"/>
-      <c r="V98" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W98" s="2" t="n"/>
+      <c r="V98" s="2" t="n"/>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X98" s="2" t="n"/>
-      <c r="Y98" s="2" t="n"/>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 8</t>
+        </is>
+      </c>
       <c r="Z98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary school teacher </t>
+          <t>pre-existing knowledge or skill</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>knowledge or skill</t>
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
@@ -6377,12 +6371,12 @@
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="2" t="n"/>
       <c r="P99" s="2" t="n"/>
-      <c r="Q99" s="2" t="n"/>
-      <c r="R99" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="n"/>
       <c r="S99" s="2" t="n"/>
       <c r="T99" s="2" t="inlineStr">
         <is>
@@ -6390,39 +6384,35 @@
         </is>
       </c>
       <c r="U99" s="2" t="n"/>
-      <c r="V99" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W99" s="2" t="n"/>
+      <c r="V99" s="2" t="n"/>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X99" s="2" t="n"/>
-      <c r="Y99" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2341</t>
-        </is>
-      </c>
+      <c r="Y99" s="2" t="n"/>
       <c r="Z99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t xml:space="preserve">primary school teacher </t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E100" s="2" t="n"/>
@@ -6450,16 +6440,16 @@
         </is>
       </c>
       <c r="U100" s="2" t="n"/>
-      <c r="V100" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W100" s="2" t="n"/>
+      <c r="V100" s="2" t="n"/>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X100" s="2" t="n"/>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2</t>
+          <t>ISCO: 2341</t>
         </is>
       </c>
       <c r="Z100" s="2" t="n"/>
@@ -6467,22 +6457,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">protective services worker </t>
+          <t>professional</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E101" s="2" t="n"/>
@@ -6497,11 +6487,7 @@
       <c r="N101" s="2" t="n"/>
       <c r="O101" s="2" t="n"/>
       <c r="P101" s="2" t="n"/>
-      <c r="Q101" s="2" t="inlineStr">
-        <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
+      <c r="Q101" s="2" t="n"/>
       <c r="R101" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -6514,16 +6500,16 @@
         </is>
       </c>
       <c r="U101" s="2" t="n"/>
-      <c r="V101" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W101" s="2" t="n"/>
+      <c r="V101" s="2" t="n"/>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X101" s="2" t="n"/>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 54</t>
+          <t>ISCO: 2</t>
         </is>
       </c>
       <c r="Z101" s="2" t="n"/>
@@ -6531,22 +6517,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>psychological influence on intervention delivery of person source</t>
+          <t xml:space="preserve">protective services worker </t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E102" s="2" t="n"/>
@@ -6561,8 +6547,16 @@
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="2" t="n"/>
       <c r="P102" s="2" t="n"/>
-      <c r="Q102" s="2" t="n"/>
-      <c r="R102" s="2" t="n"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S102" s="2" t="n"/>
       <c r="T102" s="2" t="inlineStr">
         <is>
@@ -6570,35 +6564,39 @@
         </is>
       </c>
       <c r="U102" s="2" t="n"/>
-      <c r="V102" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W102" s="2" t="n"/>
+      <c r="V102" s="2" t="n"/>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X102" s="2" t="n"/>
-      <c r="Y102" s="2" t="n"/>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 54</t>
+        </is>
+      </c>
       <c r="Z102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>psychologist</t>
+          <t>psychological influence on intervention delivery of person source</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social professional </t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E103" s="2" t="n"/>
@@ -6613,16 +6611,8 @@
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="2" t="n"/>
       <c r="P103" s="2" t="n"/>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
-        </is>
-      </c>
-      <c r="R103" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q103" s="2" t="n"/>
+      <c r="R103" s="2" t="n"/>
       <c r="S103" s="2" t="n"/>
       <c r="T103" s="2" t="inlineStr">
         <is>
@@ -6630,39 +6620,35 @@
         </is>
       </c>
       <c r="U103" s="2" t="n"/>
-      <c r="V103" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W103" s="2" t="n"/>
+      <c r="V103" s="2" t="n"/>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X103" s="2" t="n"/>
-      <c r="Y103" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2634</t>
-        </is>
-      </c>
+      <c r="Y103" s="2" t="n"/>
       <c r="Z103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>psychologist</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>personal role of source</t>
+          <t xml:space="preserve">social professional </t>
         </is>
       </c>
       <c r="E104" s="2" t="n"/>
@@ -6677,8 +6663,16 @@
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="2" t="n"/>
       <c r="P104" s="2" t="n"/>
-      <c r="Q104" s="2" t="n"/>
-      <c r="R104" s="2" t="n"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S104" s="2" t="n"/>
       <c r="T104" s="2" t="inlineStr">
         <is>
@@ -6686,35 +6680,39 @@
         </is>
       </c>
       <c r="U104" s="2" t="n"/>
-      <c r="V104" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W104" s="2" t="n"/>
+      <c r="V104" s="2" t="n"/>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X104" s="2" t="n"/>
-      <c r="Y104" s="2" t="n"/>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2634</t>
+        </is>
+      </c>
       <c r="Z104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">religious associate professional </t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>personal role of source</t>
         </is>
       </c>
       <c r="E105" s="2" t="n"/>
@@ -6729,16 +6727,8 @@
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="2" t="n"/>
       <c r="P105" s="2" t="n"/>
-      <c r="Q105" s="2" t="inlineStr">
-        <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
-        </is>
-      </c>
-      <c r="R105" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q105" s="2" t="n"/>
+      <c r="R105" s="2" t="n"/>
       <c r="S105" s="2" t="n"/>
       <c r="T105" s="2" t="inlineStr">
         <is>
@@ -6746,39 +6736,35 @@
         </is>
       </c>
       <c r="U105" s="2" t="n"/>
-      <c r="V105" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W105" s="2" t="n"/>
+      <c r="V105" s="2" t="n"/>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X105" s="2" t="n"/>
-      <c r="Y105" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 3413</t>
-        </is>
-      </c>
+      <c r="Y105" s="2" t="n"/>
       <c r="Z105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>religious group membership of person source</t>
+          <t xml:space="preserve">religious associate professional </t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion. </t>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E106" s="2" t="n"/>
@@ -6795,10 +6781,14 @@
       <c r="P106" s="2" t="n"/>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
-        </is>
-      </c>
-      <c r="R106" s="2" t="n"/>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S106" s="2" t="n"/>
       <c r="T106" s="2" t="inlineStr">
         <is>
@@ -6806,35 +6796,39 @@
         </is>
       </c>
       <c r="U106" s="2" t="n"/>
-      <c r="V106" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W106" s="2" t="n"/>
+      <c r="V106" s="2" t="n"/>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X106" s="2" t="n"/>
-      <c r="Y106" s="2" t="n"/>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3413</t>
+        </is>
+      </c>
       <c r="Z106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">religious professional </t>
+          <t>religious group membership of person source</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+          <t xml:space="preserve">A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion. </t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E107" s="2" t="n"/>
@@ -6851,14 +6845,10 @@
       <c r="P107" s="2" t="n"/>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
-        </is>
-      </c>
-      <c r="R107" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
       <c r="T107" s="2" t="inlineStr">
         <is>
@@ -6866,39 +6856,35 @@
         </is>
       </c>
       <c r="U107" s="2" t="n"/>
-      <c r="V107" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W107" s="2" t="n"/>
+      <c r="V107" s="2" t="n"/>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X107" s="2" t="n"/>
-      <c r="Y107" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2636</t>
-        </is>
-      </c>
+      <c r="Y107" s="2" t="n"/>
       <c r="Z107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>researcher</t>
+          <t xml:space="preserve">religious professional </t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study</t>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E108" s="2" t="n"/>
@@ -6915,10 +6901,14 @@
       <c r="P108" s="2" t="n"/>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>researcher, research assistant, investigator</t>
-        </is>
-      </c>
-      <c r="R108" s="2" t="n"/>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S108" s="2" t="n"/>
       <c r="T108" s="2" t="inlineStr">
         <is>
@@ -6926,35 +6916,39 @@
         </is>
       </c>
       <c r="U108" s="2" t="n"/>
-      <c r="V108" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W108" s="2" t="n"/>
+      <c r="V108" s="2" t="n"/>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X108" s="2" t="n"/>
-      <c r="Y108" s="2" t="n"/>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2636</t>
+        </is>
+      </c>
       <c r="Z108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>role model for a person</t>
+          <t>researcher</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
@@ -6969,25 +6963,25 @@
       <c r="N109" s="2" t="n"/>
       <c r="O109" s="2" t="n"/>
       <c r="P109" s="2" t="n"/>
-      <c r="Q109" s="2" t="n"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>researcher, research assistant, investigator</t>
+        </is>
+      </c>
       <c r="R109" s="2" t="n"/>
-      <c r="S109" s="2" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
-        </is>
-      </c>
+      <c r="S109" s="2" t="n"/>
       <c r="T109" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
       <c r="U109" s="2" t="n"/>
-      <c r="V109" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W109" s="2" t="n"/>
+      <c r="V109" s="2" t="n"/>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X109" s="2" t="n"/>
       <c r="Y109" s="2" t="n"/>
       <c r="Z109" s="2" t="n"/>
@@ -6995,22 +6989,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales worker </t>
+          <t>role model for a person</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets. </t>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t>person</t>
         </is>
       </c>
       <c r="E110" s="2" t="n"/>
@@ -7025,56 +7019,48 @@
       <c r="N110" s="2" t="n"/>
       <c r="O110" s="2" t="n"/>
       <c r="P110" s="2" t="n"/>
-      <c r="Q110" s="2" t="inlineStr">
-        <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
-      <c r="R110" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
-      <c r="S110" s="2" t="n"/>
+      <c r="Q110" s="2" t="n"/>
+      <c r="R110" s="2" t="n"/>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+        </is>
+      </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
       <c r="U110" s="2" t="n"/>
-      <c r="V110" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W110" s="2" t="n"/>
+      <c r="V110" s="2" t="n"/>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X110" s="2" t="n"/>
-      <c r="Y110" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 52</t>
-        </is>
-      </c>
+      <c r="Y110" s="2" t="n"/>
       <c r="Z110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>school student role</t>
+          <t xml:space="preserve">sales worker </t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t xml:space="preserve">A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets. </t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
@@ -7089,8 +7075,16 @@
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="2" t="n"/>
       <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="n"/>
-      <c r="R111" s="2" t="n"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S111" s="2" t="n"/>
       <c r="T111" s="2" t="inlineStr">
         <is>
@@ -7098,35 +7092,39 @@
         </is>
       </c>
       <c r="U111" s="2" t="n"/>
-      <c r="V111" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W111" s="2" t="n"/>
+      <c r="V111" s="2" t="n"/>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X111" s="2" t="n"/>
-      <c r="Y111" s="2" t="n"/>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 52</t>
+        </is>
+      </c>
       <c r="Z111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">science and engineering professional </t>
+          <t>school student role</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E112" s="2" t="n"/>
@@ -7141,16 +7139,8 @@
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="2" t="n"/>
       <c r="P112" s="2" t="n"/>
-      <c r="Q112" s="2" t="inlineStr">
-        <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
-        </is>
-      </c>
-      <c r="R112" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q112" s="2" t="n"/>
+      <c r="R112" s="2" t="n"/>
       <c r="S112" s="2" t="n"/>
       <c r="T112" s="2" t="inlineStr">
         <is>
@@ -7158,39 +7148,35 @@
         </is>
       </c>
       <c r="U112" s="2" t="n"/>
-      <c r="V112" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W112" s="2" t="n"/>
+      <c r="V112" s="2" t="n"/>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X112" s="2" t="n"/>
-      <c r="Y112" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 21</t>
-        </is>
-      </c>
+      <c r="Y112" s="2" t="n"/>
       <c r="Z112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">secondary education teacher </t>
+          <t xml:space="preserve">science and engineering professional </t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E113" s="2" t="n"/>
@@ -7207,7 +7193,7 @@
       <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Secondary school teacher, High school teacher</t>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
@@ -7222,16 +7208,16 @@
         </is>
       </c>
       <c r="U113" s="2" t="n"/>
-      <c r="V113" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W113" s="2" t="n"/>
+      <c r="V113" s="2" t="n"/>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X113" s="2" t="n"/>
       <c r="Y113" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 233</t>
+          <t>ISCO: 21</t>
         </is>
       </c>
       <c r="Z113" s="2" t="n"/>
@@ -7239,22 +7225,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t xml:space="preserve">secondary education teacher </t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E114" s="2" t="n"/>
@@ -7269,7 +7255,11 @@
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="2" t="n"/>
       <c r="P114" s="2" t="n"/>
-      <c r="Q114" s="2" t="n"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>Secondary school teacher, High school teacher</t>
+        </is>
+      </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -7282,16 +7272,16 @@
         </is>
       </c>
       <c r="U114" s="2" t="n"/>
-      <c r="V114" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W114" s="2" t="n"/>
+      <c r="V114" s="2" t="n"/>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X114" s="2" t="n"/>
       <c r="Y114" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 5</t>
+          <t>ISCO: 233</t>
         </is>
       </c>
       <c r="Z114" s="2" t="n"/>
@@ -7299,22 +7289,22 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>sibling relationship</t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
@@ -7329,12 +7319,12 @@
       <c r="N115" s="2" t="n"/>
       <c r="O115" s="2" t="n"/>
       <c r="P115" s="2" t="n"/>
-      <c r="Q115" s="2" t="inlineStr">
-        <is>
-          <t>brother, sister, step-brother, step-sister</t>
-        </is>
-      </c>
-      <c r="R115" s="2" t="n"/>
+      <c r="Q115" s="2" t="n"/>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S115" s="2" t="n"/>
       <c r="T115" s="2" t="inlineStr">
         <is>
@@ -7342,35 +7332,39 @@
         </is>
       </c>
       <c r="U115" s="2" t="n"/>
-      <c r="V115" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W115" s="2" t="n"/>
+      <c r="V115" s="2" t="n"/>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X115" s="2" t="n"/>
-      <c r="Y115" s="2" t="n"/>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 5</t>
+        </is>
+      </c>
       <c r="Z115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">skilled agricultural, forestry and fishery worker </t>
+          <t>sibling relationship</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
@@ -7387,14 +7381,10 @@
       <c r="P116" s="2" t="n"/>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
-      <c r="R116" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>brother, sister, step-brother, step-sister</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="n"/>
       <c r="S116" s="2" t="n"/>
       <c r="T116" s="2" t="inlineStr">
         <is>
@@ -7402,39 +7392,35 @@
         </is>
       </c>
       <c r="U116" s="2" t="n"/>
-      <c r="V116" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W116" s="2" t="n"/>
+      <c r="V116" s="2" t="n"/>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X116" s="2" t="n"/>
-      <c r="Y116" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 6</t>
-        </is>
-      </c>
+      <c r="Y116" s="2" t="n"/>
       <c r="Z116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social professional </t>
+          <t xml:space="preserve">skilled agricultural, forestry and fishery worker </t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E117" s="2" t="n"/>
@@ -7451,7 +7437,7 @@
       <c r="P117" s="2" t="n"/>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
@@ -7466,16 +7452,16 @@
         </is>
       </c>
       <c r="U117" s="2" t="n"/>
-      <c r="V117" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W117" s="2" t="n"/>
+      <c r="V117" s="2" t="n"/>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X117" s="2" t="n"/>
       <c r="Y117" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 263</t>
+          <t>ISCO: 6</t>
         </is>
       </c>
       <c r="Z117" s="2" t="n"/>
@@ -7483,22 +7469,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social work and counselling professional </t>
+          <t xml:space="preserve">social professional </t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems. </t>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social professional </t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E118" s="2" t="n"/>
@@ -7515,7 +7501,7 @@
       <c r="P118" s="2" t="n"/>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
@@ -7530,16 +7516,16 @@
         </is>
       </c>
       <c r="U118" s="2" t="n"/>
-      <c r="V118" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W118" s="2" t="n"/>
+      <c r="V118" s="2" t="n"/>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X118" s="2" t="n"/>
       <c r="Y118" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2635</t>
+          <t>ISCO: 263</t>
         </is>
       </c>
       <c r="Z118" s="2" t="n"/>
@@ -7547,22 +7533,22 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social work associate professional </t>
+          <t xml:space="preserve">social work and counselling professional </t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+          <t xml:space="preserve">A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems. </t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t xml:space="preserve">social professional </t>
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
@@ -7579,7 +7565,7 @@
       <c r="P119" s="2" t="n"/>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -7594,16 +7580,16 @@
         </is>
       </c>
       <c r="U119" s="2" t="n"/>
-      <c r="V119" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W119" s="2" t="n"/>
+      <c r="V119" s="2" t="n"/>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X119" s="2" t="n"/>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3412</t>
+          <t>ISCO: 2635</t>
         </is>
       </c>
       <c r="Z119" s="2" t="n"/>
@@ -7611,22 +7597,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t xml:space="preserve">social work associate professional </t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A social or demographic characteristic of a human being who is the bearer of a person source role. </t>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
@@ -7639,14 +7625,18 @@
       <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n"/>
       <c r="N120" s="2" t="n"/>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="O120" s="2" t="n"/>
       <c r="P120" s="2" t="n"/>
-      <c r="Q120" s="2" t="n"/>
-      <c r="R120" s="2" t="n"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S120" s="2" t="n"/>
       <c r="T120" s="2" t="inlineStr">
         <is>
@@ -7654,35 +7644,39 @@
         </is>
       </c>
       <c r="U120" s="2" t="n"/>
-      <c r="V120" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W120" s="2" t="n"/>
+      <c r="V120" s="2" t="n"/>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X120" s="2" t="n"/>
-      <c r="Y120" s="2" t="n"/>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3412</t>
+        </is>
+      </c>
       <c r="Z120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>source involved in co-production of intervention</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+          <t xml:space="preserve">A social or demographic characteristic of a human being who is the bearer of a person source role. </t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>source involved in development of intervention</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
@@ -7695,7 +7689,11 @@
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n"/>
       <c r="N121" s="2" t="n"/>
-      <c r="O121" s="2" t="n"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="P121" s="2" t="n"/>
       <c r="Q121" s="2" t="n"/>
       <c r="R121" s="2" t="n"/>
@@ -7706,12 +7704,12 @@
         </is>
       </c>
       <c r="U121" s="2" t="n"/>
-      <c r="V121" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W121" s="2" t="n"/>
+      <c r="V121" s="2" t="n"/>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X121" s="2" t="n"/>
       <c r="Y121" s="2" t="n"/>
       <c r="Z121" s="2" t="n"/>
@@ -7719,22 +7717,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
+          <t>source involved in co-production of intervention</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
           <t>source involved in development of intervention</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A BCI source that is involved in the development of intervention content. </t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
         </is>
       </c>
       <c r="E122" s="2" t="n"/>
@@ -7758,12 +7756,12 @@
         </is>
       </c>
       <c r="U122" s="2" t="n"/>
-      <c r="V122" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W122" s="2" t="n"/>
+      <c r="V122" s="2" t="n"/>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X122" s="2" t="n"/>
       <c r="Y122" s="2" t="n"/>
       <c r="Z122" s="2" t="n"/>
@@ -7771,17 +7769,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>source role related to intervention</t>
+          <t>source involved in development of intervention</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention. </t>
+          <t xml:space="preserve">A BCI source that is involved in the development of intervention content. </t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -7810,12 +7808,12 @@
         </is>
       </c>
       <c r="U123" s="2" t="n"/>
-      <c r="V123" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W123" s="2" t="n"/>
+      <c r="V123" s="2" t="n"/>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X123" s="2" t="n"/>
       <c r="Y123" s="2" t="n"/>
       <c r="Z123" s="2" t="n"/>
@@ -7823,22 +7821,22 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">special needs teacher </t>
+          <t>source role related to intervention</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A teaching professional that teaches children, young persons or adults with physical or intellectual special needs. </t>
+          <t xml:space="preserve">A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention. </t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>behaviour change intervention source</t>
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
@@ -7853,16 +7851,8 @@
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="2" t="n"/>
       <c r="P124" s="2" t="n"/>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
-        </is>
-      </c>
-      <c r="R124" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q124" s="2" t="n"/>
+      <c r="R124" s="2" t="n"/>
       <c r="S124" s="2" t="n"/>
       <c r="T124" s="2" t="inlineStr">
         <is>
@@ -7870,39 +7860,35 @@
         </is>
       </c>
       <c r="U124" s="2" t="n"/>
-      <c r="V124" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W124" s="2" t="n"/>
+      <c r="V124" s="2" t="n"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X124" s="2" t="n"/>
-      <c r="Y124" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2352</t>
-        </is>
-      </c>
+      <c r="Y124" s="2" t="n"/>
       <c r="Z124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">specialist medical practitioner </t>
+          <t xml:space="preserve">special needs teacher </t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization. </t>
+          <t xml:space="preserve">A teaching professional that teaches children, young persons or adults with physical or intellectual special needs. </t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>medical doctor</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
@@ -7919,7 +7905,7 @@
       <c r="P125" s="2" t="n"/>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
@@ -7934,16 +7920,16 @@
         </is>
       </c>
       <c r="U125" s="2" t="n"/>
-      <c r="V125" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W125" s="2" t="n"/>
+      <c r="V125" s="2" t="n"/>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X125" s="2" t="n"/>
       <c r="Y125" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2212</t>
+          <t>ISCO: 2352</t>
         </is>
       </c>
       <c r="Z125" s="2" t="n"/>
@@ -7951,22 +7937,22 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sport and fitness worker </t>
+          <t xml:space="preserve">specialist medical practitioner </t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization. </t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>medical doctor</t>
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
@@ -7983,7 +7969,7 @@
       <c r="P126" s="2" t="n"/>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
@@ -7998,16 +7984,16 @@
         </is>
       </c>
       <c r="U126" s="2" t="n"/>
-      <c r="V126" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W126" s="2" t="n"/>
+      <c r="V126" s="2" t="n"/>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X126" s="2" t="n"/>
       <c r="Y126" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 342</t>
+          <t>ISCO: 2212</t>
         </is>
       </c>
       <c r="Z126" s="2" t="n"/>
@@ -8015,22 +8001,22 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sports coach, instructor and official </t>
+          <t xml:space="preserve">sport and fitness worker </t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sport and fitness worker </t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
@@ -8047,7 +8033,7 @@
       <c r="P127" s="2" t="n"/>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
@@ -8062,16 +8048,16 @@
         </is>
       </c>
       <c r="U127" s="2" t="n"/>
-      <c r="V127" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W127" s="2" t="n"/>
+      <c r="V127" s="2" t="n"/>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X127" s="2" t="n"/>
       <c r="Y127" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3422</t>
+          <t>ISCO: 342</t>
         </is>
       </c>
       <c r="Z127" s="2" t="n"/>
@@ -8079,22 +8065,22 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>spouse or partner</t>
+          <t xml:space="preserve">sports coach, instructor and official </t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t xml:space="preserve">sport and fitness worker </t>
         </is>
       </c>
       <c r="E128" s="2" t="n"/>
@@ -8111,10 +8097,14 @@
       <c r="P128" s="2" t="n"/>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
-        </is>
-      </c>
-      <c r="R128" s="2" t="n"/>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S128" s="2" t="n"/>
       <c r="T128" s="2" t="inlineStr">
         <is>
@@ -8122,35 +8112,39 @@
         </is>
       </c>
       <c r="U128" s="2" t="n"/>
-      <c r="V128" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W128" s="2" t="n"/>
+      <c r="V128" s="2" t="n"/>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X128" s="2" t="n"/>
-      <c r="Y128" s="2" t="n"/>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3422</t>
+        </is>
+      </c>
       <c r="Z128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>spouse or partner</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
@@ -8165,7 +8159,11 @@
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="2" t="n"/>
       <c r="P129" s="2" t="n"/>
-      <c r="Q129" s="2" t="n"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
+        </is>
+      </c>
       <c r="R129" s="2" t="n"/>
       <c r="S129" s="2" t="n"/>
       <c r="T129" s="2" t="inlineStr">
@@ -8174,47 +8172,39 @@
         </is>
       </c>
       <c r="U129" s="2" t="n"/>
-      <c r="V129" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W129" s="2" t="n"/>
+      <c r="V129" s="2" t="n"/>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X129" s="2" t="n"/>
       <c r="Y129" s="2" t="n"/>
-      <c r="Z129" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>supervision of person source</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>role</t>
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="F130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
@@ -8225,11 +8215,7 @@
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="2" t="n"/>
       <c r="P130" s="2" t="n"/>
-      <c r="Q130" s="2" t="inlineStr">
-        <is>
-          <t>supervised</t>
-        </is>
-      </c>
+      <c r="Q130" s="2" t="n"/>
       <c r="R130" s="2" t="n"/>
       <c r="S130" s="2" t="n"/>
       <c r="T130" s="2" t="inlineStr">
@@ -8240,10 +8226,14 @@
       <c r="U130" s="2" t="n"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W130" s="2" t="n"/>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X130" s="2" t="n"/>
       <c r="Y130" s="2" t="n"/>
       <c r="Z130" s="2" t="n"/>
@@ -8251,26 +8241,30 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>BCIO:010128</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">target behaviour of person source </t>
+          <t>supervision of person source</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="n"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
@@ -8283,7 +8277,7 @@
       <c r="P131" s="2" t="n"/>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>source is highly physically active</t>
+          <t>supervised</t>
         </is>
       </c>
       <c r="R131" s="2" t="n"/>
@@ -8294,12 +8288,12 @@
         </is>
       </c>
       <c r="U131" s="2" t="n"/>
-      <c r="V131" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W131" s="2" t="n"/>
+      <c r="V131" s="2" t="n"/>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X131" s="2" t="n"/>
       <c r="Y131" s="2" t="n"/>
       <c r="Z131" s="2" t="n"/>
@@ -8307,22 +8301,22 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teachers’ aide </t>
+          <t xml:space="preserve">target behaviour of person source </t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
@@ -8339,14 +8333,10 @@
       <c r="P132" s="2" t="n"/>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
-      <c r="R132" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>source is highly physically active</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="n"/>
       <c r="S132" s="2" t="n"/>
       <c r="T132" s="2" t="inlineStr">
         <is>
@@ -8354,39 +8344,35 @@
         </is>
       </c>
       <c r="U132" s="2" t="n"/>
-      <c r="V132" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W132" s="2" t="n"/>
+      <c r="V132" s="2" t="n"/>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X132" s="2" t="n"/>
-      <c r="Y132" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 5312</t>
-        </is>
-      </c>
+      <c r="Y132" s="2" t="n"/>
       <c r="Z132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t xml:space="preserve">teachers’ aide </t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E133" s="2" t="n"/>
@@ -8403,7 +8389,7 @@
       <c r="P133" s="2" t="n"/>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
+          <t>Pre-school assistant, Teacher’s assistant</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
@@ -8418,16 +8404,16 @@
         </is>
       </c>
       <c r="U133" s="2" t="n"/>
-      <c r="V133" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W133" s="2" t="n"/>
+      <c r="V133" s="2" t="n"/>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X133" s="2" t="n"/>
       <c r="Y133" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 23</t>
+          <t>ISCO: 5312</t>
         </is>
       </c>
       <c r="Z133" s="2" t="n"/>
@@ -8435,17 +8421,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations. </t>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -8465,7 +8451,11 @@
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="2" t="n"/>
       <c r="P134" s="2" t="n"/>
-      <c r="Q134" s="2" t="n"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
+        </is>
+      </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -8478,16 +8468,16 @@
         </is>
       </c>
       <c r="U134" s="2" t="n"/>
-      <c r="V134" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W134" s="2" t="n"/>
+      <c r="V134" s="2" t="n"/>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X134" s="2" t="n"/>
       <c r="Y134" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3</t>
+          <t>ISCO: 23</t>
         </is>
       </c>
       <c r="Z134" s="2" t="n"/>
@@ -8495,22 +8485,22 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>total number of people able to deliver intervention</t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A count data item that is the total number of providers that are available and able to deliver the intervention. </t>
+          <t xml:space="preserve">A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations. </t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
@@ -8522,15 +8512,15 @@
       <c r="K135" s="2" t="n"/>
       <c r="L135" s="2" t="n"/>
       <c r="M135" s="2" t="n"/>
-      <c r="N135" s="2" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="N135" s="2" t="n"/>
       <c r="O135" s="2" t="n"/>
       <c r="P135" s="2" t="n"/>
       <c r="Q135" s="2" t="n"/>
-      <c r="R135" s="2" t="n"/>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S135" s="2" t="n"/>
       <c r="T135" s="2" t="inlineStr">
         <is>
@@ -8538,35 +8528,39 @@
         </is>
       </c>
       <c r="U135" s="2" t="n"/>
-      <c r="V135" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W135" s="2" t="n"/>
+      <c r="V135" s="2" t="n"/>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X135" s="2" t="n"/>
-      <c r="Y135" s="2" t="n"/>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3</t>
+        </is>
+      </c>
       <c r="Z135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">traditional and complementary medicine associate professional </t>
+          <t>total number of people able to deliver intervention</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional. </t>
+          <t xml:space="preserve">A count data item that is the total number of providers that are available and able to deliver the intervention. </t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
@@ -8578,19 +8572,15 @@
       <c r="K136" s="2" t="n"/>
       <c r="L136" s="2" t="n"/>
       <c r="M136" s="2" t="n"/>
-      <c r="N136" s="2" t="n"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="O136" s="2" t="n"/>
       <c r="P136" s="2" t="n"/>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q136" s="2" t="n"/>
+      <c r="R136" s="2" t="n"/>
       <c r="S136" s="2" t="n"/>
       <c r="T136" s="2" t="inlineStr">
         <is>
@@ -8598,39 +8588,35 @@
         </is>
       </c>
       <c r="U136" s="2" t="n"/>
-      <c r="V136" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W136" s="2" t="n"/>
+      <c r="V136" s="2" t="n"/>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X136" s="2" t="n"/>
-      <c r="Y136" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 323</t>
-        </is>
-      </c>
+      <c r="Y136" s="2" t="n"/>
       <c r="Z136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">traditional and complementary medicine professional </t>
+          <t xml:space="preserve">traditional and complementary medicine associate professional </t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+          <t xml:space="preserve">A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional. </t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
@@ -8647,7 +8633,7 @@
       <c r="P137" s="2" t="n"/>
       <c r="Q137" s="2" t="inlineStr">
         <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
         </is>
       </c>
       <c r="R137" s="2" t="inlineStr">
@@ -8662,16 +8648,16 @@
         </is>
       </c>
       <c r="U137" s="2" t="n"/>
-      <c r="V137" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W137" s="2" t="n"/>
+      <c r="V137" s="2" t="n"/>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X137" s="2" t="n"/>
       <c r="Y137" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 223</t>
+          <t>ISCO: 323</t>
         </is>
       </c>
       <c r="Z137" s="2" t="n"/>
@@ -8679,22 +8665,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>trainee role</t>
+          <t xml:space="preserve">traditional and complementary medicine professional </t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
@@ -8709,8 +8695,16 @@
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="2" t="n"/>
       <c r="P138" s="2" t="n"/>
-      <c r="Q138" s="2" t="n"/>
-      <c r="R138" s="2" t="n"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S138" s="2" t="n"/>
       <c r="T138" s="2" t="inlineStr">
         <is>
@@ -8718,35 +8712,39 @@
         </is>
       </c>
       <c r="U138" s="2" t="n"/>
-      <c r="V138" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W138" s="2" t="n"/>
+      <c r="V138" s="2" t="n"/>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X138" s="2" t="n"/>
-      <c r="Y138" s="2" t="n"/>
+      <c r="Y138" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 223</t>
+        </is>
+      </c>
       <c r="Z138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>undergraduate student role</t>
+          <t>trainee role</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -8761,11 +8759,7 @@
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="2" t="n"/>
       <c r="P139" s="2" t="n"/>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
+      <c r="Q139" s="2" t="n"/>
       <c r="R139" s="2" t="n"/>
       <c r="S139" s="2" t="n"/>
       <c r="T139" s="2" t="inlineStr">
@@ -8774,12 +8768,12 @@
         </is>
       </c>
       <c r="U139" s="2" t="n"/>
-      <c r="V139" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W139" s="2" t="n"/>
+      <c r="V139" s="2" t="n"/>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X139" s="2" t="n"/>
       <c r="Y139" s="2" t="n"/>
       <c r="Z139" s="2" t="n"/>
@@ -8787,23 +8781,22 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">university and higher education teacher
-</t>
+          <t>undergraduate student role</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
@@ -8820,14 +8813,10 @@
       <c r="P140" s="2" t="n"/>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>undergraduate student</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="n"/>
       <c r="S140" s="2" t="n"/>
       <c r="T140" s="2" t="inlineStr">
         <is>
@@ -8835,39 +8824,36 @@
         </is>
       </c>
       <c r="U140" s="2" t="n"/>
-      <c r="V140" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W140" s="2" t="n"/>
+      <c r="V140" s="2" t="n"/>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X140" s="2" t="n"/>
-      <c r="Y140" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 231</t>
-        </is>
-      </c>
+      <c r="Y140" s="2" t="n"/>
       <c r="Z140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">veterinarian </t>
+          <t xml:space="preserve">university and higher education teacher
+</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals. </t>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
@@ -8884,7 +8870,7 @@
       <c r="P141" s="2" t="n"/>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
@@ -8899,16 +8885,16 @@
         </is>
       </c>
       <c r="U141" s="2" t="n"/>
-      <c r="V141" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W141" s="2" t="n"/>
+      <c r="V141" s="2" t="n"/>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X141" s="2" t="n"/>
       <c r="Y141" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 225</t>
+          <t>ISCO: 231</t>
         </is>
       </c>
       <c r="Z141" s="2" t="n"/>
@@ -8916,22 +8902,22 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>vocational education teacher</t>
+          <t xml:space="preserve">veterinarian </t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges. </t>
+          <t xml:space="preserve">A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals. </t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
@@ -8948,7 +8934,7 @@
       <c r="P142" s="2" t="n"/>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr">
@@ -8963,16 +8949,16 @@
         </is>
       </c>
       <c r="U142" s="2" t="n"/>
-      <c r="V142" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W142" s="2" t="n"/>
+      <c r="V142" s="2" t="n"/>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X142" s="2" t="n"/>
       <c r="Y142" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 232</t>
+          <t>ISCO: 225</t>
         </is>
       </c>
       <c r="Z142" s="2" t="n"/>
@@ -8980,30 +8966,26 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>volunteering of person source</t>
+          <t>vocational education teacher</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+          <t xml:space="preserve">A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges. </t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>process</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E143" s="2" t="n"/>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
@@ -9016,10 +8998,14 @@
       <c r="P143" s="2" t="n"/>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
-      <c r="R143" s="2" t="n"/>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S143" s="2" t="n"/>
       <c r="T143" s="2" t="inlineStr">
         <is>
@@ -9027,15 +9013,79 @@
         </is>
       </c>
       <c r="U143" s="2" t="n"/>
-      <c r="V143" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W143" s="2" t="n"/>
+      <c r="V143" s="2" t="n"/>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
       <c r="X143" s="2" t="n"/>
-      <c r="Y143" s="2" t="n"/>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 232</t>
+        </is>
+      </c>
       <c r="Z143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010129</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>volunteering of person source</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="n"/>
+      <c r="H144" s="2" t="n"/>
+      <c r="I144" s="2" t="n"/>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
+      <c r="L144" s="2" t="n"/>
+      <c r="M144" s="2" t="n"/>
+      <c r="N144" s="2" t="n"/>
+      <c r="O144" s="2" t="n"/>
+      <c r="P144" s="2" t="n"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="n"/>
+      <c r="S144" s="2" t="n"/>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="n"/>
+      <c r="V144" s="2" t="n"/>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="n"/>
+      <c r="Y144" s="2" t="n"/>
+      <c r="Z144" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007fffd4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffffff"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,11 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1350,48 +1344,48 @@
       <c r="Z14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>BCIO:030000</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>behaviour change intervention study investigator role</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>researcher</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n"/>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="2" t="n"/>
+      <c r="Z15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -1354,7 +1354,11 @@
           <t>behaviour change intervention study investigator role</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>A researcher role played by a person that contributes substantively to production or reporting of a BCI evaluation study.</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>researcher</t>

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -1361,7 +1361,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>researcher</t>
+          <t>researcher role</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -6936,12 +6936,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>researcher</t>
+          <t>researcher role</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study</t>
+          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007fffd4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,10 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,27 +541,27 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Curation status</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>To be reviewed by</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer query</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Definition_ID</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Curator</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Curation status</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>To be reviewed by</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Definition_ID</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Reviewer query</t>
         </is>
       </c>
     </row>
@@ -567,17 +573,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>acquired knowledge or skill</t>
+          <t>acquired expertise</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+          <t>An expertise of person source that is additional knowledge or skills supplied to the source to allow them to deliver the intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>knowledge or skill</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -601,12 +607,12 @@
         </is>
       </c>
       <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
@@ -657,12 +663,12 @@
         </is>
       </c>
       <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
@@ -709,12 +715,12 @@
         </is>
       </c>
       <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="n"/>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -769,12 +775,12 @@
         </is>
       </c>
       <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n"/>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="n"/>
       <c r="Y5" s="2" t="inlineStr">
         <is>
@@ -833,12 +839,12 @@
         </is>
       </c>
       <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="n"/>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="n"/>
       <c r="Y6" s="2" t="n"/>
       <c r="Z6" s="2" t="n"/>
@@ -893,12 +899,12 @@
         </is>
       </c>
       <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="n"/>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="n"/>
       <c r="X7" s="2" t="n"/>
       <c r="Y7" s="2" t="inlineStr">
         <is>
@@ -957,12 +963,12 @@
         </is>
       </c>
       <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="n"/>
       <c r="X8" s="2" t="n"/>
       <c r="Y8" s="2" t="inlineStr">
         <is>
@@ -1021,12 +1027,12 @@
         </is>
       </c>
       <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n"/>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="n"/>
       <c r="X9" s="2" t="n"/>
       <c r="Y9" s="2" t="inlineStr">
         <is>
@@ -1081,12 +1087,12 @@
         </is>
       </c>
       <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="n"/>
       <c r="Y10" s="2" t="inlineStr">
         <is>
@@ -1145,12 +1151,12 @@
         </is>
       </c>
       <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n"/>
       <c r="X11" s="2" t="n"/>
       <c r="Y11" s="2" t="inlineStr">
         <is>
@@ -1209,12 +1215,12 @@
         </is>
       </c>
       <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n"/>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="n"/>
       <c r="X12" s="2" t="n"/>
       <c r="Y12" s="2" t="inlineStr">
         <is>
@@ -1273,12 +1279,12 @@
         </is>
       </c>
       <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n"/>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="n"/>
       <c r="X13" s="2" t="n"/>
       <c r="Y13" s="2" t="inlineStr">
         <is>
@@ -1331,17 +1337,17 @@
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>JH</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n"/>
       <c r="X14" s="2" t="n"/>
       <c r="Y14" s="2" t="n"/>
-      <c r="Z14" s="2" t="n"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1381,12 +1387,12 @@
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n"/>
       <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="n"/>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="n"/>
       <c r="X15" s="2" t="n"/>
       <c r="Y15" s="2" t="n"/>
       <c r="Z15" s="2" t="n"/>
@@ -1441,12 +1447,12 @@
         </is>
       </c>
       <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="n"/>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
@@ -1501,12 +1507,12 @@
         </is>
       </c>
       <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="n"/>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n"/>
       <c r="X17" s="2" t="n"/>
       <c r="Y17" s="2" t="n"/>
       <c r="Z17" s="2" t="n"/>
@@ -1561,12 +1567,12 @@
         </is>
       </c>
       <c r="U18" s="2" t="n"/>
-      <c r="V18" s="2" t="n"/>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n"/>
       <c r="X18" s="2" t="n"/>
       <c r="Y18" s="2" t="inlineStr">
         <is>
@@ -1621,12 +1627,12 @@
         </is>
       </c>
       <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="n"/>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="n"/>
       <c r="Y19" s="2" t="n"/>
       <c r="Z19" s="2" t="n"/>
@@ -1681,12 +1687,12 @@
         </is>
       </c>
       <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="n"/>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="n"/>
       <c r="Y20" s="2" t="inlineStr">
         <is>
@@ -1737,12 +1743,12 @@
         </is>
       </c>
       <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="n"/>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="n"/>
       <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="n"/>
       <c r="Z21" s="2" t="n"/>
@@ -1797,12 +1803,12 @@
         </is>
       </c>
       <c r="U22" s="2" t="n"/>
-      <c r="V22" s="2" t="n"/>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="n"/>
       <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
@@ -1861,12 +1867,12 @@
         </is>
       </c>
       <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="n"/>
       <c r="Y23" s="2" t="inlineStr">
         <is>
@@ -1925,12 +1931,12 @@
         </is>
       </c>
       <c r="U24" s="2" t="n"/>
-      <c r="V24" s="2" t="n"/>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="inlineStr">
         <is>
@@ -1989,12 +1995,12 @@
         </is>
       </c>
       <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="n"/>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="n"/>
       <c r="X25" s="2" t="n"/>
       <c r="Y25" s="2" t="inlineStr">
         <is>
@@ -2053,12 +2059,12 @@
         </is>
       </c>
       <c r="U26" s="2" t="n"/>
-      <c r="V26" s="2" t="n"/>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="n"/>
       <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
@@ -2117,12 +2123,12 @@
         </is>
       </c>
       <c r="U27" s="2" t="n"/>
-      <c r="V27" s="2" t="n"/>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="n"/>
       <c r="X27" s="2" t="n"/>
       <c r="Y27" s="2" t="inlineStr">
         <is>
@@ -2179,17 +2185,17 @@
       <c r="U28" s="2" t="n"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="n"/>
       <c r="X28" s="2" t="n"/>
       <c r="Y28" s="2" t="n"/>
-      <c r="Z28" s="2" t="n"/>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2241,12 +2247,12 @@
         </is>
       </c>
       <c r="U29" s="2" t="n"/>
-      <c r="V29" s="2" t="n"/>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="n"/>
       <c r="X29" s="2" t="n"/>
       <c r="Y29" s="2" t="n"/>
       <c r="Z29" s="2" t="n"/>
@@ -2297,12 +2303,12 @@
         </is>
       </c>
       <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="n"/>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="n"/>
       <c r="X30" s="2" t="n"/>
       <c r="Y30" s="2" t="n"/>
       <c r="Z30" s="2" t="n"/>
@@ -2357,12 +2363,12 @@
         </is>
       </c>
       <c r="U31" s="2" t="n"/>
-      <c r="V31" s="2" t="n"/>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="n"/>
       <c r="X31" s="2" t="n"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
@@ -2421,12 +2427,12 @@
         </is>
       </c>
       <c r="U32" s="2" t="n"/>
-      <c r="V32" s="2" t="n"/>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="n"/>
       <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
@@ -2477,12 +2483,12 @@
         </is>
       </c>
       <c r="U33" s="2" t="n"/>
-      <c r="V33" s="2" t="n"/>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="n"/>
       <c r="X33" s="2" t="n"/>
       <c r="Y33" s="2" t="n"/>
       <c r="Z33" s="2" t="n"/>
@@ -2529,12 +2535,12 @@
         </is>
       </c>
       <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="n"/>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="n"/>
       <c r="X34" s="2" t="n"/>
       <c r="Y34" s="2" t="n"/>
       <c r="Z34" s="2" t="n"/>
@@ -2589,12 +2595,12 @@
         </is>
       </c>
       <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="n"/>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="n"/>
       <c r="X35" s="2" t="n"/>
       <c r="Y35" s="2" t="inlineStr">
         <is>
@@ -2655,12 +2661,12 @@
         </is>
       </c>
       <c r="U36" s="2" t="n"/>
-      <c r="V36" s="2" t="n"/>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="n"/>
       <c r="X36" s="2" t="n"/>
       <c r="Y36" s="2" t="inlineStr">
         <is>
@@ -2715,12 +2721,12 @@
         </is>
       </c>
       <c r="U37" s="2" t="n"/>
-      <c r="V37" s="2" t="n"/>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="n"/>
       <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="n"/>
       <c r="Z37" s="2" t="n"/>
@@ -2775,12 +2781,12 @@
         </is>
       </c>
       <c r="U38" s="2" t="n"/>
-      <c r="V38" s="2" t="n"/>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="n"/>
       <c r="X38" s="2" t="n"/>
       <c r="Y38" s="2" t="n"/>
       <c r="Z38" s="2" t="n"/>
@@ -2831,12 +2837,12 @@
         </is>
       </c>
       <c r="U39" s="2" t="n"/>
-      <c r="V39" s="2" t="n"/>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="n"/>
       <c r="X39" s="2" t="n"/>
       <c r="Y39" s="2" t="n"/>
       <c r="Z39" s="2" t="n"/>
@@ -2885,17 +2891,17 @@
       <c r="U40" s="2" t="n"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="n"/>
       <c r="X40" s="2" t="n"/>
       <c r="Y40" s="2" t="n"/>
-      <c r="Z40" s="2" t="n"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2945,17 +2951,17 @@
       <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="n"/>
       <c r="X41" s="2" t="n"/>
       <c r="Y41" s="2" t="n"/>
-      <c r="Z41" s="2" t="n"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3007,12 +3013,12 @@
         </is>
       </c>
       <c r="U42" s="2" t="n"/>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="n"/>
       <c r="X42" s="2" t="n"/>
       <c r="Y42" s="2" t="inlineStr">
         <is>
@@ -3063,12 +3069,12 @@
         </is>
       </c>
       <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="n"/>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="n"/>
       <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="n"/>
       <c r="Z43" s="2" t="n"/>
@@ -3117,17 +3123,17 @@
       <c r="U44" s="2" t="n"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="n"/>
       <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
-      <c r="Z44" s="2" t="n"/>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3175,12 +3181,12 @@
         </is>
       </c>
       <c r="U45" s="2" t="n"/>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="n"/>
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="n"/>
       <c r="Z45" s="2" t="n"/>
@@ -3235,12 +3241,12 @@
         </is>
       </c>
       <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="inlineStr">
         <is>
@@ -3295,12 +3301,12 @@
         </is>
       </c>
       <c r="U47" s="2" t="n"/>
-      <c r="V47" s="2" t="n"/>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="n"/>
       <c r="X47" s="2" t="n"/>
       <c r="Y47" s="2" t="n"/>
       <c r="Z47" s="2" t="n"/>
@@ -3355,12 +3361,12 @@
         </is>
       </c>
       <c r="U48" s="2" t="n"/>
-      <c r="V48" s="2" t="n"/>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="n"/>
       <c r="X48" s="2" t="n"/>
       <c r="Y48" s="2" t="inlineStr">
         <is>
@@ -3419,12 +3425,12 @@
         </is>
       </c>
       <c r="U49" s="2" t="n"/>
-      <c r="V49" s="2" t="n"/>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="n"/>
       <c r="X49" s="2" t="n"/>
       <c r="Y49" s="2" t="inlineStr">
         <is>
@@ -3483,12 +3489,12 @@
         </is>
       </c>
       <c r="U50" s="2" t="n"/>
-      <c r="V50" s="2" t="n"/>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="n"/>
       <c r="X50" s="2" t="n"/>
       <c r="Y50" s="2" t="inlineStr">
         <is>
@@ -3543,12 +3549,12 @@
         </is>
       </c>
       <c r="U51" s="2" t="n"/>
-      <c r="V51" s="2" t="n"/>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="n"/>
       <c r="X51" s="2" t="n"/>
       <c r="Y51" s="2" t="n"/>
       <c r="Z51" s="2" t="n"/>
@@ -3599,12 +3605,12 @@
         </is>
       </c>
       <c r="U52" s="2" t="n"/>
-      <c r="V52" s="2" t="n"/>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="n"/>
       <c r="X52" s="2" t="n"/>
       <c r="Y52" s="2" t="n"/>
       <c r="Z52" s="2" t="n"/>
@@ -3659,12 +3665,12 @@
         </is>
       </c>
       <c r="U53" s="2" t="n"/>
-      <c r="V53" s="2" t="n"/>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="n"/>
       <c r="X53" s="2" t="n"/>
       <c r="Y53" s="2" t="inlineStr">
         <is>
@@ -3715,12 +3721,12 @@
         </is>
       </c>
       <c r="U54" s="2" t="n"/>
-      <c r="V54" s="2" t="n"/>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="n"/>
       <c r="X54" s="2" t="n"/>
       <c r="Y54" s="2" t="n"/>
       <c r="Z54" s="2" t="n"/>
@@ -3775,12 +3781,12 @@
         </is>
       </c>
       <c r="U55" s="2" t="n"/>
-      <c r="V55" s="2" t="n"/>
-      <c r="W55" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="n"/>
       <c r="X55" s="2" t="n"/>
       <c r="Y55" s="2" t="inlineStr">
         <is>
@@ -3790,60 +3796,60 @@
       <c r="Z55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>BCIO:010121</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>knowledge or skill</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention. </t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>expertise of person source</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
+      <c r="L56" s="3" t="n"/>
+      <c r="M56" s="3" t="n"/>
+      <c r="N56" s="3" t="n"/>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="3" t="n"/>
+      <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>trained (if unclear whether pre-existing or acquired)</t>
         </is>
       </c>
-      <c r="R56" s="2" t="n"/>
-      <c r="S56" s="2" t="n"/>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="n"/>
-      <c r="V56" s="2" t="n"/>
-      <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="X56" s="2" t="n"/>
-      <c r="Y56" s="2" t="n"/>
-      <c r="Z56" s="2" t="n"/>
+      <c r="R56" s="3" t="n"/>
+      <c r="S56" s="3" t="n"/>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="n"/>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="n"/>
+      <c r="X56" s="3" t="n"/>
+      <c r="Y56" s="3" t="n"/>
+      <c r="Z56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3891,12 +3897,12 @@
         </is>
       </c>
       <c r="U57" s="2" t="n"/>
-      <c r="V57" s="2" t="n"/>
-      <c r="W57" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="n"/>
       <c r="X57" s="2" t="n"/>
       <c r="Y57" s="2" t="n"/>
       <c r="Z57" s="2" t="n"/>
@@ -3951,12 +3957,12 @@
         </is>
       </c>
       <c r="U58" s="2" t="n"/>
-      <c r="V58" s="2" t="n"/>
-      <c r="W58" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="n"/>
       <c r="X58" s="2" t="n"/>
       <c r="Y58" s="2" t="inlineStr">
         <is>
@@ -4015,12 +4021,12 @@
         </is>
       </c>
       <c r="U59" s="2" t="n"/>
-      <c r="V59" s="2" t="n"/>
-      <c r="W59" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="n"/>
       <c r="X59" s="2" t="n"/>
       <c r="Y59" s="2" t="inlineStr">
         <is>
@@ -4075,12 +4081,12 @@
         </is>
       </c>
       <c r="U60" s="2" t="n"/>
-      <c r="V60" s="2" t="n"/>
-      <c r="W60" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="n"/>
       <c r="X60" s="2" t="n"/>
       <c r="Y60" s="2" t="inlineStr">
         <is>
@@ -4139,12 +4145,12 @@
         </is>
       </c>
       <c r="U61" s="2" t="n"/>
-      <c r="V61" s="2" t="n"/>
-      <c r="W61" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="n"/>
       <c r="X61" s="2" t="n"/>
       <c r="Y61" s="2" t="inlineStr">
         <is>
@@ -4199,12 +4205,12 @@
         </is>
       </c>
       <c r="U62" s="2" t="n"/>
-      <c r="V62" s="2" t="n"/>
-      <c r="W62" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="n"/>
       <c r="X62" s="2" t="n"/>
       <c r="Y62" s="2" t="n"/>
       <c r="Z62" s="2" t="n"/>
@@ -4257,17 +4263,17 @@
       <c r="U63" s="2" t="n"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="n"/>
       <c r="X63" s="2" t="n"/>
       <c r="Y63" s="2" t="n"/>
-      <c r="Z63" s="2" t="n"/>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4319,12 +4325,12 @@
         </is>
       </c>
       <c r="U64" s="2" t="n"/>
-      <c r="V64" s="2" t="n"/>
-      <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="n"/>
       <c r="X64" s="2" t="n"/>
       <c r="Y64" s="2" t="inlineStr">
         <is>
@@ -4379,12 +4385,12 @@
         </is>
       </c>
       <c r="U65" s="2" t="n"/>
-      <c r="V65" s="2" t="n"/>
-      <c r="W65" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="n"/>
       <c r="X65" s="2" t="n"/>
       <c r="Y65" s="2" t="n"/>
       <c r="Z65" s="2" t="n"/>
@@ -4439,12 +4445,12 @@
         </is>
       </c>
       <c r="U66" s="2" t="n"/>
-      <c r="V66" s="2" t="n"/>
-      <c r="W66" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="n"/>
       <c r="X66" s="2" t="n"/>
       <c r="Y66" s="2" t="inlineStr">
         <is>
@@ -4503,12 +4509,12 @@
         </is>
       </c>
       <c r="U67" s="2" t="n"/>
-      <c r="V67" s="2" t="n"/>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="n"/>
       <c r="X67" s="2" t="n"/>
       <c r="Y67" s="2" t="inlineStr">
         <is>
@@ -4567,12 +4573,12 @@
         </is>
       </c>
       <c r="U68" s="2" t="n"/>
-      <c r="V68" s="2" t="n"/>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="n"/>
       <c r="X68" s="2" t="n"/>
       <c r="Y68" s="2" t="inlineStr">
         <is>
@@ -4631,12 +4637,12 @@
         </is>
       </c>
       <c r="U69" s="2" t="n"/>
-      <c r="V69" s="2" t="n"/>
-      <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="n"/>
       <c r="X69" s="2" t="n"/>
       <c r="Y69" s="2" t="inlineStr">
         <is>
@@ -4695,12 +4701,12 @@
         </is>
       </c>
       <c r="U70" s="2" t="n"/>
-      <c r="V70" s="2" t="n"/>
-      <c r="W70" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="n"/>
       <c r="X70" s="2" t="n"/>
       <c r="Y70" s="2" t="inlineStr">
         <is>
@@ -4755,12 +4761,12 @@
         </is>
       </c>
       <c r="U71" s="2" t="n"/>
-      <c r="V71" s="2" t="n"/>
-      <c r="W71" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="n"/>
       <c r="X71" s="2" t="n"/>
       <c r="Y71" s="2" t="n"/>
       <c r="Z71" s="2" t="n"/>
@@ -4815,12 +4821,12 @@
         </is>
       </c>
       <c r="U72" s="2" t="n"/>
-      <c r="V72" s="2" t="n"/>
-      <c r="W72" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="n"/>
       <c r="X72" s="2" t="n"/>
       <c r="Y72" s="2" t="inlineStr">
         <is>
@@ -4875,12 +4881,12 @@
         </is>
       </c>
       <c r="U73" s="2" t="n"/>
-      <c r="V73" s="2" t="n"/>
-      <c r="W73" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="n"/>
       <c r="X73" s="2" t="n"/>
       <c r="Y73" s="2" t="n"/>
       <c r="Z73" s="2" t="n"/>
@@ -4931,12 +4937,12 @@
         </is>
       </c>
       <c r="U74" s="2" t="n"/>
-      <c r="V74" s="2" t="n"/>
-      <c r="W74" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="n"/>
       <c r="X74" s="2" t="n"/>
       <c r="Y74" s="2" t="n"/>
       <c r="Z74" s="2" t="n"/>
@@ -4991,12 +4997,12 @@
         </is>
       </c>
       <c r="U75" s="2" t="n"/>
-      <c r="V75" s="2" t="n"/>
-      <c r="W75" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="n"/>
       <c r="X75" s="2" t="n"/>
       <c r="Y75" s="2" t="inlineStr">
         <is>
@@ -5051,12 +5057,12 @@
         </is>
       </c>
       <c r="U76" s="2" t="n"/>
-      <c r="V76" s="2" t="n"/>
-      <c r="W76" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="n"/>
       <c r="X76" s="2" t="n"/>
       <c r="Y76" s="2" t="inlineStr">
         <is>
@@ -5115,12 +5121,12 @@
         </is>
       </c>
       <c r="U77" s="2" t="n"/>
-      <c r="V77" s="2" t="n"/>
-      <c r="W77" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="n"/>
       <c r="X77" s="2" t="n"/>
       <c r="Y77" s="2" t="inlineStr">
         <is>
@@ -5179,12 +5185,12 @@
         </is>
       </c>
       <c r="U78" s="2" t="n"/>
-      <c r="V78" s="2" t="n"/>
-      <c r="W78" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="n"/>
       <c r="X78" s="2" t="n"/>
       <c r="Y78" s="2" t="inlineStr">
         <is>
@@ -5239,12 +5245,12 @@
         </is>
       </c>
       <c r="U79" s="2" t="n"/>
-      <c r="V79" s="2" t="n"/>
-      <c r="W79" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="n"/>
       <c r="X79" s="2" t="n"/>
       <c r="Y79" s="2" t="n"/>
       <c r="Z79" s="2" t="n"/>
@@ -5299,12 +5305,12 @@
         </is>
       </c>
       <c r="U80" s="2" t="n"/>
-      <c r="V80" s="2" t="n"/>
-      <c r="W80" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="n"/>
       <c r="X80" s="2" t="n"/>
       <c r="Y80" s="2" t="inlineStr">
         <is>
@@ -5361,17 +5367,17 @@
       <c r="U81" s="2" t="n"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>BG; PS</t>
-        </is>
-      </c>
-      <c r="W81" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="n"/>
       <c r="X81" s="2" t="n"/>
       <c r="Y81" s="2" t="n"/>
-      <c r="Z81" s="2" t="n"/>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>BG; PS</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5415,12 +5421,12 @@
         </is>
       </c>
       <c r="U82" s="2" t="n"/>
-      <c r="V82" s="2" t="n"/>
-      <c r="W82" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="n"/>
       <c r="X82" s="2" t="n"/>
       <c r="Y82" s="2" t="n"/>
       <c r="Z82" s="2" t="n"/>
@@ -5458,12 +5464,12 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
           <t>RW</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>External</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5519,12 @@
         </is>
       </c>
       <c r="U84" s="2" t="n"/>
-      <c r="V84" s="2" t="n"/>
-      <c r="W84" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="n"/>
       <c r="X84" s="2" t="n"/>
       <c r="Y84" s="2" t="n"/>
       <c r="Z84" s="2" t="n"/>
@@ -5573,12 +5579,12 @@
         </is>
       </c>
       <c r="U85" s="2" t="n"/>
-      <c r="V85" s="2" t="n"/>
-      <c r="W85" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="n"/>
       <c r="X85" s="2" t="n"/>
       <c r="Y85" s="2" t="inlineStr">
         <is>
@@ -5633,12 +5639,12 @@
         </is>
       </c>
       <c r="U86" s="2" t="n"/>
-      <c r="V86" s="2" t="n"/>
-      <c r="W86" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="n"/>
       <c r="X86" s="2" t="n"/>
       <c r="Y86" s="2" t="n"/>
       <c r="Z86" s="2" t="n"/>
@@ -5689,12 +5695,12 @@
         </is>
       </c>
       <c r="U87" s="2" t="n"/>
-      <c r="V87" s="2" t="n"/>
-      <c r="W87" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="n"/>
       <c r="X87" s="2" t="n"/>
       <c r="Y87" s="2" t="n"/>
       <c r="Z87" s="2" t="n"/>
@@ -5741,12 +5747,12 @@
         </is>
       </c>
       <c r="U88" s="2" t="n"/>
-      <c r="V88" s="2" t="n"/>
-      <c r="W88" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="n"/>
       <c r="X88" s="2" t="n"/>
       <c r="Y88" s="2" t="n"/>
       <c r="Z88" s="2" t="n"/>
@@ -5779,12 +5785,12 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
           <t>AW</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>External</t>
         </is>
       </c>
     </row>
@@ -5836,17 +5842,17 @@
       <c r="U90" s="2" t="n"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="W90" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="n"/>
       <c r="X90" s="2" t="n"/>
       <c r="Y90" s="2" t="n"/>
-      <c r="Z90" s="2" t="n"/>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5890,12 +5896,12 @@
         </is>
       </c>
       <c r="U91" s="2" t="n"/>
-      <c r="V91" s="2" t="n"/>
-      <c r="W91" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="n"/>
       <c r="X91" s="2" t="n"/>
       <c r="Y91" s="2" t="n"/>
       <c r="Z91" s="2" t="n"/>
@@ -5950,12 +5956,12 @@
         </is>
       </c>
       <c r="U92" s="2" t="n"/>
-      <c r="V92" s="2" t="n"/>
-      <c r="W92" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="n"/>
       <c r="X92" s="2" t="n"/>
       <c r="Y92" s="2" t="inlineStr">
         <is>
@@ -6006,12 +6012,12 @@
         </is>
       </c>
       <c r="U93" s="2" t="n"/>
-      <c r="V93" s="2" t="n"/>
-      <c r="W93" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="n"/>
       <c r="X93" s="2" t="n"/>
       <c r="Y93" s="2" t="n"/>
       <c r="Z93" s="2" t="n"/>
@@ -6066,12 +6072,12 @@
         </is>
       </c>
       <c r="U94" s="2" t="n"/>
-      <c r="V94" s="2" t="n"/>
-      <c r="W94" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="n"/>
       <c r="X94" s="2" t="n"/>
       <c r="Y94" s="2" t="inlineStr">
         <is>
@@ -6130,12 +6136,12 @@
         </is>
       </c>
       <c r="U95" s="2" t="n"/>
-      <c r="V95" s="2" t="n"/>
-      <c r="W95" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="n"/>
       <c r="X95" s="2" t="n"/>
       <c r="Y95" s="2" t="inlineStr">
         <is>
@@ -6194,12 +6200,12 @@
         </is>
       </c>
       <c r="U96" s="2" t="n"/>
-      <c r="V96" s="2" t="n"/>
-      <c r="W96" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="n"/>
       <c r="X96" s="2" t="n"/>
       <c r="Y96" s="2" t="inlineStr">
         <is>
@@ -6258,12 +6264,12 @@
         </is>
       </c>
       <c r="U97" s="2" t="n"/>
-      <c r="V97" s="2" t="n"/>
-      <c r="W97" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="n"/>
       <c r="X97" s="2" t="n"/>
       <c r="Y97" s="2" t="inlineStr">
         <is>
@@ -6322,12 +6328,12 @@
         </is>
       </c>
       <c r="U98" s="2" t="n"/>
-      <c r="V98" s="2" t="n"/>
-      <c r="W98" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="n"/>
       <c r="X98" s="2" t="n"/>
       <c r="Y98" s="2" t="inlineStr">
         <is>
@@ -6344,17 +6350,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>pre-existing knowledge or skill</t>
+          <t>pre-existing expertise</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+          <t>An expertise of person source that is already possessed by the source which allows them to deliver the intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>knowledge or skill</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
@@ -6382,12 +6388,12 @@
         </is>
       </c>
       <c r="U99" s="2" t="n"/>
-      <c r="V99" s="2" t="n"/>
-      <c r="W99" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="n"/>
       <c r="X99" s="2" t="n"/>
       <c r="Y99" s="2" t="n"/>
       <c r="Z99" s="2" t="n"/>
@@ -6438,12 +6444,12 @@
         </is>
       </c>
       <c r="U100" s="2" t="n"/>
-      <c r="V100" s="2" t="n"/>
-      <c r="W100" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="n"/>
       <c r="X100" s="2" t="n"/>
       <c r="Y100" s="2" t="inlineStr">
         <is>
@@ -6498,12 +6504,12 @@
         </is>
       </c>
       <c r="U101" s="2" t="n"/>
-      <c r="V101" s="2" t="n"/>
-      <c r="W101" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="n"/>
       <c r="X101" s="2" t="n"/>
       <c r="Y101" s="2" t="inlineStr">
         <is>
@@ -6562,12 +6568,12 @@
         </is>
       </c>
       <c r="U102" s="2" t="n"/>
-      <c r="V102" s="2" t="n"/>
-      <c r="W102" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="n"/>
       <c r="X102" s="2" t="n"/>
       <c r="Y102" s="2" t="inlineStr">
         <is>
@@ -6618,12 +6624,12 @@
         </is>
       </c>
       <c r="U103" s="2" t="n"/>
-      <c r="V103" s="2" t="n"/>
-      <c r="W103" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="n"/>
       <c r="X103" s="2" t="n"/>
       <c r="Y103" s="2" t="n"/>
       <c r="Z103" s="2" t="n"/>
@@ -6678,12 +6684,12 @@
         </is>
       </c>
       <c r="U104" s="2" t="n"/>
-      <c r="V104" s="2" t="n"/>
-      <c r="W104" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="n"/>
       <c r="X104" s="2" t="n"/>
       <c r="Y104" s="2" t="inlineStr">
         <is>
@@ -6734,12 +6740,12 @@
         </is>
       </c>
       <c r="U105" s="2" t="n"/>
-      <c r="V105" s="2" t="n"/>
-      <c r="W105" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="n"/>
       <c r="X105" s="2" t="n"/>
       <c r="Y105" s="2" t="n"/>
       <c r="Z105" s="2" t="n"/>
@@ -6794,12 +6800,12 @@
         </is>
       </c>
       <c r="U106" s="2" t="n"/>
-      <c r="V106" s="2" t="n"/>
-      <c r="W106" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="n"/>
       <c r="X106" s="2" t="n"/>
       <c r="Y106" s="2" t="inlineStr">
         <is>
@@ -6854,12 +6860,12 @@
         </is>
       </c>
       <c r="U107" s="2" t="n"/>
-      <c r="V107" s="2" t="n"/>
-      <c r="W107" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="n"/>
       <c r="X107" s="2" t="n"/>
       <c r="Y107" s="2" t="n"/>
       <c r="Z107" s="2" t="n"/>
@@ -6914,12 +6920,12 @@
         </is>
       </c>
       <c r="U108" s="2" t="n"/>
-      <c r="V108" s="2" t="n"/>
-      <c r="W108" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="n"/>
       <c r="X108" s="2" t="n"/>
       <c r="Y108" s="2" t="inlineStr">
         <is>
@@ -6974,12 +6980,12 @@
         </is>
       </c>
       <c r="U109" s="2" t="n"/>
-      <c r="V109" s="2" t="n"/>
-      <c r="W109" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="n"/>
       <c r="X109" s="2" t="n"/>
       <c r="Y109" s="2" t="n"/>
       <c r="Z109" s="2" t="n"/>
@@ -7030,12 +7036,12 @@
         </is>
       </c>
       <c r="U110" s="2" t="n"/>
-      <c r="V110" s="2" t="n"/>
-      <c r="W110" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="n"/>
       <c r="X110" s="2" t="n"/>
       <c r="Y110" s="2" t="n"/>
       <c r="Z110" s="2" t="n"/>
@@ -7090,12 +7096,12 @@
         </is>
       </c>
       <c r="U111" s="2" t="n"/>
-      <c r="V111" s="2" t="n"/>
-      <c r="W111" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="n"/>
       <c r="X111" s="2" t="n"/>
       <c r="Y111" s="2" t="inlineStr">
         <is>
@@ -7146,12 +7152,12 @@
         </is>
       </c>
       <c r="U112" s="2" t="n"/>
-      <c r="V112" s="2" t="n"/>
-      <c r="W112" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="n"/>
       <c r="X112" s="2" t="n"/>
       <c r="Y112" s="2" t="n"/>
       <c r="Z112" s="2" t="n"/>
@@ -7206,12 +7212,12 @@
         </is>
       </c>
       <c r="U113" s="2" t="n"/>
-      <c r="V113" s="2" t="n"/>
-      <c r="W113" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="n"/>
       <c r="X113" s="2" t="n"/>
       <c r="Y113" s="2" t="inlineStr">
         <is>
@@ -7270,12 +7276,12 @@
         </is>
       </c>
       <c r="U114" s="2" t="n"/>
-      <c r="V114" s="2" t="n"/>
-      <c r="W114" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="n"/>
       <c r="X114" s="2" t="n"/>
       <c r="Y114" s="2" t="inlineStr">
         <is>
@@ -7330,12 +7336,12 @@
         </is>
       </c>
       <c r="U115" s="2" t="n"/>
-      <c r="V115" s="2" t="n"/>
-      <c r="W115" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="n"/>
       <c r="X115" s="2" t="n"/>
       <c r="Y115" s="2" t="inlineStr">
         <is>
@@ -7390,12 +7396,12 @@
         </is>
       </c>
       <c r="U116" s="2" t="n"/>
-      <c r="V116" s="2" t="n"/>
-      <c r="W116" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="n"/>
       <c r="X116" s="2" t="n"/>
       <c r="Y116" s="2" t="n"/>
       <c r="Z116" s="2" t="n"/>
@@ -7450,12 +7456,12 @@
         </is>
       </c>
       <c r="U117" s="2" t="n"/>
-      <c r="V117" s="2" t="n"/>
-      <c r="W117" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W117" s="2" t="n"/>
       <c r="X117" s="2" t="n"/>
       <c r="Y117" s="2" t="inlineStr">
         <is>
@@ -7514,12 +7520,12 @@
         </is>
       </c>
       <c r="U118" s="2" t="n"/>
-      <c r="V118" s="2" t="n"/>
-      <c r="W118" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="n"/>
       <c r="X118" s="2" t="n"/>
       <c r="Y118" s="2" t="inlineStr">
         <is>
@@ -7578,12 +7584,12 @@
         </is>
       </c>
       <c r="U119" s="2" t="n"/>
-      <c r="V119" s="2" t="n"/>
-      <c r="W119" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W119" s="2" t="n"/>
       <c r="X119" s="2" t="n"/>
       <c r="Y119" s="2" t="inlineStr">
         <is>
@@ -7642,12 +7648,12 @@
         </is>
       </c>
       <c r="U120" s="2" t="n"/>
-      <c r="V120" s="2" t="n"/>
-      <c r="W120" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W120" s="2" t="n"/>
       <c r="X120" s="2" t="n"/>
       <c r="Y120" s="2" t="inlineStr">
         <is>
@@ -7702,12 +7708,12 @@
         </is>
       </c>
       <c r="U121" s="2" t="n"/>
-      <c r="V121" s="2" t="n"/>
-      <c r="W121" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W121" s="2" t="n"/>
       <c r="X121" s="2" t="n"/>
       <c r="Y121" s="2" t="n"/>
       <c r="Z121" s="2" t="n"/>
@@ -7754,12 +7760,12 @@
         </is>
       </c>
       <c r="U122" s="2" t="n"/>
-      <c r="V122" s="2" t="n"/>
-      <c r="W122" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W122" s="2" t="n"/>
       <c r="X122" s="2" t="n"/>
       <c r="Y122" s="2" t="n"/>
       <c r="Z122" s="2" t="n"/>
@@ -7806,12 +7812,12 @@
         </is>
       </c>
       <c r="U123" s="2" t="n"/>
-      <c r="V123" s="2" t="n"/>
-      <c r="W123" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="n"/>
       <c r="X123" s="2" t="n"/>
       <c r="Y123" s="2" t="n"/>
       <c r="Z123" s="2" t="n"/>
@@ -7858,12 +7864,12 @@
         </is>
       </c>
       <c r="U124" s="2" t="n"/>
-      <c r="V124" s="2" t="n"/>
-      <c r="W124" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="n"/>
       <c r="X124" s="2" t="n"/>
       <c r="Y124" s="2" t="n"/>
       <c r="Z124" s="2" t="n"/>
@@ -7918,12 +7924,12 @@
         </is>
       </c>
       <c r="U125" s="2" t="n"/>
-      <c r="V125" s="2" t="n"/>
-      <c r="W125" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="n"/>
       <c r="X125" s="2" t="n"/>
       <c r="Y125" s="2" t="inlineStr">
         <is>
@@ -7982,12 +7988,12 @@
         </is>
       </c>
       <c r="U126" s="2" t="n"/>
-      <c r="V126" s="2" t="n"/>
-      <c r="W126" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="n"/>
       <c r="X126" s="2" t="n"/>
       <c r="Y126" s="2" t="inlineStr">
         <is>
@@ -8046,12 +8052,12 @@
         </is>
       </c>
       <c r="U127" s="2" t="n"/>
-      <c r="V127" s="2" t="n"/>
-      <c r="W127" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W127" s="2" t="n"/>
       <c r="X127" s="2" t="n"/>
       <c r="Y127" s="2" t="inlineStr">
         <is>
@@ -8110,12 +8116,12 @@
         </is>
       </c>
       <c r="U128" s="2" t="n"/>
-      <c r="V128" s="2" t="n"/>
-      <c r="W128" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W128" s="2" t="n"/>
       <c r="X128" s="2" t="n"/>
       <c r="Y128" s="2" t="inlineStr">
         <is>
@@ -8170,12 +8176,12 @@
         </is>
       </c>
       <c r="U129" s="2" t="n"/>
-      <c r="V129" s="2" t="n"/>
-      <c r="W129" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V129" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W129" s="2" t="n"/>
       <c r="X129" s="2" t="n"/>
       <c r="Y129" s="2" t="n"/>
       <c r="Z129" s="2" t="n"/>
@@ -8224,17 +8230,17 @@
       <c r="U130" s="2" t="n"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>AW</t>
-        </is>
-      </c>
-      <c r="W130" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="n"/>
       <c r="X130" s="2" t="n"/>
       <c r="Y130" s="2" t="n"/>
-      <c r="Z130" s="2" t="n"/>
+      <c r="Z130" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8286,12 +8292,12 @@
         </is>
       </c>
       <c r="U131" s="2" t="n"/>
-      <c r="V131" s="2" t="n"/>
-      <c r="W131" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="n"/>
       <c r="X131" s="2" t="n"/>
       <c r="Y131" s="2" t="n"/>
       <c r="Z131" s="2" t="n"/>
@@ -8342,12 +8348,12 @@
         </is>
       </c>
       <c r="U132" s="2" t="n"/>
-      <c r="V132" s="2" t="n"/>
-      <c r="W132" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="n"/>
       <c r="X132" s="2" t="n"/>
       <c r="Y132" s="2" t="n"/>
       <c r="Z132" s="2" t="n"/>
@@ -8402,12 +8408,12 @@
         </is>
       </c>
       <c r="U133" s="2" t="n"/>
-      <c r="V133" s="2" t="n"/>
-      <c r="W133" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="n"/>
       <c r="X133" s="2" t="n"/>
       <c r="Y133" s="2" t="inlineStr">
         <is>
@@ -8466,12 +8472,12 @@
         </is>
       </c>
       <c r="U134" s="2" t="n"/>
-      <c r="V134" s="2" t="n"/>
-      <c r="W134" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W134" s="2" t="n"/>
       <c r="X134" s="2" t="n"/>
       <c r="Y134" s="2" t="inlineStr">
         <is>
@@ -8526,12 +8532,12 @@
         </is>
       </c>
       <c r="U135" s="2" t="n"/>
-      <c r="V135" s="2" t="n"/>
-      <c r="W135" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V135" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W135" s="2" t="n"/>
       <c r="X135" s="2" t="n"/>
       <c r="Y135" s="2" t="inlineStr">
         <is>
@@ -8586,12 +8592,12 @@
         </is>
       </c>
       <c r="U136" s="2" t="n"/>
-      <c r="V136" s="2" t="n"/>
-      <c r="W136" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V136" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W136" s="2" t="n"/>
       <c r="X136" s="2" t="n"/>
       <c r="Y136" s="2" t="n"/>
       <c r="Z136" s="2" t="n"/>
@@ -8646,12 +8652,12 @@
         </is>
       </c>
       <c r="U137" s="2" t="n"/>
-      <c r="V137" s="2" t="n"/>
-      <c r="W137" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V137" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W137" s="2" t="n"/>
       <c r="X137" s="2" t="n"/>
       <c r="Y137" s="2" t="inlineStr">
         <is>
@@ -8710,12 +8716,12 @@
         </is>
       </c>
       <c r="U138" s="2" t="n"/>
-      <c r="V138" s="2" t="n"/>
-      <c r="W138" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V138" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W138" s="2" t="n"/>
       <c r="X138" s="2" t="n"/>
       <c r="Y138" s="2" t="inlineStr">
         <is>
@@ -8766,12 +8772,12 @@
         </is>
       </c>
       <c r="U139" s="2" t="n"/>
-      <c r="V139" s="2" t="n"/>
-      <c r="W139" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V139" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W139" s="2" t="n"/>
       <c r="X139" s="2" t="n"/>
       <c r="Y139" s="2" t="n"/>
       <c r="Z139" s="2" t="n"/>
@@ -8822,12 +8828,12 @@
         </is>
       </c>
       <c r="U140" s="2" t="n"/>
-      <c r="V140" s="2" t="n"/>
-      <c r="W140" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V140" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W140" s="2" t="n"/>
       <c r="X140" s="2" t="n"/>
       <c r="Y140" s="2" t="n"/>
       <c r="Z140" s="2" t="n"/>
@@ -8883,12 +8889,12 @@
         </is>
       </c>
       <c r="U141" s="2" t="n"/>
-      <c r="V141" s="2" t="n"/>
-      <c r="W141" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V141" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W141" s="2" t="n"/>
       <c r="X141" s="2" t="n"/>
       <c r="Y141" s="2" t="inlineStr">
         <is>
@@ -8947,12 +8953,12 @@
         </is>
       </c>
       <c r="U142" s="2" t="n"/>
-      <c r="V142" s="2" t="n"/>
-      <c r="W142" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V142" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W142" s="2" t="n"/>
       <c r="X142" s="2" t="n"/>
       <c r="Y142" s="2" t="inlineStr">
         <is>
@@ -9011,12 +9017,12 @@
         </is>
       </c>
       <c r="U143" s="2" t="n"/>
-      <c r="V143" s="2" t="n"/>
-      <c r="W143" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W143" s="2" t="n"/>
       <c r="X143" s="2" t="n"/>
       <c r="Y143" s="2" t="inlineStr">
         <is>
@@ -9075,12 +9081,12 @@
         </is>
       </c>
       <c r="U144" s="2" t="n"/>
-      <c r="V144" s="2" t="n"/>
-      <c r="W144" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="V144" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W144" s="2" t="n"/>
       <c r="X144" s="2" t="n"/>
       <c r="Y144" s="2" t="n"/>
       <c r="Z144" s="2" t="n"/>

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z144"/>
+  <dimension ref="A1:Z146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1520,86 +1520,70 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:051024</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">child care worker </t>
+          <t>certified professional role</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+          <t>A personal role that inheres in a human being by virtue of formal recognition of their competence by a professional or regulatory body.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="n"/>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="n"/>
+          <t>personal role</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="W18" s="2" t="n"/>
-      <c r="X18" s="2" t="n"/>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 5311</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="n"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>child relationship</t>
+          <t xml:space="preserve">child care worker </t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -1616,10 +1600,14 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>daughter, son, step-daughter, step-son</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="n"/>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
@@ -1634,28 +1622,32 @@
       </c>
       <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="n"/>
-      <c r="Y19" s="2" t="n"/>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 5311</t>
+        </is>
+      </c>
       <c r="Z19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">clerical support worker </t>
+          <t>child relationship</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments. </t>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -1672,14 +1664,10 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>daughter, son, step-daughter, step-son</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
@@ -1694,32 +1682,28 @@
       </c>
       <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="n"/>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 4</t>
-        </is>
-      </c>
+      <c r="Y20" s="2" t="n"/>
       <c r="Z20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>colleague</t>
+          <t xml:space="preserve">clerical support worker </t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+          <t xml:space="preserve">An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments. </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -1734,8 +1718,16 @@
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
@@ -1750,28 +1742,32 @@
       </c>
       <c r="W21" s="2" t="n"/>
       <c r="X21" s="2" t="n"/>
-      <c r="Y21" s="2" t="n"/>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 4</t>
+        </is>
+      </c>
       <c r="Z21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">community health worker </t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -1786,16 +1782,8 @@
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
@@ -1810,32 +1798,28 @@
       </c>
       <c r="W22" s="2" t="n"/>
       <c r="X22" s="2" t="n"/>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 3253</t>
-        </is>
-      </c>
+      <c r="Y22" s="2" t="n"/>
       <c r="Z22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">craft and related trades worker </t>
+          <t xml:space="preserve">community health worker </t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -1852,7 +1836,7 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -1876,7 +1860,7 @@
       <c r="X23" s="2" t="n"/>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 7</t>
+          <t>ISCO: 3253</t>
         </is>
       </c>
       <c r="Z23" s="2" t="n"/>
@@ -1884,22 +1868,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">creative and performing artist </t>
+          <t xml:space="preserve">craft and related trades worker </t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
@@ -1916,7 +1900,7 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -1940,7 +1924,7 @@
       <c r="X24" s="2" t="n"/>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 265</t>
+          <t>ISCO: 7</t>
         </is>
       </c>
       <c r="Z24" s="2" t="n"/>
@@ -1948,22 +1932,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dental assistant and therapist </t>
+          <t xml:space="preserve">creative and performing artist </t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
@@ -1980,7 +1964,7 @@
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -2004,7 +1988,7 @@
       <c r="X25" s="2" t="n"/>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3251</t>
+          <t>ISCO: 265</t>
         </is>
       </c>
       <c r="Z25" s="2" t="n"/>
@@ -2012,22 +1996,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dentist </t>
+          <t xml:space="preserve">dental assistant and therapist </t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry. </t>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
@@ -2044,7 +2028,7 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2068,7 +2052,7 @@
       <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2261</t>
+          <t>ISCO: 3251</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -2076,17 +2060,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dietician and nutritionist </t>
+          <t xml:space="preserve">dentist </t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+          <t xml:space="preserve">A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry. </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2108,7 +2092,7 @@
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -2132,7 +2116,7 @@
       <c r="X27" s="2" t="n"/>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2265</t>
+          <t>ISCO: 2261</t>
         </is>
       </c>
       <c r="Z27" s="2" t="n"/>
@@ -2140,22 +2124,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>discipline of current programme of study or training</t>
+          <t xml:space="preserve">dietician and nutritionist </t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>expertise discipline</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
@@ -2172,10 +2156,14 @@
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>psychology, medicine, hairdressing</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="n"/>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
@@ -2190,27 +2178,27 @@
       </c>
       <c r="W28" s="2" t="n"/>
       <c r="X28" s="2" t="n"/>
-      <c r="Y28" s="2" t="n"/>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2265</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>discipline of pre-existing knowledge or skill</t>
+          <t>discipline of current programme of study or training</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The expertise discipline in which the person source has acquired their pre-existing knowledge and skills. </t>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2228,15 +2216,11 @@
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+          <t>psychology, medicine, hairdressing</t>
         </is>
       </c>
       <c r="R29" s="2" t="n"/>
@@ -2255,27 +2239,31 @@
       <c r="W29" s="2" t="n"/>
       <c r="X29" s="2" t="n"/>
       <c r="Y29" s="2" t="n"/>
-      <c r="Z29" s="2" t="n"/>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>discipline of pre-existing knowledge or skill</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+          <t xml:space="preserve">The expertise discipline in which the person source has acquired their pre-existing knowledge and skills. </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>expertise discipline</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
@@ -2288,11 +2276,15 @@
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>PhD student</t>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
         </is>
       </c>
       <c r="R30" s="2" t="n"/>
@@ -2316,22 +2308,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">early childhood educator </t>
+          <t>doctoral student role</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
@@ -2348,14 +2340,10 @@
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Early childhood educator, Pre-school teacher</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>PhD student</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
@@ -2370,32 +2358,28 @@
       </c>
       <c r="W31" s="2" t="n"/>
       <c r="X31" s="2" t="n"/>
-      <c r="Y31" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2342</t>
-        </is>
-      </c>
+      <c r="Y31" s="2" t="n"/>
       <c r="Z31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">elementary occupation </t>
+          <t xml:space="preserve">early childhood educator </t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
@@ -2412,7 +2396,7 @@
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -2436,7 +2420,7 @@
       <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 9</t>
+          <t>ISCO: 2342</t>
         </is>
       </c>
       <c r="Z32" s="2" t="n"/>
@@ -2444,22 +2428,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>embedded in participants’ community</t>
+          <t xml:space="preserve">elementary occupation </t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E33" s="2" t="n"/>
@@ -2474,8 +2458,16 @@
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
-      <c r="Q33" s="2" t="n"/>
-      <c r="R33" s="2" t="n"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
@@ -2490,23 +2482,27 @@
       </c>
       <c r="W33" s="2" t="n"/>
       <c r="X33" s="2" t="n"/>
-      <c r="Y33" s="2" t="n"/>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 9</t>
+        </is>
+      </c>
       <c r="Z33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>employer</t>
+          <t>embedded in participants’ community</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2548,22 +2544,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">environmental and occupational health and hygiene professional </t>
+          <t>employer</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
@@ -2578,16 +2574,8 @@
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
@@ -2602,34 +2590,28 @@
       </c>
       <c r="W35" s="2" t="n"/>
       <c r="X35" s="2" t="n"/>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2263</t>
-        </is>
-      </c>
+      <c r="Y35" s="2" t="n"/>
       <c r="Z35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">environmental and occupational health inspector and associate </t>
+          <t xml:space="preserve">environmental and occupational health and hygiene professional </t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.
-</t>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E36" s="2" t="n"/>
@@ -2646,7 +2628,7 @@
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -2670,7 +2652,7 @@
       <c r="X36" s="2" t="n"/>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3257</t>
+          <t>ISCO: 2263</t>
         </is>
       </c>
       <c r="Z36" s="2" t="n"/>
@@ -2678,22 +2660,24 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ethnic group membership of person source</t>
+          <t xml:space="preserve">environmental and occupational health inspector and associate </t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+          <t xml:space="preserve">A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E37" s="2" t="n"/>
@@ -2710,10 +2694,14 @@
       <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="n"/>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
@@ -2728,28 +2716,32 @@
       </c>
       <c r="W37" s="2" t="n"/>
       <c r="X37" s="2" t="n"/>
-      <c r="Y37" s="2" t="n"/>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3257</t>
+        </is>
+      </c>
       <c r="Z37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>expertise discipline</t>
+          <t>ethnic group membership of person source</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
@@ -2766,15 +2758,11 @@
       <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+          <t>black, white, Indian, Chinese, Somalian</t>
         </is>
       </c>
       <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
-        </is>
-      </c>
+      <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
           <t>Source</t>
@@ -2794,22 +2782,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>expertise of person source</t>
+          <t>expertise discipline</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+          <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E39" s="2" t="n"/>
@@ -2822,15 +2810,19 @@
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="n"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
       <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="n"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
           <t>Source</t>
@@ -2850,22 +2842,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="E40" s="2" t="n"/>
@@ -2878,7 +2870,11 @@
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n"/>
       <c r="R40" s="2" t="n"/>
@@ -2897,31 +2893,27 @@
       <c r="W40" s="2" t="n"/>
       <c r="X40" s="2" t="n"/>
       <c r="Y40" s="2" t="n"/>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010095</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>female gender</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E41" s="2" t="n"/>
@@ -2936,11 +2928,7 @@
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="n"/>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>female, woman</t>
-        </is>
-      </c>
+      <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="inlineStr">
@@ -2966,22 +2954,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fitness and recreation instructor and programme leader </t>
+          <t>female gender</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+          <t>A gender identity as being female.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sport and fitness worker </t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="E42" s="2" t="n"/>
@@ -2998,14 +2986,10 @@
       <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>female, woman</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
@@ -3020,32 +3004,32 @@
       </c>
       <c r="W42" s="2" t="n"/>
       <c r="X42" s="2" t="n"/>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 3423</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t xml:space="preserve">fitness and recreation instructor and programme leader </t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t xml:space="preserve">sport and fitness worker </t>
         </is>
       </c>
       <c r="E43" s="2" t="n"/>
@@ -3060,8 +3044,16 @@
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="n"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
@@ -3076,28 +3068,32 @@
       </c>
       <c r="W43" s="2" t="n"/>
       <c r="X43" s="2" t="n"/>
-      <c r="Y43" s="2" t="n"/>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3423</t>
+        </is>
+      </c>
       <c r="Z43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>self-identity</t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="E44" s="2" t="n"/>
@@ -3117,7 +3113,7 @@
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="U44" s="2" t="n"/>
@@ -3129,31 +3125,27 @@
       <c r="W44" s="2" t="n"/>
       <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>gender of person source</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>self-identity</t>
         </is>
       </c>
       <c r="E45" s="2" t="n"/>
@@ -3168,16 +3160,12 @@
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
+      <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="U45" s="2" t="n"/>
@@ -3189,27 +3177,31 @@
       <c r="W45" s="2" t="n"/>
       <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="n"/>
-      <c r="Z45" s="2" t="n"/>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">generalist medical practitioner </t>
+          <t>gender of person source</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities. </t>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical doctor </t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E46" s="2" t="n"/>
@@ -3226,14 +3218,10 @@
       <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Primary care physician, family doctor, GP</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
@@ -3248,32 +3236,28 @@
       </c>
       <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2211</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>graduate student role</t>
+          <t xml:space="preserve">generalist medical practitioner </t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities. </t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t xml:space="preserve">medical doctor </t>
         </is>
       </c>
       <c r="E47" s="2" t="n"/>
@@ -3290,10 +3274,14 @@
       <c r="P47" s="2" t="n"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>graduate student</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="n"/>
+          <t>Primary care physician, family doctor, GP</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
@@ -3308,28 +3296,32 @@
       </c>
       <c r="W47" s="2" t="n"/>
       <c r="X47" s="2" t="n"/>
-      <c r="Y47" s="2" t="n"/>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2211</t>
+        </is>
+      </c>
       <c r="Z47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>graduate student role</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E48" s="2" t="n"/>
@@ -3346,14 +3338,10 @@
       <c r="P48" s="2" t="n"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veterinary Technician </t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>graduate student</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
@@ -3368,32 +3356,28 @@
       </c>
       <c r="W48" s="2" t="n"/>
       <c r="X48" s="2" t="n"/>
-      <c r="Y48" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 32</t>
-        </is>
-      </c>
+      <c r="Y48" s="2" t="n"/>
       <c r="Z48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health care assistant </t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E49" s="2" t="n"/>
@@ -3410,7 +3394,7 @@
       <c r="P49" s="2" t="n"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
+          <t xml:space="preserve">Veterinary Technician </t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -3434,7 +3418,7 @@
       <c r="X49" s="2" t="n"/>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 5321</t>
+          <t>ISCO: 32</t>
         </is>
       </c>
       <c r="Z49" s="2" t="n"/>
@@ -3442,22 +3426,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">health care assistant </t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E50" s="2" t="n"/>
@@ -3474,7 +3458,7 @@
       <c r="P50" s="2" t="n"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -3498,7 +3482,7 @@
       <c r="X50" s="2" t="n"/>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 22</t>
+          <t>ISCO: 5321</t>
         </is>
       </c>
       <c r="Z50" s="2" t="n"/>
@@ -3506,22 +3490,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>health status of person source</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E51" s="2" t="n"/>
@@ -3538,10 +3522,14 @@
       <c r="P51" s="2" t="n"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="n"/>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="2" t="inlineStr">
         <is>
@@ -3556,28 +3544,32 @@
       </c>
       <c r="W51" s="2" t="n"/>
       <c r="X51" s="2" t="n"/>
-      <c r="Y51" s="2" t="n"/>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 22</t>
+        </is>
+      </c>
       <c r="Z51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>health status of person source</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. </t>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E52" s="2" t="n"/>
@@ -3594,7 +3586,7 @@
       <c r="P52" s="2" t="n"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
         </is>
       </c>
       <c r="R52" s="2" t="n"/>
@@ -3618,22 +3610,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">home-based personal care worker </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+          <t xml:space="preserve">A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school. </t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
@@ -3650,14 +3642,10 @@
       <c r="P53" s="2" t="n"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="2" t="inlineStr">
         <is>
@@ -3672,32 +3660,28 @@
       </c>
       <c r="W53" s="2" t="n"/>
       <c r="X53" s="2" t="n"/>
-      <c r="Y53" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 5322</t>
-        </is>
-      </c>
+      <c r="Y53" s="2" t="n"/>
       <c r="Z53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t xml:space="preserve">home-based personal care worker </t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
@@ -3712,8 +3696,16 @@
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="n"/>
-      <c r="Q54" s="2" t="n"/>
-      <c r="R54" s="2" t="n"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="inlineStr">
         <is>
@@ -3728,28 +3720,32 @@
       </c>
       <c r="W54" s="2" t="n"/>
       <c r="X54" s="2" t="n"/>
-      <c r="Y54" s="2" t="n"/>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 5322</t>
+        </is>
+      </c>
       <c r="Z54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">information and communications technician </t>
+          <t>informal education student role</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E55" s="2" t="n"/>
@@ -3764,16 +3760,8 @@
       <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="n"/>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="n"/>
       <c r="S55" s="2" t="n"/>
       <c r="T55" s="2" t="inlineStr">
         <is>
@@ -3788,144 +3776,148 @@
       </c>
       <c r="W55" s="2" t="n"/>
       <c r="X55" s="2" t="n"/>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Y55" s="2" t="n"/>
+      <c r="Z55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010066</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">information and communications technician </t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technician and associate professional </t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="n"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="n"/>
+      <c r="X56" s="2" t="n"/>
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>ISCO: 35</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="Z56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>BCIO:010121</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>knowledge or skill</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention. </t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>expertise of person source</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="n"/>
-      <c r="L56" s="3" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="3" t="n"/>
-      <c r="O56" s="3" t="n"/>
-      <c r="P56" s="3" t="n"/>
-      <c r="Q56" s="3" t="inlineStr">
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="n"/>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="3" t="n"/>
+      <c r="Q57" s="3" t="inlineStr">
         <is>
           <t>trained (if unclear whether pre-existing or acquired)</t>
         </is>
       </c>
-      <c r="R56" s="3" t="n"/>
-      <c r="S56" s="3" t="n"/>
-      <c r="T56" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U56" s="3" t="n"/>
-      <c r="V56" s="3" t="inlineStr">
+      <c r="R57" s="3" t="n"/>
+      <c r="S57" s="3" t="n"/>
+      <c r="T57" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="n"/>
+      <c r="V57" s="3" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="W56" s="3" t="n"/>
-      <c r="X56" s="3" t="n"/>
-      <c r="Y56" s="3" t="n"/>
-      <c r="Z56" s="3" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010116</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>language proficiency of person source</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n"/>
-      <c r="N57" s="2" t="n"/>
-      <c r="O57" s="2" t="n"/>
-      <c r="P57" s="2" t="n"/>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>fluent, native</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="n"/>
-      <c r="S57" s="2" t="n"/>
-      <c r="T57" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U57" s="2" t="n"/>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W57" s="2" t="n"/>
-      <c r="X57" s="2" t="n"/>
-      <c r="Y57" s="2" t="n"/>
-      <c r="Z57" s="2" t="n"/>
+      <c r="W57" s="3" t="n"/>
+      <c r="X57" s="3" t="n"/>
+      <c r="Y57" s="3" t="n"/>
+      <c r="Z57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal and related associate professional  </t>
+          <t>language proficiency of person source</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients. </t>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E58" s="2" t="n"/>
@@ -3942,14 +3934,10 @@
       <c r="P58" s="2" t="n"/>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>fluent, native</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="2" t="inlineStr">
         <is>
@@ -3964,32 +3952,28 @@
       </c>
       <c r="W58" s="2" t="n"/>
       <c r="X58" s="2" t="n"/>
-      <c r="Y58" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 3411</t>
-        </is>
-      </c>
+      <c r="Y58" s="2" t="n"/>
       <c r="Z58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal professional </t>
+          <t xml:space="preserve">legal and related associate professional  </t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+          <t xml:space="preserve">A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients. </t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E59" s="2" t="n"/>
@@ -4006,7 +3990,7 @@
       <c r="P59" s="2" t="n"/>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>Lawyer, Judge, Coroner</t>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -4030,7 +4014,7 @@
       <c r="X59" s="2" t="n"/>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 261</t>
+          <t>ISCO: 3411</t>
         </is>
       </c>
       <c r="Z59" s="2" t="n"/>
@@ -4038,22 +4022,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">legal professional </t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">legal, social and cultural professional </t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies. </t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>professional</t>
         </is>
       </c>
       <c r="E60" s="2" t="n"/>
@@ -4068,7 +4052,11 @@
       <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="n"/>
-      <c r="Q60" s="2" t="n"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
+        </is>
+      </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -4090,7 +4078,7 @@
       <c r="X60" s="2" t="n"/>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 26</t>
+          <t>ISCO: 261</t>
         </is>
       </c>
       <c r="Z60" s="2" t="n"/>
@@ -4098,22 +4086,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">librarian, archivist and curator </t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments. </t>
+          <t xml:space="preserve">A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies. </t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E61" s="2" t="n"/>
@@ -4128,11 +4116,7 @@
       <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>Librarian, Archivist,  Curator</t>
-        </is>
-      </c>
+      <c r="Q61" s="2" t="n"/>
       <c r="R61" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -4154,7 +4138,7 @@
       <c r="X61" s="2" t="n"/>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 262</t>
+          <t>ISCO: 26</t>
         </is>
       </c>
       <c r="Z61" s="2" t="n"/>
@@ -4162,17 +4146,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>linguist</t>
+          <t xml:space="preserve">librarian, archivist and curator </t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+          <t xml:space="preserve">A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments. </t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4194,10 +4178,14 @@
       <c r="P62" s="2" t="n"/>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="n"/>
+          <t>Librarian, Archivist,  Curator</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="2" t="inlineStr">
         <is>
@@ -4212,28 +4200,32 @@
       </c>
       <c r="W62" s="2" t="n"/>
       <c r="X62" s="2" t="n"/>
-      <c r="Y62" s="2" t="n"/>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 262</t>
+        </is>
+      </c>
       <c r="Z62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>male gender</t>
+          <t>linguist</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -4250,7 +4242,7 @@
       <c r="P63" s="2" t="n"/>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>male, man</t>
+          <t>Interpretator; other linguist</t>
         </is>
       </c>
       <c r="R63" s="2" t="n"/>
@@ -4269,31 +4261,27 @@
       <c r="W63" s="2" t="n"/>
       <c r="X63" s="2" t="n"/>
       <c r="Y63" s="2" t="n"/>
-      <c r="Z63" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Z63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>male gender</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+          <t>A gender identity as being male.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -4310,14 +4298,10 @@
       <c r="P64" s="2" t="n"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>male, man</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="inlineStr">
         <is>
@@ -4332,32 +4316,32 @@
       </c>
       <c r="W64" s="2" t="n"/>
       <c r="X64" s="2" t="n"/>
-      <c r="Y64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISCO: 1 </t>
-        </is>
-      </c>
-      <c r="Z64" s="2" t="n"/>
+      <c r="Y64" s="2" t="n"/>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>masters student role</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -4374,10 +4358,14 @@
       <c r="P65" s="2" t="n"/>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>MSc student, Masters student</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="n"/>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S65" s="2" t="n"/>
       <c r="T65" s="2" t="inlineStr">
         <is>
@@ -4392,28 +4380,32 @@
       </c>
       <c r="W65" s="2" t="n"/>
       <c r="X65" s="2" t="n"/>
-      <c r="Y65" s="2" t="n"/>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISCO: 1 </t>
+        </is>
+      </c>
       <c r="Z65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical and pharmaceutical technician </t>
+          <t>masters student role</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -4430,14 +4422,10 @@
       <c r="P66" s="2" t="n"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>MSc student, Masters student</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="2" t="inlineStr">
         <is>
@@ -4452,27 +4440,23 @@
       </c>
       <c r="W66" s="2" t="n"/>
       <c r="X66" s="2" t="n"/>
-      <c r="Y66" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 321</t>
-        </is>
-      </c>
+      <c r="Y66" s="2" t="n"/>
       <c r="Z66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical assistant </t>
+          <t xml:space="preserve">medical and pharmaceutical technician </t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional. </t>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4494,7 +4478,7 @@
       <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
@@ -4518,7 +4502,7 @@
       <c r="X67" s="2" t="n"/>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3256</t>
+          <t>ISCO: 321</t>
         </is>
       </c>
       <c r="Z67" s="2" t="n"/>
@@ -4526,22 +4510,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">medical doctor </t>
+          <t xml:space="preserve">medical assistant </t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+          <t xml:space="preserve">A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional. </t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E68" s="2" t="n"/>
@@ -4558,7 +4542,7 @@
       <c r="P68" s="2" t="n"/>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -4582,7 +4566,7 @@
       <c r="X68" s="2" t="n"/>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 221</t>
+          <t>ISCO: 3256</t>
         </is>
       </c>
       <c r="Z68" s="2" t="n"/>
@@ -4590,22 +4574,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">midwifery associate professional </t>
+          <t xml:space="preserve">medical doctor </t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery associate professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E69" s="2" t="n"/>
@@ -4622,7 +4606,7 @@
       <c r="P69" s="2" t="n"/>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>Assistant midwife, Traditional midwife</t>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -4646,7 +4630,7 @@
       <c r="X69" s="2" t="n"/>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3222</t>
+          <t>ISCO: 221</t>
         </is>
       </c>
       <c r="Z69" s="2" t="n"/>
@@ -4654,22 +4638,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">midwifery professional </t>
+          <t xml:space="preserve">midwifery associate professional </t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">nursing and midwifery associate professional </t>
         </is>
       </c>
       <c r="E70" s="2" t="n"/>
@@ -4686,7 +4670,7 @@
       <c r="P70" s="2" t="n"/>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -4710,7 +4694,7 @@
       <c r="X70" s="2" t="n"/>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2222</t>
+          <t>ISCO: 3222</t>
         </is>
       </c>
       <c r="Z70" s="2" t="n"/>
@@ -4718,22 +4702,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010131</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>monetary payment</t>
+          <t xml:space="preserve">midwifery professional </t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>payment of person source</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E71" s="2" t="n"/>
@@ -4750,10 +4734,14 @@
       <c r="P71" s="2" t="n"/>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>paid in cash, vouchers</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="n"/>
+          <t>Midwife</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="n"/>
       <c r="T71" s="2" t="inlineStr">
         <is>
@@ -4768,28 +4756,32 @@
       </c>
       <c r="W71" s="2" t="n"/>
       <c r="X71" s="2" t="n"/>
-      <c r="Y71" s="2" t="n"/>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2222</t>
+        </is>
+      </c>
       <c r="Z71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010131</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">music teacher </t>
+          <t>monetary payment</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -4806,14 +4798,10 @@
       <c r="P72" s="2" t="n"/>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>paid in cash, vouchers</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="inlineStr">
         <is>
@@ -4828,32 +4816,28 @@
       </c>
       <c r="W72" s="2" t="n"/>
       <c r="X72" s="2" t="n"/>
-      <c r="Y72" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2354</t>
-        </is>
-      </c>
+      <c r="Y72" s="2" t="n"/>
       <c r="Z72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>non-monetary payment</t>
+          <t xml:space="preserve">music teacher </t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>payment of person source</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -4870,10 +4854,14 @@
       <c r="P73" s="2" t="n"/>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>course credit</t>
-        </is>
-      </c>
-      <c r="R73" s="2" t="n"/>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S73" s="2" t="n"/>
       <c r="T73" s="2" t="inlineStr">
         <is>
@@ -4888,28 +4876,32 @@
       </c>
       <c r="W73" s="2" t="n"/>
       <c r="X73" s="2" t="n"/>
-      <c r="Y73" s="2" t="n"/>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2354</t>
+        </is>
+      </c>
       <c r="Z73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>number of people delivering intervention to each participant</t>
+          <t>non-monetary payment</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -4921,14 +4913,14 @@
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="N74" s="2" t="n"/>
       <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="n"/>
-      <c r="Q74" s="2" t="n"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>course credit</t>
+        </is>
+      </c>
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="inlineStr">
@@ -4950,22 +4942,22 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery associate professional </t>
+          <t>number of people delivering intervention to each participant</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -4977,19 +4969,15 @@
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
-      <c r="N75" s="2" t="n"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="n"/>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q75" s="2" t="n"/>
+      <c r="R75" s="2" t="n"/>
       <c r="S75" s="2" t="n"/>
       <c r="T75" s="2" t="inlineStr">
         <is>
@@ -5004,32 +4992,28 @@
       </c>
       <c r="W75" s="2" t="n"/>
       <c r="X75" s="2" t="n"/>
-      <c r="Y75" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 322</t>
-        </is>
-      </c>
+      <c r="Y75" s="2" t="n"/>
       <c r="Z75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery professional </t>
+          <t xml:space="preserve">nursing and midwifery associate professional </t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>health professional</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -5044,7 +5028,11 @@
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="n"/>
-      <c r="Q76" s="2" t="n"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
+        </is>
+      </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -5066,7 +5054,7 @@
       <c r="X76" s="2" t="n"/>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 222</t>
+          <t>ISCO: 322</t>
         </is>
       </c>
       <c r="Z76" s="2" t="n"/>
@@ -5074,22 +5062,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing associate professional </t>
+          <t xml:space="preserve">nursing and midwifery professional </t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing and midwifery associate professional </t>
+          <t>health professional</t>
         </is>
       </c>
       <c r="E77" s="2" t="n"/>
@@ -5104,11 +5092,7 @@
       <c r="N77" s="2" t="n"/>
       <c r="O77" s="2" t="n"/>
       <c r="P77" s="2" t="n"/>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
-        </is>
-      </c>
+      <c r="Q77" s="2" t="n"/>
       <c r="R77" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -5130,7 +5114,7 @@
       <c r="X77" s="2" t="n"/>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3221</t>
+          <t>ISCO: 222</t>
         </is>
       </c>
       <c r="Z77" s="2" t="n"/>
@@ -5138,22 +5122,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">nursing professional </t>
+          <t xml:space="preserve">nursing associate professional </t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health. </t>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">nursing and midwifery associate professional </t>
         </is>
       </c>
       <c r="E78" s="2" t="n"/>
@@ -5170,7 +5154,7 @@
       <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
@@ -5194,7 +5178,7 @@
       <c r="X78" s="2" t="n"/>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2221</t>
+          <t>ISCO: 3221</t>
         </is>
       </c>
       <c r="Z78" s="2" t="n"/>
@@ -5202,22 +5186,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">nursing professional </t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+          <t xml:space="preserve">A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health. </t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>personal role of source</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E79" s="2" t="n"/>
@@ -5234,10 +5218,14 @@
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>Interventionist, facilitator, study staff</t>
-        </is>
-      </c>
-      <c r="R79" s="2" t="n"/>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S79" s="2" t="n"/>
       <c r="T79" s="2" t="inlineStr">
         <is>
@@ -5252,28 +5240,32 @@
       </c>
       <c r="W79" s="2" t="n"/>
       <c r="X79" s="2" t="n"/>
-      <c r="Y79" s="2" t="n"/>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2221</t>
+        </is>
+      </c>
       <c r="Z79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">optometrist and ophthalmic optician </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system. </t>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>personal role of source</t>
         </is>
       </c>
       <c r="E80" s="2" t="n"/>
@@ -5290,14 +5282,10 @@
       <c r="P80" s="2" t="n"/>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
-        </is>
-      </c>
-      <c r="R80" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>Interventionist, facilitator, study staff</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="n"/>
       <c r="S80" s="2" t="n"/>
       <c r="T80" s="2" t="inlineStr">
         <is>
@@ -5312,32 +5300,28 @@
       </c>
       <c r="W80" s="2" t="n"/>
       <c r="X80" s="2" t="n"/>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2267</t>
-        </is>
-      </c>
+      <c r="Y80" s="2" t="n"/>
       <c r="Z80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>organisation source</t>
+          <t xml:space="preserve">optometrist and ophthalmic optician </t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+          <t xml:space="preserve">A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system. </t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">organization </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E81" s="2" t="n"/>
@@ -5351,13 +5335,17 @@
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="n"/>
       <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>(organisation and 'has characteristic' some 'organisational source role')</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="n"/>
-      <c r="R81" s="2" t="n"/>
+      <c r="P81" s="2" t="n"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S81" s="2" t="n"/>
       <c r="T81" s="2" t="inlineStr">
         <is>
@@ -5372,32 +5360,32 @@
       </c>
       <c r="W81" s="2" t="n"/>
       <c r="X81" s="2" t="n"/>
-      <c r="Y81" s="2" t="n"/>
-      <c r="Z81" s="2" t="inlineStr">
-        <is>
-          <t>BG; PS</t>
-        </is>
-      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2267</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>organisational source role</t>
+          <t>organisation source</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>behaviour change intervention source</t>
+          <t xml:space="preserve">organization </t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -5411,7 +5399,11 @@
       <c r="M82" s="2" t="n"/>
       <c r="N82" s="2" t="n"/>
       <c r="O82" s="2" t="n"/>
-      <c r="P82" s="2" t="n"/>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>(organisation and 'has characteristic' some 'organisational source role')</t>
+        </is>
+      </c>
       <c r="Q82" s="2" t="n"/>
       <c r="R82" s="2" t="n"/>
       <c r="S82" s="2" t="n"/>
@@ -5429,125 +5421,125 @@
       <c r="W82" s="2" t="n"/>
       <c r="X82" s="2" t="n"/>
       <c r="Y82" s="2" t="n"/>
-      <c r="Z82" s="2" t="n"/>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>BG; PS</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010138</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>A BCI source role that is borne by an organisation.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="n"/>
+      <c r="M83" s="2" t="n"/>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="n"/>
+      <c r="P83" s="2" t="n"/>
+      <c r="Q83" s="2" t="n"/>
+      <c r="R83" s="2" t="n"/>
+      <c r="S83" s="2" t="n"/>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="n"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="n"/>
+      <c r="X83" s="2" t="n"/>
+      <c r="Y83" s="2" t="n"/>
+      <c r="Z83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>OBI:0000245</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t xml:space="preserve">organization </t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t xml:space="preserve">An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members. </t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>organisational source role</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010113</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>other gender</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female. </t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>gender of person source</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
-      <c r="L84" s="2" t="n"/>
-      <c r="M84" s="2" t="n"/>
-      <c r="N84" s="2" t="n"/>
-      <c r="O84" s="2" t="n"/>
-      <c r="P84" s="2" t="n"/>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>non-binary, transexual</t>
-        </is>
-      </c>
-      <c r="R84" s="2" t="n"/>
-      <c r="S84" s="2" t="n"/>
-      <c r="T84" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U84" s="2" t="n"/>
-      <c r="V84" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W84" s="2" t="n"/>
-      <c r="X84" s="2" t="n"/>
-      <c r="Y84" s="2" t="n"/>
-      <c r="Z84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">paramedical practitioner </t>
+          <t>other gender</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+          <t xml:space="preserve">A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female. </t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>gender of person source</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -5564,14 +5556,10 @@
       <c r="P85" s="2" t="n"/>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
-        </is>
-      </c>
-      <c r="R85" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>non-binary, transexual</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="n"/>
       <c r="S85" s="2" t="n"/>
       <c r="T85" s="2" t="inlineStr">
         <is>
@@ -5586,32 +5574,28 @@
       </c>
       <c r="W85" s="2" t="n"/>
       <c r="X85" s="2" t="n"/>
-      <c r="Y85" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 224</t>
-        </is>
-      </c>
+      <c r="Y85" s="2" t="n"/>
       <c r="Z85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>parent or guardian</t>
+          <t xml:space="preserve">paramedical practitioner </t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -5628,10 +5612,14 @@
       <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
-        </is>
-      </c>
-      <c r="R86" s="2" t="n"/>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S86" s="2" t="n"/>
       <c r="T86" s="2" t="inlineStr">
         <is>
@@ -5646,36 +5634,36 @@
       </c>
       <c r="W86" s="2" t="n"/>
       <c r="X86" s="2" t="n"/>
-      <c r="Y86" s="2" t="n"/>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 224</t>
+        </is>
+      </c>
       <c r="Z86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>payment of person source</t>
+          <t>parent or guardian</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
@@ -5686,7 +5674,11 @@
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="2" t="n"/>
       <c r="P87" s="2" t="n"/>
-      <c r="Q87" s="2" t="n"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>mother, father, step-mother, step-father, guardian</t>
+        </is>
+      </c>
       <c r="R87" s="2" t="n"/>
       <c r="S87" s="2" t="n"/>
       <c r="T87" s="2" t="inlineStr">
@@ -5708,26 +5700,30 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010130</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>peer</t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc. </t>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
@@ -5758,121 +5754,113 @@
       <c r="Z88" s="2" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010104</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>peer</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc. </t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="2" t="n"/>
+      <c r="M89" s="2" t="n"/>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="n"/>
+      <c r="P89" s="2" t="n"/>
+      <c r="Q89" s="2" t="n"/>
+      <c r="R89" s="2" t="n"/>
+      <c r="S89" s="2" t="n"/>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="n"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="n"/>
+      <c r="X89" s="2" t="n"/>
+      <c r="Y89" s="2" t="n"/>
+      <c r="Z89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>MF:0000016</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t xml:space="preserve">An extended organism that is a member of the species Homo sapiens. </t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>extended organism</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>AW</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>BCIO:010002</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
-      <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="n"/>
-      <c r="J90" s="2" t="n"/>
-      <c r="K90" s="2" t="n"/>
-      <c r="L90" s="2" t="n"/>
-      <c r="M90" s="2" t="n"/>
-      <c r="N90" s="2" t="n"/>
-      <c r="O90" s="2" t="n"/>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>(person and 'has characteristic' some 'person source role')</t>
-        </is>
-      </c>
-      <c r="Q90" s="2" t="n"/>
-      <c r="R90" s="2" t="n"/>
-      <c r="S90" s="2" t="n"/>
-      <c r="T90" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U90" s="2" t="n"/>
-      <c r="V90" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W90" s="2" t="n"/>
-      <c r="X90" s="2" t="n"/>
-      <c r="Y90" s="2" t="n"/>
-      <c r="Z90" s="2" t="inlineStr">
-        <is>
-          <t>BG</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>person source role</t>
+          <t>person source</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>behaviour change intervention source</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E91" s="2" t="n"/>
@@ -5886,7 +5874,11 @@
       <c r="M91" s="2" t="n"/>
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="2" t="n"/>
-      <c r="P91" s="2" t="n"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>(person and 'has characteristic' some 'person source role')</t>
+        </is>
+      </c>
       <c r="Q91" s="2" t="n"/>
       <c r="R91" s="2" t="n"/>
       <c r="S91" s="2" t="n"/>
@@ -5904,27 +5896,31 @@
       <c r="W91" s="2" t="n"/>
       <c r="X91" s="2" t="n"/>
       <c r="Y91" s="2" t="n"/>
-      <c r="Z91" s="2" t="n"/>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t>person source role</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t>behaviour change intervention source</t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
@@ -5939,16 +5935,8 @@
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="2" t="n"/>
       <c r="P92" s="2" t="n"/>
-      <c r="Q92" s="2" t="inlineStr">
-        <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
-      <c r="R92" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q92" s="2" t="n"/>
+      <c r="R92" s="2" t="n"/>
       <c r="S92" s="2" t="n"/>
       <c r="T92" s="2" t="inlineStr">
         <is>
@@ -5963,32 +5951,28 @@
       </c>
       <c r="W92" s="2" t="n"/>
       <c r="X92" s="2" t="n"/>
-      <c r="Y92" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 53</t>
-        </is>
-      </c>
+      <c r="Y92" s="2" t="n"/>
       <c r="Z92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>personal role of source</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A role that inheres in a person source. </t>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E93" s="2" t="n"/>
@@ -6003,8 +5987,16 @@
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="2" t="n"/>
       <c r="P93" s="2" t="n"/>
-      <c r="Q93" s="2" t="n"/>
-      <c r="R93" s="2" t="n"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>Personal carer</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S93" s="2" t="n"/>
       <c r="T93" s="2" t="inlineStr">
         <is>
@@ -6019,92 +6011,84 @@
       </c>
       <c r="W93" s="2" t="n"/>
       <c r="X93" s="2" t="n"/>
-      <c r="Y93" s="2" t="n"/>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 53</t>
+        </is>
+      </c>
       <c r="Z93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>BCIO:006081</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal services worker </t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="n"/>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="n"/>
-      <c r="L94" s="2" t="n"/>
-      <c r="M94" s="2" t="n"/>
-      <c r="N94" s="2" t="n"/>
-      <c r="O94" s="2" t="n"/>
-      <c r="P94" s="2" t="n"/>
-      <c r="Q94" s="2" t="inlineStr">
-        <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
-      <c r="R94" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
-      <c r="S94" s="2" t="n"/>
-      <c r="T94" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U94" s="2" t="n"/>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="W94" s="2" t="n"/>
-      <c r="X94" s="2" t="n"/>
-      <c r="Y94" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 51</t>
-        </is>
-      </c>
-      <c r="Z94" s="2" t="n"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr"/>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>pharmacist</t>
+          <t>personal role of source</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+          <t xml:space="preserve">A role that inheres in a person source. </t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>role</t>
         </is>
       </c>
       <c r="E95" s="2" t="n"/>
@@ -6119,16 +6103,8 @@
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="2" t="n"/>
       <c r="P95" s="2" t="n"/>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
-        </is>
-      </c>
-      <c r="R95" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q95" s="2" t="n"/>
+      <c r="R95" s="2" t="n"/>
       <c r="S95" s="2" t="n"/>
       <c r="T95" s="2" t="inlineStr">
         <is>
@@ -6143,32 +6119,28 @@
       </c>
       <c r="W95" s="2" t="n"/>
       <c r="X95" s="2" t="n"/>
-      <c r="Y95" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2262</t>
-        </is>
-      </c>
+      <c r="Y95" s="2" t="n"/>
       <c r="Z95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t xml:space="preserve">personal services worker </t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
@@ -6185,7 +6157,7 @@
       <c r="P96" s="2" t="n"/>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr">
@@ -6209,7 +6181,7 @@
       <c r="X96" s="2" t="n"/>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2264</t>
+          <t>ISCO: 51</t>
         </is>
       </c>
       <c r="Z96" s="2" t="n"/>
@@ -6217,22 +6189,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">physiotherapy technician and assistant </t>
+          <t>pharmacist</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E97" s="2" t="n"/>
@@ -6249,7 +6221,7 @@
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
         </is>
       </c>
       <c r="R97" s="2" t="inlineStr">
@@ -6273,7 +6245,7 @@
       <c r="X97" s="2" t="n"/>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3255</t>
+          <t>ISCO: 2262</t>
         </is>
       </c>
       <c r="Z97" s="2" t="n"/>
@@ -6281,22 +6253,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">plant and machine operator </t>
+          <t>physiotherapist</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment. </t>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E98" s="2" t="n"/>
@@ -6313,7 +6285,7 @@
       <c r="P98" s="2" t="n"/>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr">
@@ -6337,7 +6309,7 @@
       <c r="X98" s="2" t="n"/>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 8</t>
+          <t>ISCO: 2264</t>
         </is>
       </c>
       <c r="Z98" s="2" t="n"/>
@@ -6345,22 +6317,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>pre-existing expertise</t>
+          <t xml:space="preserve">physiotherapy technician and assistant </t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>An expertise of person source that is already possessed by the source which allows them to deliver the intervention, including educational level and qualifications.</t>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>expertise of person source</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E99" s="2" t="n"/>
@@ -6377,10 +6349,14 @@
       <c r="P99" s="2" t="n"/>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
-        </is>
-      </c>
-      <c r="R99" s="2" t="n"/>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S99" s="2" t="n"/>
       <c r="T99" s="2" t="inlineStr">
         <is>
@@ -6395,28 +6371,32 @@
       </c>
       <c r="W99" s="2" t="n"/>
       <c r="X99" s="2" t="n"/>
-      <c r="Y99" s="2" t="n"/>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3255</t>
+        </is>
+      </c>
       <c r="Z99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary school teacher </t>
+          <t xml:space="preserve">plant and machine operator </t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+          <t xml:space="preserve">An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment. </t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E100" s="2" t="n"/>
@@ -6431,7 +6411,11 @@
       <c r="N100" s="2" t="n"/>
       <c r="O100" s="2" t="n"/>
       <c r="P100" s="2" t="n"/>
-      <c r="Q100" s="2" t="n"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
+        </is>
+      </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -6453,7 +6437,7 @@
       <c r="X100" s="2" t="n"/>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2341</t>
+          <t>ISCO: 8</t>
         </is>
       </c>
       <c r="Z100" s="2" t="n"/>
@@ -6461,22 +6445,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>pre-existing expertise</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+          <t>An expertise of person source that is already possessed by the source which allows them to deliver the intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="E101" s="2" t="n"/>
@@ -6491,12 +6475,12 @@
       <c r="N101" s="2" t="n"/>
       <c r="O101" s="2" t="n"/>
       <c r="P101" s="2" t="n"/>
-      <c r="Q101" s="2" t="n"/>
-      <c r="R101" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="n"/>
       <c r="S101" s="2" t="n"/>
       <c r="T101" s="2" t="inlineStr">
         <is>
@@ -6511,32 +6495,28 @@
       </c>
       <c r="W101" s="2" t="n"/>
       <c r="X101" s="2" t="n"/>
-      <c r="Y101" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2</t>
-        </is>
-      </c>
+      <c r="Y101" s="2" t="n"/>
       <c r="Z101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">protective services worker </t>
+          <t xml:space="preserve">primary school teacher </t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E102" s="2" t="n"/>
@@ -6551,11 +6531,7 @@
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="2" t="n"/>
       <c r="P102" s="2" t="n"/>
-      <c r="Q102" s="2" t="inlineStr">
-        <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
+      <c r="Q102" s="2" t="n"/>
       <c r="R102" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -6577,7 +6553,7 @@
       <c r="X102" s="2" t="n"/>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 54</t>
+          <t>ISCO: 2341</t>
         </is>
       </c>
       <c r="Z102" s="2" t="n"/>
@@ -6585,22 +6561,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>psychological influence on intervention delivery of person source</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E103" s="2" t="n"/>
@@ -6616,7 +6592,11 @@
       <c r="O103" s="2" t="n"/>
       <c r="P103" s="2" t="n"/>
       <c r="Q103" s="2" t="n"/>
-      <c r="R103" s="2" t="n"/>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S103" s="2" t="n"/>
       <c r="T103" s="2" t="inlineStr">
         <is>
@@ -6631,28 +6611,32 @@
       </c>
       <c r="W103" s="2" t="n"/>
       <c r="X103" s="2" t="n"/>
-      <c r="Y103" s="2" t="n"/>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2</t>
+        </is>
+      </c>
       <c r="Z103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>psychologist</t>
+          <t xml:space="preserve">protective services worker </t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social professional </t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E104" s="2" t="n"/>
@@ -6669,7 +6653,7 @@
       <c r="P104" s="2" t="n"/>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr">
@@ -6693,7 +6677,7 @@
       <c r="X104" s="2" t="n"/>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2634</t>
+          <t>ISCO: 54</t>
         </is>
       </c>
       <c r="Z104" s="2" t="n"/>
@@ -6701,22 +6685,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>relatedness between person source and the target population</t>
+          <t>psychological influence on intervention delivery of person source</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>personal role of source</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E105" s="2" t="n"/>
@@ -6753,22 +6737,22 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">religious associate professional </t>
+          <t>psychologist</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t xml:space="preserve">social professional </t>
         </is>
       </c>
       <c r="E106" s="2" t="n"/>
@@ -6785,7 +6769,7 @@
       <c r="P106" s="2" t="n"/>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr">
@@ -6809,7 +6793,7 @@
       <c r="X106" s="2" t="n"/>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3413</t>
+          <t>ISCO: 2634</t>
         </is>
       </c>
       <c r="Z106" s="2" t="n"/>
@@ -6817,22 +6801,22 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>religious group membership of person source</t>
+          <t>relatedness between person source and the target population</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion. </t>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>personal role of source</t>
         </is>
       </c>
       <c r="E107" s="2" t="n"/>
@@ -6847,11 +6831,7 @@
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="2" t="n"/>
       <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
-        </is>
-      </c>
+      <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
       <c r="T107" s="2" t="inlineStr">
@@ -6873,22 +6853,22 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">religious professional </t>
+          <t xml:space="preserve">religious associate professional </t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E108" s="2" t="n"/>
@@ -6905,7 +6885,7 @@
       <c r="P108" s="2" t="n"/>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr">
@@ -6929,7 +6909,7 @@
       <c r="X108" s="2" t="n"/>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2636</t>
+          <t>ISCO: 3413</t>
         </is>
       </c>
       <c r="Z108" s="2" t="n"/>
@@ -6937,22 +6917,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>researcher role</t>
+          <t>religious group membership of person source</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study.</t>
+          <t xml:space="preserve">A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion. </t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
@@ -6969,7 +6949,7 @@
       <c r="P109" s="2" t="n"/>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>researcher, research assistant, investigator</t>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
         </is>
       </c>
       <c r="R109" s="2" t="n"/>
@@ -6993,22 +6973,22 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>role model for a person</t>
+          <t xml:space="preserve">religious professional </t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E110" s="2" t="n"/>
@@ -7023,13 +7003,17 @@
       <c r="N110" s="2" t="n"/>
       <c r="O110" s="2" t="n"/>
       <c r="P110" s="2" t="n"/>
-      <c r="Q110" s="2" t="n"/>
-      <c r="R110" s="2" t="n"/>
-      <c r="S110" s="2" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
-        </is>
-      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="n"/>
       <c r="T110" s="2" t="inlineStr">
         <is>
           <t>Source</t>
@@ -7043,28 +7027,32 @@
       </c>
       <c r="W110" s="2" t="n"/>
       <c r="X110" s="2" t="n"/>
-      <c r="Y110" s="2" t="n"/>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2636</t>
+        </is>
+      </c>
       <c r="Z110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales worker </t>
+          <t>researcher role</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets. </t>
+          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
@@ -7081,14 +7069,10 @@
       <c r="P111" s="2" t="n"/>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
-      <c r="R111" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>researcher, research assistant, investigator</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="n"/>
       <c r="S111" s="2" t="n"/>
       <c r="T111" s="2" t="inlineStr">
         <is>
@@ -7103,32 +7087,28 @@
       </c>
       <c r="W111" s="2" t="n"/>
       <c r="X111" s="2" t="n"/>
-      <c r="Y111" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 52</t>
-        </is>
-      </c>
+      <c r="Y111" s="2" t="n"/>
       <c r="Z111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>school student role</t>
+          <t>role model for a person</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>person</t>
         </is>
       </c>
       <c r="E112" s="2" t="n"/>
@@ -7145,7 +7125,11 @@
       <c r="P112" s="2" t="n"/>
       <c r="Q112" s="2" t="n"/>
       <c r="R112" s="2" t="n"/>
-      <c r="S112" s="2" t="n"/>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+        </is>
+      </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
           <t>Source</t>
@@ -7165,22 +7149,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">science and engineering professional </t>
+          <t xml:space="preserve">sales worker </t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+          <t xml:space="preserve">A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets. </t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="E113" s="2" t="n"/>
@@ -7197,7 +7181,7 @@
       <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
@@ -7221,7 +7205,7 @@
       <c r="X113" s="2" t="n"/>
       <c r="Y113" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 21</t>
+          <t>ISCO: 52</t>
         </is>
       </c>
       <c r="Z113" s="2" t="n"/>
@@ -7229,22 +7213,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">secondary education teacher </t>
+          <t>school student role</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E114" s="2" t="n"/>
@@ -7259,16 +7243,8 @@
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="2" t="n"/>
       <c r="P114" s="2" t="n"/>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>Secondary school teacher, High school teacher</t>
-        </is>
-      </c>
-      <c r="R114" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q114" s="2" t="n"/>
+      <c r="R114" s="2" t="n"/>
       <c r="S114" s="2" t="n"/>
       <c r="T114" s="2" t="inlineStr">
         <is>
@@ -7283,32 +7259,28 @@
       </c>
       <c r="W114" s="2" t="n"/>
       <c r="X114" s="2" t="n"/>
-      <c r="Y114" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 233</t>
-        </is>
-      </c>
+      <c r="Y114" s="2" t="n"/>
       <c r="Z114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">services and sales worker </t>
+          <t xml:space="preserve">science and engineering professional </t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
@@ -7323,7 +7295,11 @@
       <c r="N115" s="2" t="n"/>
       <c r="O115" s="2" t="n"/>
       <c r="P115" s="2" t="n"/>
-      <c r="Q115" s="2" t="n"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
+        </is>
+      </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -7345,7 +7321,7 @@
       <c r="X115" s="2" t="n"/>
       <c r="Y115" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 5</t>
+          <t>ISCO: 21</t>
         </is>
       </c>
       <c r="Z115" s="2" t="n"/>
@@ -7353,22 +7329,22 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>sibling relationship</t>
+          <t xml:space="preserve">secondary education teacher </t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
@@ -7385,10 +7361,14 @@
       <c r="P116" s="2" t="n"/>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>brother, sister, step-brother, step-sister</t>
-        </is>
-      </c>
-      <c r="R116" s="2" t="n"/>
+          <t>Secondary school teacher, High school teacher</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S116" s="2" t="n"/>
       <c r="T116" s="2" t="inlineStr">
         <is>
@@ -7403,23 +7383,27 @@
       </c>
       <c r="W116" s="2" t="n"/>
       <c r="X116" s="2" t="n"/>
-      <c r="Y116" s="2" t="n"/>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 233</t>
+        </is>
+      </c>
       <c r="Z116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">skilled agricultural, forestry and fishery worker </t>
+          <t xml:space="preserve">services and sales worker </t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -7439,11 +7423,7 @@
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="2" t="n"/>
       <c r="P117" s="2" t="n"/>
-      <c r="Q117" s="2" t="inlineStr">
-        <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
+      <c r="Q117" s="2" t="n"/>
       <c r="R117" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -7465,7 +7445,7 @@
       <c r="X117" s="2" t="n"/>
       <c r="Y117" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 6</t>
+          <t>ISCO: 5</t>
         </is>
       </c>
       <c r="Z117" s="2" t="n"/>
@@ -7473,22 +7453,22 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social professional </t>
+          <t>sibling relationship</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legal, social and cultural professional </t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E118" s="2" t="n"/>
@@ -7505,14 +7485,10 @@
       <c r="P118" s="2" t="n"/>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
-        </is>
-      </c>
-      <c r="R118" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>brother, sister, step-brother, step-sister</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="n"/>
       <c r="S118" s="2" t="n"/>
       <c r="T118" s="2" t="inlineStr">
         <is>
@@ -7527,32 +7503,28 @@
       </c>
       <c r="W118" s="2" t="n"/>
       <c r="X118" s="2" t="n"/>
-      <c r="Y118" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 263</t>
-        </is>
-      </c>
+      <c r="Y118" s="2" t="n"/>
       <c r="Z118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social work and counselling professional </t>
+          <t xml:space="preserve">skilled agricultural, forestry and fishery worker </t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems. </t>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social professional </t>
+          <t>occupational role of source</t>
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
@@ -7569,7 +7541,7 @@
       <c r="P119" s="2" t="n"/>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
@@ -7593,7 +7565,7 @@
       <c r="X119" s="2" t="n"/>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 2635</t>
+          <t>ISCO: 6</t>
         </is>
       </c>
       <c r="Z119" s="2" t="n"/>
@@ -7601,22 +7573,22 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">social work associate professional </t>
+          <t xml:space="preserve">social professional </t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t xml:space="preserve">legal, social and cultural professional </t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
@@ -7633,7 +7605,7 @@
       <c r="P120" s="2" t="n"/>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
@@ -7657,7 +7629,7 @@
       <c r="X120" s="2" t="n"/>
       <c r="Y120" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3412</t>
+          <t>ISCO: 263</t>
         </is>
       </c>
       <c r="Z120" s="2" t="n"/>
@@ -7665,22 +7637,22 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t xml:space="preserve">social work and counselling professional </t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A social or demographic characteristic of a human being who is the bearer of a person source role. </t>
+          <t xml:space="preserve">A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems. </t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t xml:space="preserve">social professional </t>
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
@@ -7693,14 +7665,18 @@
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="2" t="n"/>
       <c r="N121" s="2" t="n"/>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="O121" s="2" t="n"/>
       <c r="P121" s="2" t="n"/>
-      <c r="Q121" s="2" t="n"/>
-      <c r="R121" s="2" t="n"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S121" s="2" t="n"/>
       <c r="T121" s="2" t="inlineStr">
         <is>
@@ -7715,28 +7691,32 @@
       </c>
       <c r="W121" s="2" t="n"/>
       <c r="X121" s="2" t="n"/>
-      <c r="Y121" s="2" t="n"/>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 2635</t>
+        </is>
+      </c>
       <c r="Z121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>source involved in co-production of intervention</t>
+          <t xml:space="preserve">social work associate professional </t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>source involved in development of intervention</t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E122" s="2" t="n"/>
@@ -7751,8 +7731,16 @@
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="2" t="n"/>
       <c r="P122" s="2" t="n"/>
-      <c r="Q122" s="2" t="n"/>
-      <c r="R122" s="2" t="n"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S122" s="2" t="n"/>
       <c r="T122" s="2" t="inlineStr">
         <is>
@@ -7767,28 +7755,32 @@
       </c>
       <c r="W122" s="2" t="n"/>
       <c r="X122" s="2" t="n"/>
-      <c r="Y122" s="2" t="n"/>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3412</t>
+        </is>
+      </c>
       <c r="Z122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>source involved in development of intervention</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A BCI source that is involved in the development of intervention content. </t>
+          <t xml:space="preserve">A social or demographic characteristic of a human being who is the bearer of a person source role. </t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>behaviour change intervention source</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E123" s="2" t="n"/>
@@ -7801,7 +7793,11 @@
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="2" t="n"/>
       <c r="N123" s="2" t="n"/>
-      <c r="O123" s="2" t="n"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="P123" s="2" t="n"/>
       <c r="Q123" s="2" t="n"/>
       <c r="R123" s="2" t="n"/>
@@ -7825,22 +7821,22 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>source role related to intervention</t>
+          <t>source involved in co-production of intervention</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention. </t>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>behaviour change intervention source</t>
+          <t>source involved in development of intervention</t>
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
@@ -7877,22 +7873,22 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">special needs teacher </t>
+          <t>source involved in development of intervention</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A teaching professional that teaches children, young persons or adults with physical or intellectual special needs. </t>
+          <t xml:space="preserve">A BCI source that is involved in the development of intervention content. </t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>behaviour change intervention source</t>
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
@@ -7907,16 +7903,8 @@
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="2" t="n"/>
       <c r="P125" s="2" t="n"/>
-      <c r="Q125" s="2" t="inlineStr">
-        <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
-        </is>
-      </c>
-      <c r="R125" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q125" s="2" t="n"/>
+      <c r="R125" s="2" t="n"/>
       <c r="S125" s="2" t="n"/>
       <c r="T125" s="2" t="inlineStr">
         <is>
@@ -7931,32 +7919,28 @@
       </c>
       <c r="W125" s="2" t="n"/>
       <c r="X125" s="2" t="n"/>
-      <c r="Y125" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2352</t>
-        </is>
-      </c>
+      <c r="Y125" s="2" t="n"/>
       <c r="Z125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">specialist medical practitioner </t>
+          <t>source role related to intervention</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization. </t>
+          <t xml:space="preserve">A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention. </t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>medical doctor</t>
+          <t>behaviour change intervention source</t>
         </is>
       </c>
       <c r="E126" s="2" t="n"/>
@@ -7971,16 +7955,8 @@
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="2" t="n"/>
       <c r="P126" s="2" t="n"/>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
-        </is>
-      </c>
-      <c r="R126" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q126" s="2" t="n"/>
+      <c r="R126" s="2" t="n"/>
       <c r="S126" s="2" t="n"/>
       <c r="T126" s="2" t="inlineStr">
         <is>
@@ -7995,32 +7971,28 @@
       </c>
       <c r="W126" s="2" t="n"/>
       <c r="X126" s="2" t="n"/>
-      <c r="Y126" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 2212</t>
-        </is>
-      </c>
+      <c r="Y126" s="2" t="n"/>
       <c r="Z126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sport and fitness worker </t>
+          <t xml:space="preserve">special needs teacher </t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+          <t xml:space="preserve">A teaching professional that teaches children, young persons or adults with physical or intellectual special needs. </t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="E127" s="2" t="n"/>
@@ -8037,7 +8009,7 @@
       <c r="P127" s="2" t="n"/>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
@@ -8061,7 +8033,7 @@
       <c r="X127" s="2" t="n"/>
       <c r="Y127" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 342</t>
+          <t>ISCO: 2352</t>
         </is>
       </c>
       <c r="Z127" s="2" t="n"/>
@@ -8069,22 +8041,22 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sports coach, instructor and official </t>
+          <t xml:space="preserve">specialist medical practitioner </t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+          <t xml:space="preserve">A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization. </t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sport and fitness worker </t>
+          <t>medical doctor</t>
         </is>
       </c>
       <c r="E128" s="2" t="n"/>
@@ -8101,7 +8073,7 @@
       <c r="P128" s="2" t="n"/>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
@@ -8125,7 +8097,7 @@
       <c r="X128" s="2" t="n"/>
       <c r="Y128" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3422</t>
+          <t>ISCO: 2212</t>
         </is>
       </c>
       <c r="Z128" s="2" t="n"/>
@@ -8133,22 +8105,22 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>spouse or partner</t>
+          <t xml:space="preserve">sport and fitness worker </t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="E129" s="2" t="n"/>
@@ -8165,10 +8137,14 @@
       <c r="P129" s="2" t="n"/>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
-        </is>
-      </c>
-      <c r="R129" s="2" t="n"/>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S129" s="2" t="n"/>
       <c r="T129" s="2" t="inlineStr">
         <is>
@@ -8183,28 +8159,32 @@
       </c>
       <c r="W129" s="2" t="n"/>
       <c r="X129" s="2" t="n"/>
-      <c r="Y129" s="2" t="n"/>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 342</t>
+        </is>
+      </c>
       <c r="Z129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t xml:space="preserve">sports coach, instructor and official </t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t xml:space="preserve">sport and fitness worker </t>
         </is>
       </c>
       <c r="E130" s="2" t="n"/>
@@ -8219,8 +8199,16 @@
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="2" t="n"/>
       <c r="P130" s="2" t="n"/>
-      <c r="Q130" s="2" t="n"/>
-      <c r="R130" s="2" t="n"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S130" s="2" t="n"/>
       <c r="T130" s="2" t="inlineStr">
         <is>
@@ -8235,40 +8223,36 @@
       </c>
       <c r="W130" s="2" t="n"/>
       <c r="X130" s="2" t="n"/>
-      <c r="Y130" s="2" t="n"/>
-      <c r="Z130" s="2" t="inlineStr">
-        <is>
-          <t>AW</t>
-        </is>
-      </c>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 3422</t>
+        </is>
+      </c>
+      <c r="Z130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>supervision of person source</t>
+          <t>spouse or partner</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>family member</t>
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
@@ -8281,7 +8265,7 @@
       <c r="P131" s="2" t="n"/>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>supervised</t>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
         </is>
       </c>
       <c r="R131" s="2" t="n"/>
@@ -8305,22 +8289,22 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">target behaviour of person source </t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>socio demographic attribute of person source</t>
+          <t>role</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
@@ -8335,11 +8319,7 @@
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="2" t="n"/>
       <c r="P132" s="2" t="n"/>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>source is highly physically active</t>
-        </is>
-      </c>
+      <c r="Q132" s="2" t="n"/>
       <c r="R132" s="2" t="n"/>
       <c r="S132" s="2" t="n"/>
       <c r="T132" s="2" t="inlineStr">
@@ -8356,31 +8336,39 @@
       <c r="W132" s="2" t="n"/>
       <c r="X132" s="2" t="n"/>
       <c r="Y132" s="2" t="n"/>
-      <c r="Z132" s="2" t="n"/>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010128</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teachers’ aide </t>
+          <t>supervision of person source</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">personal care worker </t>
+          <t>process</t>
         </is>
       </c>
       <c r="E133" s="2" t="n"/>
-      <c r="F133" s="2" t="n"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="G133" s="2" t="n"/>
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="2" t="n"/>
@@ -8393,14 +8381,10 @@
       <c r="P133" s="2" t="n"/>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
-      <c r="R133" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>supervised</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="n"/>
       <c r="S133" s="2" t="n"/>
       <c r="T133" s="2" t="inlineStr">
         <is>
@@ -8415,32 +8399,28 @@
       </c>
       <c r="W133" s="2" t="n"/>
       <c r="X133" s="2" t="n"/>
-      <c r="Y133" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 5312</t>
-        </is>
-      </c>
+      <c r="Y133" s="2" t="n"/>
       <c r="Z133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t xml:space="preserve">target behaviour of person source </t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>socio demographic attribute of person source</t>
         </is>
       </c>
       <c r="E134" s="2" t="n"/>
@@ -8457,14 +8437,10 @@
       <c r="P134" s="2" t="n"/>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
-        </is>
-      </c>
-      <c r="R134" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>source is highly physically active</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="n"/>
       <c r="S134" s="2" t="n"/>
       <c r="T134" s="2" t="inlineStr">
         <is>
@@ -8479,32 +8455,28 @@
       </c>
       <c r="W134" s="2" t="n"/>
       <c r="X134" s="2" t="n"/>
-      <c r="Y134" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 23</t>
-        </is>
-      </c>
+      <c r="Y134" s="2" t="n"/>
       <c r="Z134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician and associate professional </t>
+          <t xml:space="preserve">teachers’ aide </t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations. </t>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t xml:space="preserve">personal care worker </t>
         </is>
       </c>
       <c r="E135" s="2" t="n"/>
@@ -8519,7 +8491,11 @@
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="2" t="n"/>
       <c r="P135" s="2" t="n"/>
-      <c r="Q135" s="2" t="n"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>Pre-school assistant, Teacher’s assistant</t>
+        </is>
+      </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -8541,7 +8517,7 @@
       <c r="X135" s="2" t="n"/>
       <c r="Y135" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 3</t>
+          <t>ISCO: 5312</t>
         </is>
       </c>
       <c r="Z135" s="2" t="n"/>
@@ -8549,22 +8525,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>total number of people able to deliver intervention</t>
+          <t xml:space="preserve">teaching professional </t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A count data item that is the total number of providers that are available and able to deliver the intervention. </t>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
@@ -8576,15 +8552,19 @@
       <c r="K136" s="2" t="n"/>
       <c r="L136" s="2" t="n"/>
       <c r="M136" s="2" t="n"/>
-      <c r="N136" s="2" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="N136" s="2" t="n"/>
       <c r="O136" s="2" t="n"/>
       <c r="P136" s="2" t="n"/>
-      <c r="Q136" s="2" t="n"/>
-      <c r="R136" s="2" t="n"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S136" s="2" t="n"/>
       <c r="T136" s="2" t="inlineStr">
         <is>
@@ -8599,28 +8579,32 @@
       </c>
       <c r="W136" s="2" t="n"/>
       <c r="X136" s="2" t="n"/>
-      <c r="Y136" s="2" t="n"/>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 23</t>
+        </is>
+      </c>
       <c r="Z136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">traditional and complementary medicine associate professional </t>
+          <t xml:space="preserve">technician and associate professional </t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional. </t>
+          <t xml:space="preserve">A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations. </t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health associate professional </t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
@@ -8635,11 +8619,7 @@
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="2" t="n"/>
       <c r="P137" s="2" t="n"/>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
-        </is>
-      </c>
+      <c r="Q137" s="2" t="n"/>
       <c r="R137" s="2" t="inlineStr">
         <is>
           <t>International Standard Classification of Occupations (ISCO)</t>
@@ -8661,7 +8641,7 @@
       <c r="X137" s="2" t="n"/>
       <c r="Y137" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 323</t>
+          <t>ISCO: 3</t>
         </is>
       </c>
       <c r="Z137" s="2" t="n"/>
@@ -8669,22 +8649,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">traditional and complementary medicine professional </t>
+          <t>total number of people able to deliver intervention</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+          <t xml:space="preserve">A count data item that is the total number of providers that are available and able to deliver the intervention. </t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E138" s="2" t="n"/>
@@ -8696,19 +8676,15 @@
       <c r="K138" s="2" t="n"/>
       <c r="L138" s="2" t="n"/>
       <c r="M138" s="2" t="n"/>
-      <c r="N138" s="2" t="n"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="O138" s="2" t="n"/>
       <c r="P138" s="2" t="n"/>
-      <c r="Q138" s="2" t="inlineStr">
-        <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
-        </is>
-      </c>
-      <c r="R138" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q138" s="2" t="n"/>
+      <c r="R138" s="2" t="n"/>
       <c r="S138" s="2" t="n"/>
       <c r="T138" s="2" t="inlineStr">
         <is>
@@ -8723,32 +8699,28 @@
       </c>
       <c r="W138" s="2" t="n"/>
       <c r="X138" s="2" t="n"/>
-      <c r="Y138" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 223</t>
-        </is>
-      </c>
+      <c r="Y138" s="2" t="n"/>
       <c r="Z138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>trainee role</t>
+          <t xml:space="preserve">traditional and complementary medicine associate professional </t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t xml:space="preserve">A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional. </t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t xml:space="preserve">health associate professional </t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -8763,8 +8735,16 @@
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="2" t="n"/>
       <c r="P139" s="2" t="n"/>
-      <c r="Q139" s="2" t="n"/>
-      <c r="R139" s="2" t="n"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S139" s="2" t="n"/>
       <c r="T139" s="2" t="inlineStr">
         <is>
@@ -8779,28 +8759,32 @@
       </c>
       <c r="W139" s="2" t="n"/>
       <c r="X139" s="2" t="n"/>
-      <c r="Y139" s="2" t="n"/>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 323</t>
+        </is>
+      </c>
       <c r="Z139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>undergraduate student role</t>
+          <t xml:space="preserve">traditional and complementary medicine professional </t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>higher education student role</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
@@ -8817,10 +8801,14 @@
       <c r="P140" s="2" t="n"/>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="n"/>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S140" s="2" t="n"/>
       <c r="T140" s="2" t="inlineStr">
         <is>
@@ -8835,29 +8823,32 @@
       </c>
       <c r="W140" s="2" t="n"/>
       <c r="X140" s="2" t="n"/>
-      <c r="Y140" s="2" t="n"/>
+      <c r="Y140" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 223</t>
+        </is>
+      </c>
       <c r="Z140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">university and higher education teacher
-</t>
+          <t>trainee role</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">teaching professional </t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
@@ -8872,16 +8863,8 @@
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="2" t="n"/>
       <c r="P141" s="2" t="n"/>
-      <c r="Q141" s="2" t="inlineStr">
-        <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
-      <c r="R141" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+      <c r="Q141" s="2" t="n"/>
+      <c r="R141" s="2" t="n"/>
       <c r="S141" s="2" t="n"/>
       <c r="T141" s="2" t="inlineStr">
         <is>
@@ -8896,32 +8879,28 @@
       </c>
       <c r="W141" s="2" t="n"/>
       <c r="X141" s="2" t="n"/>
-      <c r="Y141" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 231</t>
-        </is>
-      </c>
+      <c r="Y141" s="2" t="n"/>
       <c r="Z141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">veterinarian </t>
+          <t>undergraduate student role</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals. </t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">health professional </t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="E142" s="2" t="n"/>
@@ -8938,14 +8917,10 @@
       <c r="P142" s="2" t="n"/>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
-        </is>
-      </c>
-      <c r="R142" s="2" t="inlineStr">
-        <is>
-          <t>International Standard Classification of Occupations (ISCO)</t>
-        </is>
-      </c>
+          <t>undergraduate student</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="n"/>
       <c r="S142" s="2" t="n"/>
       <c r="T142" s="2" t="inlineStr">
         <is>
@@ -8960,27 +8935,24 @@
       </c>
       <c r="W142" s="2" t="n"/>
       <c r="X142" s="2" t="n"/>
-      <c r="Y142" s="2" t="inlineStr">
-        <is>
-          <t>ISCO: 225</t>
-        </is>
-      </c>
+      <c r="Y142" s="2" t="n"/>
       <c r="Z142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>vocational education teacher</t>
+          <t xml:space="preserve">university and higher education teacher
+</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges. </t>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -9002,7 +8974,7 @@
       <c r="P143" s="2" t="n"/>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr">
@@ -9026,7 +8998,7 @@
       <c r="X143" s="2" t="n"/>
       <c r="Y143" s="2" t="inlineStr">
         <is>
-          <t>ISCO: 232</t>
+          <t>ISCO: 231</t>
         </is>
       </c>
       <c r="Z143" s="2" t="n"/>
@@ -9034,30 +9006,26 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>volunteering of person source</t>
+          <t xml:space="preserve">veterinarian </t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+          <t xml:space="preserve">A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals. </t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>process</t>
+          <t xml:space="preserve">health professional </t>
         </is>
       </c>
       <c r="E144" s="2" t="n"/>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
@@ -9070,10 +9038,14 @@
       <c r="P144" s="2" t="n"/>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
-      <c r="R144" s="2" t="n"/>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
       <c r="S144" s="2" t="n"/>
       <c r="T144" s="2" t="inlineStr">
         <is>
@@ -9088,8 +9060,136 @@
       </c>
       <c r="W144" s="2" t="n"/>
       <c r="X144" s="2" t="n"/>
-      <c r="Y144" s="2" t="n"/>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 225</t>
+        </is>
+      </c>
       <c r="Z144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010027</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>vocational education teacher</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges. </t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teaching professional </t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="n"/>
+      <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
+      <c r="J145" s="2" t="n"/>
+      <c r="K145" s="2" t="n"/>
+      <c r="L145" s="2" t="n"/>
+      <c r="M145" s="2" t="n"/>
+      <c r="N145" s="2" t="n"/>
+      <c r="O145" s="2" t="n"/>
+      <c r="P145" s="2" t="n"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>International Standard Classification of Occupations (ISCO)</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="n"/>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U145" s="2" t="n"/>
+      <c r="V145" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W145" s="2" t="n"/>
+      <c r="X145" s="2" t="n"/>
+      <c r="Y145" s="2" t="inlineStr">
+        <is>
+          <t>ISCO: 232</t>
+        </is>
+      </c>
+      <c r="Z145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>BCIO:010129</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>volunteering of person source</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="n"/>
+      <c r="H146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+      <c r="J146" s="2" t="n"/>
+      <c r="K146" s="2" t="n"/>
+      <c r="L146" s="2" t="n"/>
+      <c r="M146" s="2" t="n"/>
+      <c r="N146" s="2" t="n"/>
+      <c r="O146" s="2" t="n"/>
+      <c r="P146" s="2" t="n"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="n"/>
+      <c r="S146" s="2" t="n"/>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U146" s="2" t="n"/>
+      <c r="V146" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="W146" s="2" t="n"/>
+      <c r="X146" s="2" t="n"/>
+      <c r="Y146" s="2" t="n"/>
+      <c r="Z146" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -618,60 +618,64 @@
       <c r="Z2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>BCIO:010127</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>affiliation to a formal group or organisation</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>pre-existing knowledge or skill</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>member of British Psychological Society</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="n"/>
-      <c r="X3" s="2" t="n"/>
-      <c r="Y3" s="2" t="n"/>
-      <c r="Z3" s="2" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Please refer to class "certified professional role" (BCIO:051024)</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="n"/>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="3" t="n"/>
+      <c r="Z3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -821,7 +825,7 @@
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>knowledge or skill</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="O6" s="2" t="n"/>
@@ -1538,32 +1542,32 @@
           <t>personal role</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr"/>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="2" t="n"/>
+      <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr"/>
-      <c r="X18" s="2" t="inlineStr"/>
-      <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="n"/>
+      <c r="X18" s="2" t="n"/>
+      <c r="Y18" s="2" t="n"/>
+      <c r="Z18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2253,7 +2257,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>discipline of pre-existing knowledge or skill</t>
+          <t>discipline of pre-existing expertise</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2278,7 +2282,7 @@
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>pre-existing knowledge or skill</t>
+          <t>pre-existing expertise</t>
         </is>
       </c>
       <c r="P30" s="2" t="n"/>
@@ -6039,36 +6043,36 @@
           <t>role</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
-      <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="n"/>
+      <c r="L94" s="2" t="n"/>
+      <c r="M94" s="2" t="n"/>
+      <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="n"/>
+      <c r="P94" s="2" t="n"/>
+      <c r="Q94" s="2" t="n"/>
+      <c r="R94" s="2" t="n"/>
       <c r="S94" s="2" t="inlineStr">
         <is>
           <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
         </is>
       </c>
-      <c r="T94" s="2" t="inlineStr"/>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="n"/>
+      <c r="U94" s="2" t="n"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr"/>
-      <c r="X94" s="2" t="inlineStr"/>
-      <c r="Y94" s="2" t="inlineStr"/>
-      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="n"/>
+      <c r="X94" s="2" t="n"/>
+      <c r="Y94" s="2" t="n"/>
+      <c r="Z94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -3744,7 +3744,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">

--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>Definition_ID</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Reviewer query</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Definition_ID</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -785,12 +785,12 @@
         </is>
       </c>
       <c r="W5" s="2" t="n"/>
-      <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3258</t>
         </is>
       </c>
+      <c r="Y5" s="2" t="n"/>
       <c r="Z5" s="2" t="n"/>
     </row>
     <row r="6">
@@ -909,12 +909,12 @@
         </is>
       </c>
       <c r="W7" s="2" t="n"/>
-      <c r="X7" s="2" t="n"/>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>ISCO: 10</t>
         </is>
       </c>
+      <c r="Y7" s="2" t="n"/>
       <c r="Z7" s="2" t="n"/>
     </row>
     <row r="8">
@@ -973,12 +973,12 @@
         </is>
       </c>
       <c r="W8" s="2" t="n"/>
-      <c r="X8" s="2" t="n"/>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>ISCO: 343</t>
         </is>
       </c>
+      <c r="Y8" s="2" t="n"/>
       <c r="Z8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -1037,12 +1037,12 @@
         </is>
       </c>
       <c r="W9" s="2" t="n"/>
-      <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2355</t>
         </is>
       </c>
+      <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="n"/>
     </row>
     <row r="10">
@@ -1097,12 +1097,12 @@
         </is>
       </c>
       <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>ISCO: 8</t>
         </is>
       </c>
+      <c r="Y10" s="2" t="n"/>
       <c r="Z10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -1161,12 +1161,12 @@
         </is>
       </c>
       <c r="W11" s="2" t="n"/>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3421</t>
         </is>
       </c>
+      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
     </row>
     <row r="12">
@@ -1225,12 +1225,12 @@
         </is>
       </c>
       <c r="W12" s="2" t="n"/>
-      <c r="X12" s="2" t="n"/>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ISCO: 2266 </t>
         </is>
       </c>
+      <c r="Y12" s="2" t="n"/>
       <c r="Z12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -1289,12 +1289,12 @@
         </is>
       </c>
       <c r="W13" s="2" t="n"/>
-      <c r="X13" s="2" t="n"/>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>ISCO: 264</t>
         </is>
       </c>
+      <c r="Y13" s="2" t="n"/>
       <c r="Z13" s="2" t="n"/>
     </row>
     <row r="14">
@@ -1457,12 +1457,12 @@
         </is>
       </c>
       <c r="W16" s="2" t="n"/>
-      <c r="X16" s="2" t="n"/>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>ISCO: 33</t>
         </is>
       </c>
+      <c r="Y16" s="2" t="n"/>
       <c r="Z16" s="2" t="n"/>
     </row>
     <row r="17">
@@ -1625,12 +1625,12 @@
         </is>
       </c>
       <c r="W19" s="2" t="n"/>
-      <c r="X19" s="2" t="n"/>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>ISCO: 5311</t>
         </is>
       </c>
+      <c r="Y19" s="2" t="n"/>
       <c r="Z19" s="2" t="n"/>
     </row>
     <row r="20">
@@ -1745,12 +1745,12 @@
         </is>
       </c>
       <c r="W21" s="2" t="n"/>
-      <c r="X21" s="2" t="n"/>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>ISCO: 4</t>
         </is>
       </c>
+      <c r="Y21" s="2" t="n"/>
       <c r="Z21" s="2" t="n"/>
     </row>
     <row r="22">
@@ -1861,12 +1861,12 @@
         </is>
       </c>
       <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3253</t>
         </is>
       </c>
+      <c r="Y23" s="2" t="n"/>
       <c r="Z23" s="2" t="n"/>
     </row>
     <row r="24">
@@ -1925,12 +1925,12 @@
         </is>
       </c>
       <c r="W24" s="2" t="n"/>
-      <c r="X24" s="2" t="n"/>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>ISCO: 7</t>
         </is>
       </c>
+      <c r="Y24" s="2" t="n"/>
       <c r="Z24" s="2" t="n"/>
     </row>
     <row r="25">
@@ -1989,12 +1989,12 @@
         </is>
       </c>
       <c r="W25" s="2" t="n"/>
-      <c r="X25" s="2" t="n"/>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>ISCO: 265</t>
         </is>
       </c>
+      <c r="Y25" s="2" t="n"/>
       <c r="Z25" s="2" t="n"/>
     </row>
     <row r="26">
@@ -2053,12 +2053,12 @@
         </is>
       </c>
       <c r="W26" s="2" t="n"/>
-      <c r="X26" s="2" t="n"/>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3251</t>
         </is>
       </c>
+      <c r="Y26" s="2" t="n"/>
       <c r="Z26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -2117,12 +2117,12 @@
         </is>
       </c>
       <c r="W27" s="2" t="n"/>
-      <c r="X27" s="2" t="n"/>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2261</t>
         </is>
       </c>
+      <c r="Y27" s="2" t="n"/>
       <c r="Z27" s="2" t="n"/>
     </row>
     <row r="28">
@@ -2181,12 +2181,12 @@
         </is>
       </c>
       <c r="W28" s="2" t="n"/>
-      <c r="X28" s="2" t="n"/>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2265</t>
         </is>
       </c>
+      <c r="Y28" s="2" t="n"/>
       <c r="Z28" s="2" t="n"/>
     </row>
     <row r="29">
@@ -2421,12 +2421,12 @@
         </is>
       </c>
       <c r="W32" s="2" t="n"/>
-      <c r="X32" s="2" t="n"/>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2342</t>
         </is>
       </c>
+      <c r="Y32" s="2" t="n"/>
       <c r="Z32" s="2" t="n"/>
     </row>
     <row r="33">
@@ -2485,12 +2485,12 @@
         </is>
       </c>
       <c r="W33" s="2" t="n"/>
-      <c r="X33" s="2" t="n"/>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>ISCO: 9</t>
         </is>
       </c>
+      <c r="Y33" s="2" t="n"/>
       <c r="Z33" s="2" t="n"/>
     </row>
     <row r="34">
@@ -2653,12 +2653,12 @@
         </is>
       </c>
       <c r="W36" s="2" t="n"/>
-      <c r="X36" s="2" t="n"/>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2263</t>
         </is>
       </c>
+      <c r="Y36" s="2" t="n"/>
       <c r="Z36" s="2" t="n"/>
     </row>
     <row r="37">
@@ -2719,12 +2719,12 @@
         </is>
       </c>
       <c r="W37" s="2" t="n"/>
-      <c r="X37" s="2" t="n"/>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3257</t>
         </is>
       </c>
+      <c r="Y37" s="2" t="n"/>
       <c r="Z37" s="2" t="n"/>
     </row>
     <row r="38">
@@ -3071,12 +3071,12 @@
         </is>
       </c>
       <c r="W43" s="2" t="n"/>
-      <c r="X43" s="2" t="n"/>
-      <c r="Y43" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3423</t>
         </is>
       </c>
+      <c r="Y43" s="2" t="n"/>
       <c r="Z43" s="2" t="n"/>
     </row>
     <row r="44">
@@ -3299,12 +3299,12 @@
         </is>
       </c>
       <c r="W47" s="2" t="n"/>
-      <c r="X47" s="2" t="n"/>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="X47" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2211</t>
         </is>
       </c>
+      <c r="Y47" s="2" t="n"/>
       <c r="Z47" s="2" t="n"/>
     </row>
     <row r="48">
@@ -3419,12 +3419,12 @@
         </is>
       </c>
       <c r="W49" s="2" t="n"/>
-      <c r="X49" s="2" t="n"/>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr">
         <is>
           <t>ISCO: 32</t>
         </is>
       </c>
+      <c r="Y49" s="2" t="n"/>
       <c r="Z49" s="2" t="n"/>
     </row>
     <row r="50">
@@ -3483,12 +3483,12 @@
         </is>
       </c>
       <c r="W50" s="2" t="n"/>
-      <c r="X50" s="2" t="n"/>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="X50" s="2" t="inlineStr">
         <is>
           <t>ISCO: 5321</t>
         </is>
       </c>
+      <c r="Y50" s="2" t="n"/>
       <c r="Z50" s="2" t="n"/>
     </row>
     <row r="51">
@@ -3547,12 +3547,12 @@
         </is>
       </c>
       <c r="W51" s="2" t="n"/>
-      <c r="X51" s="2" t="n"/>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="X51" s="2" t="inlineStr">
         <is>
           <t>ISCO: 22</t>
         </is>
       </c>
+      <c r="Y51" s="2" t="n"/>
       <c r="Z51" s="2" t="n"/>
     </row>
     <row r="52">
@@ -3723,12 +3723,12 @@
         </is>
       </c>
       <c r="W54" s="2" t="n"/>
-      <c r="X54" s="2" t="n"/>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="X54" s="2" t="inlineStr">
         <is>
           <t>ISCO: 5322</t>
         </is>
       </c>
+      <c r="Y54" s="2" t="n"/>
       <c r="Z54" s="2" t="n"/>
     </row>
     <row r="55">
@@ -3839,12 +3839,12 @@
         </is>
       </c>
       <c r="W56" s="2" t="n"/>
-      <c r="X56" s="2" t="n"/>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="X56" s="2" t="inlineStr">
         <is>
           <t>ISCO: 35</t>
         </is>
       </c>
+      <c r="Y56" s="2" t="n"/>
       <c r="Z56" s="2" t="n"/>
     </row>
     <row r="57">
@@ -4015,12 +4015,12 @@
         </is>
       </c>
       <c r="W59" s="2" t="n"/>
-      <c r="X59" s="2" t="n"/>
-      <c r="Y59" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3411</t>
         </is>
       </c>
+      <c r="Y59" s="2" t="n"/>
       <c r="Z59" s="2" t="n"/>
     </row>
     <row r="60">
@@ -4079,12 +4079,12 @@
         </is>
       </c>
       <c r="W60" s="2" t="n"/>
-      <c r="X60" s="2" t="n"/>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="X60" s="2" t="inlineStr">
         <is>
           <t>ISCO: 261</t>
         </is>
       </c>
+      <c r="Y60" s="2" t="n"/>
       <c r="Z60" s="2" t="n"/>
     </row>
     <row r="61">
@@ -4139,12 +4139,12 @@
         </is>
       </c>
       <c r="W61" s="2" t="n"/>
-      <c r="X61" s="2" t="n"/>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>ISCO: 26</t>
         </is>
       </c>
+      <c r="Y61" s="2" t="n"/>
       <c r="Z61" s="2" t="n"/>
     </row>
     <row r="62">
@@ -4203,12 +4203,12 @@
         </is>
       </c>
       <c r="W62" s="2" t="n"/>
-      <c r="X62" s="2" t="n"/>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="X62" s="2" t="inlineStr">
         <is>
           <t>ISCO: 262</t>
         </is>
       </c>
+      <c r="Y62" s="2" t="n"/>
       <c r="Z62" s="2" t="n"/>
     </row>
     <row r="63">
@@ -4383,12 +4383,12 @@
         </is>
       </c>
       <c r="W65" s="2" t="n"/>
-      <c r="X65" s="2" t="n"/>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="X65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ISCO: 1 </t>
         </is>
       </c>
+      <c r="Y65" s="2" t="n"/>
       <c r="Z65" s="2" t="n"/>
     </row>
     <row r="66">
@@ -4503,12 +4503,12 @@
         </is>
       </c>
       <c r="W67" s="2" t="n"/>
-      <c r="X67" s="2" t="n"/>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
         <is>
           <t>ISCO: 321</t>
         </is>
       </c>
+      <c r="Y67" s="2" t="n"/>
       <c r="Z67" s="2" t="n"/>
     </row>
     <row r="68">
@@ -4567,12 +4567,12 @@
         </is>
       </c>
       <c r="W68" s="2" t="n"/>
-      <c r="X68" s="2" t="n"/>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3256</t>
         </is>
       </c>
+      <c r="Y68" s="2" t="n"/>
       <c r="Z68" s="2" t="n"/>
     </row>
     <row r="69">
@@ -4631,12 +4631,12 @@
         </is>
       </c>
       <c r="W69" s="2" t="n"/>
-      <c r="X69" s="2" t="n"/>
-      <c r="Y69" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>ISCO: 221</t>
         </is>
       </c>
+      <c r="Y69" s="2" t="n"/>
       <c r="Z69" s="2" t="n"/>
     </row>
     <row r="70">
@@ -4695,12 +4695,12 @@
         </is>
       </c>
       <c r="W70" s="2" t="n"/>
-      <c r="X70" s="2" t="n"/>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="X70" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3222</t>
         </is>
       </c>
+      <c r="Y70" s="2" t="n"/>
       <c r="Z70" s="2" t="n"/>
     </row>
     <row r="71">
@@ -4759,12 +4759,12 @@
         </is>
       </c>
       <c r="W71" s="2" t="n"/>
-      <c r="X71" s="2" t="n"/>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2222</t>
         </is>
       </c>
+      <c r="Y71" s="2" t="n"/>
       <c r="Z71" s="2" t="n"/>
     </row>
     <row r="72">
@@ -4879,12 +4879,12 @@
         </is>
       </c>
       <c r="W73" s="2" t="n"/>
-      <c r="X73" s="2" t="n"/>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2354</t>
         </is>
       </c>
+      <c r="Y73" s="2" t="n"/>
       <c r="Z73" s="2" t="n"/>
     </row>
     <row r="74">
@@ -5055,12 +5055,12 @@
         </is>
       </c>
       <c r="W76" s="2" t="n"/>
-      <c r="X76" s="2" t="n"/>
-      <c r="Y76" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>ISCO: 322</t>
         </is>
       </c>
+      <c r="Y76" s="2" t="n"/>
       <c r="Z76" s="2" t="n"/>
     </row>
     <row r="77">
@@ -5115,12 +5115,12 @@
         </is>
       </c>
       <c r="W77" s="2" t="n"/>
-      <c r="X77" s="2" t="n"/>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>ISCO: 222</t>
         </is>
       </c>
+      <c r="Y77" s="2" t="n"/>
       <c r="Z77" s="2" t="n"/>
     </row>
     <row r="78">
@@ -5179,12 +5179,12 @@
         </is>
       </c>
       <c r="W78" s="2" t="n"/>
-      <c r="X78" s="2" t="n"/>
-      <c r="Y78" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3221</t>
         </is>
       </c>
+      <c r="Y78" s="2" t="n"/>
       <c r="Z78" s="2" t="n"/>
     </row>
     <row r="79">
@@ -5243,12 +5243,12 @@
         </is>
       </c>
       <c r="W79" s="2" t="n"/>
-      <c r="X79" s="2" t="n"/>
-      <c r="Y79" s="2" t="inlineStr">
+      <c r="X79" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2221</t>
         </is>
       </c>
+      <c r="Y79" s="2" t="n"/>
       <c r="Z79" s="2" t="n"/>
     </row>
     <row r="80">
@@ -5363,12 +5363,12 @@
         </is>
       </c>
       <c r="W81" s="2" t="n"/>
-      <c r="X81" s="2" t="n"/>
-      <c r="Y81" s="2" t="inlineStr">
+      <c r="X81" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2267</t>
         </is>
       </c>
+      <c r="Y81" s="2" t="n"/>
       <c r="Z81" s="2" t="n"/>
     </row>
     <row r="82">
@@ -5637,12 +5637,12 @@
         </is>
       </c>
       <c r="W86" s="2" t="n"/>
-      <c r="X86" s="2" t="n"/>
-      <c r="Y86" s="2" t="inlineStr">
+      <c r="X86" s="2" t="inlineStr">
         <is>
           <t>ISCO: 224</t>
         </is>
       </c>
+      <c r="Y86" s="2" t="n"/>
       <c r="Z86" s="2" t="n"/>
     </row>
     <row r="87">
@@ -6014,12 +6014,12 @@
         </is>
       </c>
       <c r="W93" s="2" t="n"/>
-      <c r="X93" s="2" t="n"/>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
         <is>
           <t>ISCO: 53</t>
         </is>
       </c>
+      <c r="Y93" s="2" t="n"/>
       <c r="Z93" s="2" t="n"/>
     </row>
     <row r="94">
@@ -6182,12 +6182,12 @@
         </is>
       </c>
       <c r="W96" s="2" t="n"/>
-      <c r="X96" s="2" t="n"/>
-      <c r="Y96" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>ISCO: 51</t>
         </is>
       </c>
+      <c r="Y96" s="2" t="n"/>
       <c r="Z96" s="2" t="n"/>
     </row>
     <row r="97">
@@ -6246,12 +6246,12 @@
         </is>
       </c>
       <c r="W97" s="2" t="n"/>
-      <c r="X97" s="2" t="n"/>
-      <c r="Y97" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2262</t>
         </is>
       </c>
+      <c r="Y97" s="2" t="n"/>
       <c r="Z97" s="2" t="n"/>
     </row>
     <row r="98">
@@ -6310,12 +6310,12 @@
         </is>
       </c>
       <c r="W98" s="2" t="n"/>
-      <c r="X98" s="2" t="n"/>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2264</t>
         </is>
       </c>
+      <c r="Y98" s="2" t="n"/>
       <c r="Z98" s="2" t="n"/>
     </row>
     <row r="99">
@@ -6374,12 +6374,12 @@
         </is>
       </c>
       <c r="W99" s="2" t="n"/>
-      <c r="X99" s="2" t="n"/>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3255</t>
         </is>
       </c>
+      <c r="Y99" s="2" t="n"/>
       <c r="Z99" s="2" t="n"/>
     </row>
     <row r="100">
@@ -6438,12 +6438,12 @@
         </is>
       </c>
       <c r="W100" s="2" t="n"/>
-      <c r="X100" s="2" t="n"/>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="X100" s="2" t="inlineStr">
         <is>
           <t>ISCO: 8</t>
         </is>
       </c>
+      <c r="Y100" s="2" t="n"/>
       <c r="Z100" s="2" t="n"/>
     </row>
     <row r="101">
@@ -6554,12 +6554,12 @@
         </is>
       </c>
       <c r="W102" s="2" t="n"/>
-      <c r="X102" s="2" t="n"/>
-      <c r="Y102" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2341</t>
         </is>
       </c>
+      <c r="Y102" s="2" t="n"/>
       <c r="Z102" s="2" t="n"/>
     </row>
     <row r="103">
@@ -6614,12 +6614,12 @@
         </is>
       </c>
       <c r="W103" s="2" t="n"/>
-      <c r="X103" s="2" t="n"/>
-      <c r="Y103" s="2" t="inlineStr">
+      <c r="X103" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2</t>
         </is>
       </c>
+      <c r="Y103" s="2" t="n"/>
       <c r="Z103" s="2" t="n"/>
     </row>
     <row r="104">
@@ -6678,12 +6678,12 @@
         </is>
       </c>
       <c r="W104" s="2" t="n"/>
-      <c r="X104" s="2" t="n"/>
-      <c r="Y104" s="2" t="inlineStr">
+      <c r="X104" s="2" t="inlineStr">
         <is>
           <t>ISCO: 54</t>
         </is>
       </c>
+      <c r="Y104" s="2" t="n"/>
       <c r="Z104" s="2" t="n"/>
     </row>
     <row r="105">
@@ -6794,12 +6794,12 @@
         </is>
       </c>
       <c r="W106" s="2" t="n"/>
-      <c r="X106" s="2" t="n"/>
-      <c r="Y106" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2634</t>
         </is>
       </c>
+      <c r="Y106" s="2" t="n"/>
       <c r="Z106" s="2" t="n"/>
     </row>
     <row r="107">
@@ -6910,12 +6910,12 @@
         </is>
       </c>
       <c r="W108" s="2" t="n"/>
-      <c r="X108" s="2" t="n"/>
-      <c r="Y108" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3413</t>
         </is>
       </c>
+      <c r="Y108" s="2" t="n"/>
       <c r="Z108" s="2" t="n"/>
     </row>
     <row r="109">
@@ -7030,12 +7030,12 @@
         </is>
       </c>
       <c r="W110" s="2" t="n"/>
-      <c r="X110" s="2" t="n"/>
-      <c r="Y110" s="2" t="inlineStr">
+      <c r="X110" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2636</t>
         </is>
       </c>
+      <c r="Y110" s="2" t="n"/>
       <c r="Z110" s="2" t="n"/>
     </row>
     <row r="111">
@@ -7206,12 +7206,12 @@
         </is>
       </c>
       <c r="W113" s="2" t="n"/>
-      <c r="X113" s="2" t="n"/>
-      <c r="Y113" s="2" t="inlineStr">
+      <c r="X113" s="2" t="inlineStr">
         <is>
           <t>ISCO: 52</t>
         </is>
       </c>
+      <c r="Y113" s="2" t="n"/>
       <c r="Z113" s="2" t="n"/>
     </row>
     <row r="114">
@@ -7322,12 +7322,12 @@
         </is>
       </c>
       <c r="W115" s="2" t="n"/>
-      <c r="X115" s="2" t="n"/>
-      <c r="Y115" s="2" t="inlineStr">
+      <c r="X115" s="2" t="inlineStr">
         <is>
           <t>ISCO: 21</t>
         </is>
       </c>
+      <c r="Y115" s="2" t="n"/>
       <c r="Z115" s="2" t="n"/>
     </row>
     <row r="116">
@@ -7386,12 +7386,12 @@
         </is>
       </c>
       <c r="W116" s="2" t="n"/>
-      <c r="X116" s="2" t="n"/>
-      <c r="Y116" s="2" t="inlineStr">
+      <c r="X116" s="2" t="inlineStr">
         <is>
           <t>ISCO: 233</t>
         </is>
       </c>
+      <c r="Y116" s="2" t="n"/>
       <c r="Z116" s="2" t="n"/>
     </row>
     <row r="117">
@@ -7446,12 +7446,12 @@
         </is>
       </c>
       <c r="W117" s="2" t="n"/>
-      <c r="X117" s="2" t="n"/>
-      <c r="Y117" s="2" t="inlineStr">
+      <c r="X117" s="2" t="inlineStr">
         <is>
           <t>ISCO: 5</t>
         </is>
       </c>
+      <c r="Y117" s="2" t="n"/>
       <c r="Z117" s="2" t="n"/>
     </row>
     <row r="118">
@@ -7566,12 +7566,12 @@
         </is>
       </c>
       <c r="W119" s="2" t="n"/>
-      <c r="X119" s="2" t="n"/>
-      <c r="Y119" s="2" t="inlineStr">
+      <c r="X119" s="2" t="inlineStr">
         <is>
           <t>ISCO: 6</t>
         </is>
       </c>
+      <c r="Y119" s="2" t="n"/>
       <c r="Z119" s="2" t="n"/>
     </row>
     <row r="120">
@@ -7630,12 +7630,12 @@
         </is>
       </c>
       <c r="W120" s="2" t="n"/>
-      <c r="X120" s="2" t="n"/>
-      <c r="Y120" s="2" t="inlineStr">
+      <c r="X120" s="2" t="inlineStr">
         <is>
           <t>ISCO: 263</t>
         </is>
       </c>
+      <c r="Y120" s="2" t="n"/>
       <c r="Z120" s="2" t="n"/>
     </row>
     <row r="121">
@@ -7694,12 +7694,12 @@
         </is>
       </c>
       <c r="W121" s="2" t="n"/>
-      <c r="X121" s="2" t="n"/>
-      <c r="Y121" s="2" t="inlineStr">
+      <c r="X121" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2635</t>
         </is>
       </c>
+      <c r="Y121" s="2" t="n"/>
       <c r="Z121" s="2" t="n"/>
     </row>
     <row r="122">
@@ -7758,12 +7758,12 @@
         </is>
       </c>
       <c r="W122" s="2" t="n"/>
-      <c r="X122" s="2" t="n"/>
-      <c r="Y122" s="2" t="inlineStr">
+      <c r="X122" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3412</t>
         </is>
       </c>
+      <c r="Y122" s="2" t="n"/>
       <c r="Z122" s="2" t="n"/>
     </row>
     <row r="123">
@@ -8034,12 +8034,12 @@
         </is>
       </c>
       <c r="W127" s="2" t="n"/>
-      <c r="X127" s="2" t="n"/>
-      <c r="Y127" s="2" t="inlineStr">
+      <c r="X127" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2352</t>
         </is>
       </c>
+      <c r="Y127" s="2" t="n"/>
       <c r="Z127" s="2" t="n"/>
     </row>
     <row r="128">
@@ -8098,12 +8098,12 @@
         </is>
       </c>
       <c r="W128" s="2" t="n"/>
-      <c r="X128" s="2" t="n"/>
-      <c r="Y128" s="2" t="inlineStr">
+      <c r="X128" s="2" t="inlineStr">
         <is>
           <t>ISCO: 2212</t>
         </is>
       </c>
+      <c r="Y128" s="2" t="n"/>
       <c r="Z128" s="2" t="n"/>
     </row>
     <row r="129">
@@ -8162,12 +8162,12 @@
         </is>
       </c>
       <c r="W129" s="2" t="n"/>
-      <c r="X129" s="2" t="n"/>
-      <c r="Y129" s="2" t="inlineStr">
+      <c r="X129" s="2" t="inlineStr">
         <is>
           <t>ISCO: 342</t>
         </is>
       </c>
+      <c r="Y129" s="2" t="n"/>
       <c r="Z129" s="2" t="n"/>
     </row>
     <row r="130">
@@ -8226,12 +8226,12 @@
         </is>
       </c>
       <c r="W130" s="2" t="n"/>
-      <c r="X130" s="2" t="n"/>
-      <c r="Y130" s="2" t="inlineStr">
+      <c r="X130" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3422</t>
         </is>
       </c>
+      <c r="Y130" s="2" t="n"/>
       <c r="Z130" s="2" t="n"/>
     </row>
     <row r="131">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="E132" s="2" t="n"/>
@@ -8518,12 +8518,12 @@
         </is>
       </c>
       <c r="W135" s="2" t="n"/>
-      <c r="X135" s="2" t="n"/>
-      <c r="Y135" s="2" t="inlineStr">
+      <c r="X135" s="2" t="inlineStr">
         <is>
           <t>ISCO: 5312</t>
         </is>
       </c>
+      <c r="Y135" s="2" t="n"/>
       <c r="Z135" s="2" t="n"/>
     </row>
     <row r="136">
@@ -8582,12 +8582,12 @@
         </is>
       </c>
       <c r="W136" s="2" t="n"/>
-      <c r="X136" s="2" t="n"/>
-      <c r="Y136" s="2" t="inlineStr">
+      <c r="X136" s="2" t="inlineStr">
         <is>
           <t>ISCO: 23</t>
         </is>
       </c>
+      <c r="Y136" s="2" t="n"/>
       <c r="Z136" s="2" t="n"/>
     </row>
     <row r="137">
@@ -8642,12 +8642,12 @@
         </is>
       </c>
       <c r="W137" s="2" t="n"/>
-      <c r="X137" s="2" t="n"/>
-      <c r="Y137" s="2" t="inlineStr">
+      <c r="X137" s="2" t="inlineStr">
         <is>
           <t>ISCO: 3</t>
         </is>
       </c>
+      <c r="Y137" s="2" t="n"/>
       <c r="Z137" s="2" t="n"/>
     </row>
     <row r="138">
@@ -8762,12 +8762,12 @@
         </is>
       </c>
       <c r="W139" s="2" t="n"/>
-      <c r="X139" s="2" t="n"/>
-      <c r="Y139" s="2" t="inlineStr">
+      <c r="X139" s="2" t="inlineStr">
         <is>
           <t>ISCO: 323</t>
         </is>
       </c>
+      <c r="Y139" s="2" t="n"/>
       <c r="Z139" s="2" t="n"/>
     </row>
     <row r="140">
@@ -8826,12 +8826,12 @@
         </is>
       </c>
       <c r="W140" s="2" t="n"/>
-      <c r="X140" s="2" t="n"/>
-      <c r="Y140" s="2" t="inlineStr">
+      <c r="X140" s="2" t="inlineStr">
         <is>
           <t>ISCO: 223</t>
         </is>
       </c>
+      <c r="Y140" s="2" t="n"/>
       <c r="Z140" s="2" t="n"/>
     </row>
     <row r="141">
@@ -8999,12 +8999,12 @@
         </is>
       </c>
       <c r="W143" s="2" t="n"/>
-      <c r="X143" s="2" t="n"/>
-      <c r="Y143" s="2" t="inlineStr">
+      <c r="X143" s="2" t="inlineStr">
         <is>
           <t>ISCO: 231</t>
         </is>
       </c>
+      <c r="Y143" s="2" t="n"/>
       <c r="Z143" s="2" t="n"/>
     </row>
     <row r="144">
@@ -9063,12 +9063,12 @@
         </is>
       </c>
       <c r="W144" s="2" t="n"/>
-      <c r="X144" s="2" t="n"/>
-      <c r="Y144" s="2" t="inlineStr">
+      <c r="X144" s="2" t="inlineStr">
         <is>
           <t>ISCO: 225</t>
         </is>
       </c>
+      <c r="Y144" s="2" t="n"/>
       <c r="Z144" s="2" t="n"/>
     </row>
     <row r="145">
@@ -9127,12 +9127,12 @@
         </is>
       </c>
       <c r="W145" s="2" t="n"/>
-      <c r="X145" s="2" t="n"/>
-      <c r="Y145" s="2" t="inlineStr">
+      <c r="X145" s="2" t="inlineStr">
         <is>
           <t>ISCO: 232</t>
         </is>
       </c>
+      <c r="Y145" s="2" t="n"/>
       <c r="Z145" s="2" t="n"/>
     </row>
     <row r="146">
